--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141958326246824</v>
+        <v>7.141915134747894</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.152417975278728</v>
+        <v>7.152346415041787</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.15590961625906</v>
+        <v>7.155840556405726</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.169363093466322</v>
+        <v>7.16928590146495</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.184281669877153</v>
+        <v>7.184208358392936</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.196175916929655</v>
+        <v>7.196107543954879</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198387947512931</v>
+        <v>7.198326096113864</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192849972615455</v>
+        <v>7.192795276974795</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175093364241725</v>
+        <v>7.175130992224167</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179433935572649</v>
+        <v>7.179514760418872</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.183528373703337</v>
+        <v>7.18360402766521</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.188639326486146</v>
+        <v>7.188713941647864</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.181754844869644</v>
+        <v>7.181889229074523</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.180678564751726</v>
+        <v>7.180833478034693</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182038985369912</v>
+        <v>7.182168652410169</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.167489722395682</v>
+        <v>7.167606922748079</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.153479044641244</v>
+        <v>7.15365072343789</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.146027023114756</v>
+        <v>7.14622225251438</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.141344043573468</v>
+        <v>7.141583316060983</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.121859250110997</v>
+        <v>7.122060378259414</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.108530862644706</v>
+        <v>7.108792855131913</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.099599736878237</v>
+        <v>7.099889285762359</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.071527112616766</v>
+        <v>7.071840841062181</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.046838097055474</v>
+        <v>7.047159063145768</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.044931326119769</v>
+        <v>7.045276897899502</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.042411934753416</v>
+        <v>7.042853433122415</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.048151517834047</v>
+        <v>7.048700761495846</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.051254098979095</v>
+        <v>7.05202137695218</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.007377455133987</v>
+        <v>7.008095712250427</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.961510786907485</v>
+        <v>6.962070922835689</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.962378111083563</v>
+        <v>6.962906525592167</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.941216618540258</v>
+        <v>6.941830539581181</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.894244028674981</v>
+        <v>6.894565448977231</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.857550293297995</v>
+        <v>6.857880555303108</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.844128405369767</v>
+        <v>6.844368598218135</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.827376425498148</v>
+        <v>6.82706066554935</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.846980095379051</v>
+        <v>6.846586471792289</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.865565063292916</v>
+        <v>6.864829237302983</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.89220618246571</v>
+        <v>6.891852787524804</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.893041215440542</v>
+        <v>6.892833981624644</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.882476165609287</v>
+        <v>6.882111431197228</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.868734474958361</v>
+        <v>6.869011649674838</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.844255034666078</v>
+        <v>6.844400474493209</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.838992591769089</v>
+        <v>6.839239767391252</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.811674560204878</v>
+        <v>6.811430790507313</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.827750047913041</v>
+        <v>6.823518084499719</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.832882532906169</v>
+        <v>6.826705756188283</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.831770140349987</v>
+        <v>6.825335695088658</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.83066549667639</v>
+        <v>6.822651836739901</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.830758436054071</v>
+        <v>6.820694904139916</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.834277909671528</v>
+        <v>6.819844670387181</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.81070190337412</v>
+        <v>6.797674832711242</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.826051975383916</v>
+        <v>6.804596236059741</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.81787291497519</v>
+        <v>6.792255898465629</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.816613542717156</v>
+        <v>6.784588115740426</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.816790895973863</v>
+        <v>6.778477529446984</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.811976115399329</v>
+        <v>6.765789844563111</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.804037779944396</v>
+        <v>6.750491992992793</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,15 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.8126</v>
+        <v>6.719239304410019</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B101">
+        <v>6.695842089873302</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141915134747894</v>
+        <v>7.141895157631538</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.152346415041787</v>
+        <v>7.152313297447041</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155840556405726</v>
+        <v>7.15580855436618</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.16928590146495</v>
+        <v>7.169250123368686</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.184208358392936</v>
+        <v>7.184174383478681</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.196107543954879</v>
+        <v>7.196075861999596</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198326096113864</v>
+        <v>7.19829743704271</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192795276974795</v>
+        <v>7.192769932542856</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175130992224167</v>
+        <v>7.175148241377338</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179514760418872</v>
+        <v>7.179552106074199</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.18360402766521</v>
+        <v>7.183638989517728</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.188713941647864</v>
+        <v>7.188748427408472</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.181889229074523</v>
+        <v>7.181951351956213</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.180833478034693</v>
+        <v>7.180905152058571</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182168652410169</v>
+        <v>7.182228637493563</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.167606922748079</v>
+        <v>7.167661019361782</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.15365072343789</v>
+        <v>7.153730041706551</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.14622225251438</v>
+        <v>7.146312487414873</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.141583316060983</v>
+        <v>7.14169401542798</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.122060378259414</v>
+        <v>7.122153276502977</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.108792855131913</v>
+        <v>7.10891419539634</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.099889285762359</v>
+        <v>7.100023620294582</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.071840841062181</v>
+        <v>7.071986710762535</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.047159063145768</v>
+        <v>7.047308327484066</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.045276897899502</v>
+        <v>7.045437437582136</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.042853433122415</v>
+        <v>7.043058117311547</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.048700761495846</v>
+        <v>7.048955214947258</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.05202137695218</v>
+        <v>7.052376670963014</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.008095712250427</v>
+        <v>7.008427760351516</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.962070922835689</v>
+        <v>6.962330742644747</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.962906525592167</v>
+        <v>6.963152247139778</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.941830539581181</v>
+        <v>6.942117778423674</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.894565448977231</v>
+        <v>6.894716358658487</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.857880555303108</v>
+        <v>6.858035859802597</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.844368598218135</v>
+        <v>6.844482948576934</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.82706066554935</v>
+        <v>6.826915385760351</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.846586471792289</v>
+        <v>6.846404910694909</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.864829237302983</v>
+        <v>6.864487072204463</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.891852787524804</v>
+        <v>6.891688356852252</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.892833981624644</v>
+        <v>6.892736448583902</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.882111431197228</v>
+        <v>6.8819401419681</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.869011649674838</v>
+        <v>6.869140498110981</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.844400474493209</v>
+        <v>6.844468567020074</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.839239767391252</v>
+        <v>6.839355331873722</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.811430790507313</v>
+        <v>6.811276324522327</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823518084499719</v>
+        <v>6.823544946813218</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.826705756188283</v>
+        <v>6.820888880119935</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.825335695088658</v>
+        <v>6.818818538834787</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.822651836739901</v>
+        <v>6.815977739790305</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.820694904139916</v>
+        <v>6.81350611126631</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.819844670387181</v>
+        <v>6.811897403356218</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.797674832711242</v>
+        <v>6.790791705746227</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.804596236059741</v>
+        <v>6.795106689735646</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.792255898465629</v>
+        <v>6.782223589370636</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.784588115740426</v>
+        <v>6.773443542232773</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.778477529446984</v>
+        <v>6.76490083295398</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.765789844563111</v>
+        <v>6.751195982380798</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.750491992992793</v>
+        <v>6.734904376279776</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.719239304410019</v>
+        <v>6.705938122814445</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,15 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.695842089873302</v>
+        <v>6.675099954616016</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B102">
+        <v>6.646216369895317</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.818818538834787</v>
+        <v>6.818805531233505</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.815977739790305</v>
+        <v>6.815961987577811</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.81350611126631</v>
+        <v>6.813503212170078</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.811897403356218</v>
+        <v>6.811915981361772</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.790791705746227</v>
+        <v>6.790831619929387</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.795106689735646</v>
+        <v>6.79515767999466</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.782223589370636</v>
+        <v>6.782311109804966</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.773443542232773</v>
+        <v>6.773473748122569</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.76490083295398</v>
+        <v>6.764685311842353</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.751195982380798</v>
+        <v>6.7511532252798</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.734904376279776</v>
+        <v>6.734880111486362</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.705938122814445</v>
+        <v>6.705722596394744</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.675099954616016</v>
+        <v>6.674982910149951</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.646216369895317</v>
+        <v>6.645589281206227</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B102"/>
+  <dimension ref="A1:B103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.674982910149951</v>
+        <v>6.674727480875426</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,15 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.645589281206227</v>
+        <v>6.644406471166661</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B103">
+        <v>6.636209471790232</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141895157631538</v>
+        <v>7.141876154414325</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.152313297447041</v>
+        <v>7.152281783094544</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.15580855436618</v>
+        <v>7.155778077188875</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.169250123368686</v>
+        <v>7.169216045580714</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.184174383478681</v>
+        <v>7.184142025859077</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.196075861999596</v>
+        <v>7.196045690698647</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.19829743704271</v>
+        <v>7.198270145056449</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192769932542856</v>
+        <v>7.192745796478377</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175148241377338</v>
+        <v>7.175164558660251</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179552106074199</v>
+        <v>7.179587608793959</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.183638989517728</v>
+        <v>7.183672229270624</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.188748427408472</v>
+        <v>7.188781216852734</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.181951351956213</v>
+        <v>7.182010426485192</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.180905152058571</v>
+        <v>7.180973344608075</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182228637493563</v>
+        <v>7.182285704336788</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.167661019361782</v>
+        <v>7.1677124127569</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.153730041706551</v>
+        <v>7.15380544063975</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.146312487414873</v>
+        <v>7.146398284027932</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.14169401542798</v>
+        <v>7.141799334178115</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.122153276502977</v>
+        <v>7.122241568980458</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.10891419539634</v>
+        <v>7.109029712556012</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.100023620294582</v>
+        <v>7.100151643630287</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.071986710762535</v>
+        <v>7.072125914957707</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.047308327484066</v>
+        <v>7.047450788210432</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.045437437582136</v>
+        <v>7.045590561616369</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.043058117311547</v>
+        <v>7.043253100529344</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.048955214947258</v>
+        <v>7.04919749929819</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.052376670963014</v>
+        <v>7.052714869641339</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.008427760351516</v>
+        <v>7.008743512421423</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.962330742644747</v>
+        <v>6.962578314798307</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.963152247139778</v>
+        <v>6.963386745425847</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.942117778423674</v>
+        <v>6.942392942039922</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.894716358658487</v>
+        <v>6.894861231363457</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.858035859802597</v>
+        <v>6.858185094211581</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.844482948576934</v>
+        <v>6.844593642660436</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.826915385760351</v>
+        <v>6.826777649833133</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.846404910694909</v>
+        <v>6.846232508075765</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.864487072204463</v>
+        <v>6.864160523671412</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.891688356852252</v>
+        <v>6.89153137353618</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.892736448583902</v>
+        <v>6.892642685767031</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.8819401419681</v>
+        <v>6.881775680422622</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.869140498110981</v>
+        <v>6.869263447347576</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.844468567020074</v>
+        <v>6.844533828155119</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.839355331873722</v>
+        <v>6.839465999309152</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.811276324522327</v>
+        <v>6.811127735007961</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823544946813218</v>
+        <v>6.823569902601689</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.820888880119935</v>
+        <v>6.815903888121124</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.818805531233505</v>
+        <v>6.813241742826623</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.815961987577811</v>
+        <v>6.810322083235294</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.813503212170078</v>
+        <v>6.807445913816824</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.811915981361772</v>
+        <v>6.805046053801831</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.790831619929387</v>
+        <v>6.784463060982057</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.79515767999466</v>
+        <v>6.785915631782107</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.782311109804966</v>
+        <v>6.771760493289561</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.773473748122569</v>
+        <v>6.760909420591251</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.764685311842353</v>
+        <v>6.747816842723531</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.7511532252798</v>
+        <v>6.73176805244076</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.734880111486362</v>
+        <v>6.712787013554246</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.705722596394744</v>
+        <v>6.682023200512902</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.674727480875426</v>
+        <v>6.640584512602149</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.644406471166661</v>
+        <v>6.600298643538919</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,15 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.636209471790232</v>
+        <v>6.5880998902004</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B104">
+        <v>6.539912390200401</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141876154414325</v>
+        <v>7.141858055586605</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.152281783094544</v>
+        <v>7.152251758363501</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155778077188875</v>
+        <v>7.155749018539943</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.169216045580714</v>
+        <v>7.169183549856039</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.184142025859077</v>
+        <v>7.184111172867998</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.196045690698647</v>
+        <v>7.196016924632336</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198270145056449</v>
+        <v>7.198244124707794</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192745796478377</v>
+        <v>7.192722784450056</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175164558660251</v>
+        <v>7.175180016829039</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179587608793959</v>
+        <v>7.17962140159243</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.183672229270624</v>
+        <v>7.183703870998984</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.188781216852734</v>
+        <v>7.188812432038207</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182010426485192</v>
+        <v>7.182066671358506</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.180973344608075</v>
+        <v>7.181038302815079</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182285704336788</v>
+        <v>7.182340060584325</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.1677124127569</v>
+        <v>7.167761300102557</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.15380544063975</v>
+        <v>7.15387720284934</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.146398284027932</v>
+        <v>7.14647996058285</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.141799334178115</v>
+        <v>7.141899654230787</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.122241568980458</v>
+        <v>7.122325588813323</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.109029712556012</v>
+        <v>7.109139813891248</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.100151643630287</v>
+        <v>7.100273787339205</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.072125914957707</v>
+        <v>7.072258897060689</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.047450788210432</v>
+        <v>7.047586896533071</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.045590561616369</v>
+        <v>7.04573676892703</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.043253100529344</v>
+        <v>7.043439052946161</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.04919749929819</v>
+        <v>7.049428461672004</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.052714869641339</v>
+        <v>7.053037168063965</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.008743512421423</v>
+        <v>7.009044131162264</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.962578314798307</v>
+        <v>6.962814473088192</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.963386745425847</v>
+        <v>6.963610757822801</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.942392942039922</v>
+        <v>6.94265675725701</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.894861231363457</v>
+        <v>6.895000407194058</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.858185094211581</v>
+        <v>6.858328589547927</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.844593642660436</v>
+        <v>6.844700812222408</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.826777649833133</v>
+        <v>6.826646894261433</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.846232508075765</v>
+        <v>6.846068597778387</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.864160523671412</v>
+        <v>6.863848556862575</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.89153137353618</v>
+        <v>6.891381348705363</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.892642685767031</v>
+        <v>6.892552494689484</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.881775680422622</v>
+        <v>6.881617664208429</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.869263447347576</v>
+        <v>6.869380892794038</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.844533828155119</v>
+        <v>6.844596429093452</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.839465999309152</v>
+        <v>6.839572073566652</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.811127735007961</v>
+        <v>6.810984715057488</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823569902601689</v>
+        <v>6.823593124907145</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.815903888121124</v>
+        <v>6.816038847104799</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813241742826623</v>
+        <v>6.81029950198014</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.810322083235294</v>
+        <v>6.807568098646299</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.807445913816824</v>
+        <v>6.804949124474156</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.805046053801831</v>
+        <v>6.80288340353508</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.784463060982057</v>
+        <v>6.784317590012608</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.785915631782107</v>
+        <v>6.785649689730447</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.771760493289561</v>
+        <v>6.773145620916996</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.760909420591251</v>
+        <v>6.763264796384098</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.747816842723531</v>
+        <v>6.751823986057111</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.73176805244076</v>
+        <v>6.7379842436223</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.712787013554246</v>
+        <v>6.722019504532497</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.682023200512902</v>
+        <v>6.696390104339538</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.640584512602149</v>
+        <v>6.67067797853877</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.600298643538919</v>
+        <v>6.65173347543256</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.5880998902004</v>
+        <v>6.642917148613241</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.539912390200401</v>
+        <v>6.637882792567378</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141858055586605</v>
+        <v>7.141840798098615</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.152251758363501</v>
+        <v>7.152223120117316</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155749018539943</v>
+        <v>7.155721281737083</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.169183549856039</v>
+        <v>7.169152528652099</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.184111172867998</v>
+        <v>7.184081722055103</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.196016924632336</v>
+        <v>7.195989467956969</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198244124707794</v>
+        <v>7.198219289224452</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192722784450056</v>
+        <v>7.192700819788802</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175180016829039</v>
+        <v>7.175194681320007</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.17962140159243</v>
+        <v>7.179653604994614</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.183703870998984</v>
+        <v>7.183734027147282</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.188812432038207</v>
+        <v>7.188842183595244</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182066671358506</v>
+        <v>7.182120284868638</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181038302815079</v>
+        <v>7.18110025100779</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182340060584325</v>
+        <v>7.182391894659874</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.167761300102557</v>
+        <v>7.167807859892469</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.15387720284934</v>
+        <v>7.153945584491097</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.14647996058285</v>
+        <v>7.146557805715938</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.141899654230787</v>
+        <v>7.141995322291182</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.122325588813323</v>
+        <v>7.122405637851601</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.109139813891248</v>
+        <v>7.109244869751229</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.100273787339205</v>
+        <v>7.100390444789671</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.072258897060689</v>
+        <v>7.072386062305291</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.047586896533071</v>
+        <v>7.047717064954126</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.04573676892703</v>
+        <v>7.045876514959122</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.043439052946161</v>
+        <v>7.043616584703592</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.049428461672004</v>
+        <v>7.049648872832657</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.053037168063965</v>
+        <v>7.053344653320639</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.009044131162264</v>
+        <v>7.009330671960712</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.962814473088192</v>
+        <v>6.96303997841939</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.963610757822801</v>
+        <v>6.96382495985695</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.94265675725701</v>
+        <v>6.942909895544681</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.895000407194058</v>
+        <v>6.895134202694167</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.858328589547927</v>
+        <v>6.858466655032437</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.844700812222408</v>
+        <v>6.84480458796913</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.826646894261433</v>
+        <v>6.826522609563711</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.846068597778387</v>
+        <v>6.845912575919971</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.863848556862575</v>
+        <v>6.863550225456461</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.891381348705363</v>
+        <v>6.891237834817151</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.892552494689484</v>
+        <v>6.892465688793682</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.881617664208429</v>
+        <v>6.881465737144054</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.869380892794038</v>
+        <v>6.869493195336122</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.844596429093452</v>
+        <v>6.844656527630978</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.839572073566652</v>
+        <v>6.839673833914847</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.810984715057488</v>
+        <v>6.810846976435963</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823593124907145</v>
+        <v>6.823614767770385</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.816038847104799</v>
+        <v>6.816167287667716</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.81029950198014</v>
+        <v>6.810445072029998</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807568098646299</v>
+        <v>6.804020830082042</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.804949124474156</v>
+        <v>6.800909163282314</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.80288340353508</v>
+        <v>6.798331099556668</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.784317590012608</v>
+        <v>6.779263174290643</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.785649689730447</v>
+        <v>6.778443490906167</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.773145620916996</v>
+        <v>6.764956214911081</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.763264796384098</v>
+        <v>6.753610681747126</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.751823986057111</v>
+        <v>6.740375034500209</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.7379842436223</v>
+        <v>6.723723206401717</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.722019504532497</v>
+        <v>6.701917694868301</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.696390104339538</v>
+        <v>6.673273863544271</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.67067797853877</v>
+        <v>6.638615101769279</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.65173347543256</v>
+        <v>6.610122643875101</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.642917148613241</v>
+        <v>6.593613877796619</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.637882792567378</v>
+        <v>6.574725182738474</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -30,8 +30,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -47,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,13 +63,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -357,22 +383,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>44743</v>
       </c>
       <c r="B2">
@@ -380,7 +406,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>44778</v>
       </c>
       <c r="B3">
@@ -388,7 +414,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>44806</v>
       </c>
       <c r="B4">
@@ -396,7 +422,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>44834</v>
       </c>
       <c r="B5">
@@ -404,7 +430,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>44869</v>
       </c>
       <c r="B6">
@@ -412,7 +438,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>44897</v>
       </c>
       <c r="B7">
@@ -420,7 +446,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>44932</v>
       </c>
       <c r="B8">
@@ -428,7 +454,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>44960</v>
       </c>
       <c r="B9">
@@ -436,7 +462,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>44988</v>
       </c>
       <c r="B10">
@@ -444,7 +470,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>45016</v>
       </c>
       <c r="B11">
@@ -452,7 +478,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>45051</v>
       </c>
       <c r="B12">
@@ -460,7 +486,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>45079</v>
       </c>
       <c r="B13">
@@ -468,7 +494,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>45107</v>
       </c>
       <c r="B14">
@@ -476,7 +502,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>45142</v>
       </c>
       <c r="B15">
@@ -484,7 +510,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>45170</v>
       </c>
       <c r="B16">
@@ -492,7 +518,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>45205</v>
       </c>
       <c r="B17">
@@ -500,7 +526,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <v>45233</v>
       </c>
       <c r="B18">
@@ -508,7 +534,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>45261</v>
       </c>
       <c r="B19">
@@ -516,7 +542,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>45296</v>
       </c>
       <c r="B20">
@@ -524,7 +550,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>45324</v>
       </c>
       <c r="B21">
@@ -532,7 +558,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>45352</v>
       </c>
       <c r="B22">
@@ -540,7 +566,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>45387</v>
       </c>
       <c r="B23">
@@ -548,7 +574,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <v>45415</v>
       </c>
       <c r="B24">
@@ -556,7 +582,7 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <v>45443</v>
       </c>
       <c r="B25">
@@ -564,7 +590,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>45478</v>
       </c>
       <c r="B26">
@@ -572,7 +598,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>45506</v>
       </c>
       <c r="B27">
@@ -580,7 +606,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>45541</v>
       </c>
       <c r="B28">
@@ -588,7 +614,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <v>45569</v>
       </c>
       <c r="B29">
@@ -596,7 +622,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>45597</v>
       </c>
       <c r="B30">
@@ -604,7 +630,7 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <v>45632</v>
       </c>
       <c r="B31">
@@ -612,7 +638,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>45660</v>
       </c>
       <c r="B32">
@@ -620,7 +646,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>45688</v>
       </c>
       <c r="B33">
@@ -628,7 +654,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>45716</v>
       </c>
       <c r="B34">
@@ -636,7 +662,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>45751</v>
       </c>
       <c r="B35">
@@ -644,7 +670,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>45779</v>
       </c>
       <c r="B36">
@@ -652,7 +678,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>45814</v>
       </c>
       <c r="B37">
@@ -660,7 +686,7 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>45821</v>
       </c>
       <c r="B38">
@@ -668,7 +694,7 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>45828</v>
       </c>
       <c r="B39">
@@ -676,7 +702,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>45835</v>
       </c>
       <c r="B40">
@@ -684,7 +710,7 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <v>45842</v>
       </c>
       <c r="B41">
@@ -692,507 +718,515 @@
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141840798098615</v>
+        <v>7.141824324627212</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="2">
+      <c r="A43" s="3">
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.152223120117316</v>
+        <v>7.152195774522081</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155721281737083</v>
+        <v>7.155694778679965</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="2">
+      <c r="A45" s="3">
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.169152528652099</v>
+        <v>7.169122883946162</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.184081722055103</v>
+        <v>7.184053580054933</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195989467956969</v>
+        <v>7.195963233342761</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="2">
+      <c r="A48" s="3">
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198219289224452</v>
+        <v>7.198195559546345</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192700819788802</v>
+        <v>7.192679832637575</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175194681320007</v>
+        <v>7.175208611141434</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="2">
+      <c r="A51" s="3">
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179653604994614</v>
+        <v>7.179684328467336</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="2">
+      <c r="A52" s="3">
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.183734027147282</v>
+        <v>7.183762799859997</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="2">
+      <c r="A53" s="3">
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.188842183595244</v>
+        <v>7.188870572032776</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182120284868638</v>
+        <v>7.182171447226081</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="2">
+      <c r="A55" s="3">
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.18110025100779</v>
+        <v>7.181159393276663</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182391894659874</v>
+        <v>7.182441377937599</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.167807859892469</v>
+        <v>7.1678522541002</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="2">
+      <c r="A58" s="3">
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.153945584491097</v>
+        <v>7.154010818281402</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="2">
+      <c r="A59" s="3">
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.146557805715938</v>
+        <v>7.146632081819329</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="2">
+      <c r="A60" s="3">
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.141995322291182</v>
+        <v>7.142086653806923</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="2">
+      <c r="A61" s="3">
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.122405637851601</v>
+        <v>7.12248199024879</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="2">
+      <c r="A62" s="3">
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.109244869751229</v>
+        <v>7.109345217626946</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="2">
+      <c r="A63" s="3">
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.100390444789671</v>
+        <v>7.100501975253842</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="2">
+      <c r="A64" s="3">
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.072386062305291</v>
+        <v>7.07250778173527</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="2">
+      <c r="A65" s="3">
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.047717064954126</v>
+        <v>7.047841671295908</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="2">
+      <c r="A66" s="3">
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.045876514959122</v>
+        <v>7.046010216280724</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="2">
+      <c r="A67" s="3">
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.043616584703592</v>
+        <v>7.043786252454709</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="2">
+      <c r="A68" s="3">
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.049648872832657</v>
+        <v>7.049859435546016</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.053344653320639</v>
+        <v>7.053638316346966</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="2">
+      <c r="A70" s="3">
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.009330671960712</v>
+        <v>7.009604094911397</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="2">
+      <c r="A71" s="3">
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.96303997841939</v>
+        <v>6.963255526477774</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="2">
+      <c r="A72" s="3">
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.96382495985695</v>
+        <v>6.964029971398116</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="2">
+      <c r="A73" s="3">
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.942909895544681</v>
+        <v>6.943152977966847</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="2">
+      <c r="A74" s="3">
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.895134202694167</v>
+        <v>6.895262912660021</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="2">
+      <c r="A75" s="3">
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.858466655032437</v>
+        <v>6.858599579612648</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="2">
+      <c r="A76" s="3">
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.84480458796913</v>
+        <v>6.844905098507171</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="2">
+      <c r="A77" s="3">
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.826522609563711</v>
+        <v>6.826404334033413</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="2">
+      <c r="A78" s="3">
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.845912575919971</v>
+        <v>6.845763893862657</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="2">
+      <c r="A79" s="3">
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.863550225456461</v>
+        <v>6.863264662488145</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="2">
+      <c r="A80" s="3">
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.891237834817151</v>
+        <v>6.891100421442589</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="2">
+      <c r="A81" s="3">
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.892465688793682</v>
+        <v>6.89238209282311</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="2">
+      <c r="A82" s="3">
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.881465737144054</v>
+        <v>6.881319567262622</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="2">
+      <c r="A83" s="3">
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.869493195336122</v>
+        <v>6.869600685020501</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="2">
+      <c r="A84" s="3">
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.844656527630978</v>
+        <v>6.844714269439836</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="2">
+      <c r="A85" s="3">
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.839673833914847</v>
+        <v>6.839771537464551</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="2">
+      <c r="A86" s="3">
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.810846976435963</v>
+        <v>6.810714248502063</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="2">
+      <c r="A87" s="3">
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823614767770385</v>
+        <v>6.823634968662203</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="2">
+      <c r="A88" s="3">
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.816167287667716</v>
+        <v>6.816289664668476</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="2">
+      <c r="A89" s="3">
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.810445072029998</v>
+        <v>6.81058383720646</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="2">
+      <c r="A90" s="3">
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.804020830082042</v>
+        <v>6.804175850676231</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="2">
+      <c r="A91" s="3">
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.800909163282314</v>
+        <v>6.799557029438347</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="2">
+      <c r="A92" s="3">
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.798331099556668</v>
+        <v>6.797053605028847</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="2">
+      <c r="A93" s="3">
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.779263174290643</v>
+        <v>6.779521776520699</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="2">
+      <c r="A94" s="3">
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.778443490906167</v>
+        <v>6.778958631146105</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="2">
+      <c r="A95" s="3">
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.764956214911081</v>
+        <v>6.767433360423687</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="2">
+      <c r="A96" s="3">
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.753610681747126</v>
+        <v>6.7581718474663</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="2">
+      <c r="A97" s="3">
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.740375034500209</v>
+        <v>6.747938067995594</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="2">
+      <c r="A98" s="3">
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.723723206401717</v>
+        <v>6.734809647702434</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="2">
+      <c r="A99" s="3">
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.701917694868301</v>
+        <v>6.717639964871759</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="2">
+      <c r="A100" s="3">
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.673273863544271</v>
+        <v>6.695479248107272</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="2">
+      <c r="A101" s="3">
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.638615101769279</v>
+        <v>6.671594926770631</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="2">
+      <c r="A102" s="3">
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.610122643875101</v>
+        <v>6.653739931686742</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="2">
+      <c r="A103" s="3">
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.593613877796619</v>
+        <v>6.640679947652846</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="2">
+      <c r="A104" s="3">
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.574725182738474</v>
+        <v>6.639083002269436</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B105">
+        <v>6.687270502269435</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141824324627212</v>
+        <v>7.14180858294025</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.152195774522081</v>
+        <v>7.152169636021226</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155694778679965</v>
+        <v>7.15566942891965</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.169122883946162</v>
+        <v>7.169094526205975</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.184053580054933</v>
+        <v>7.184026661602775</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195963233342761</v>
+        <v>7.195938141049892</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198195559546345</v>
+        <v>7.198172863488166</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192679832637575</v>
+        <v>7.192659759211849</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175208611141434</v>
+        <v>7.1752218596388</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179684328467336</v>
+        <v>7.179713671658104</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.183762799859997</v>
+        <v>7.183790282133746</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.188870572032776</v>
+        <v>7.188897688869136</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182171447226081</v>
+        <v>7.182220322572082</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181159393276663</v>
+        <v>7.18121591570212</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182441377937599</v>
+        <v>7.182488666625885</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.1678522541002</v>
+        <v>7.167894630043236</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154010818281402</v>
+        <v>7.154073116111416</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.146632081819329</v>
+        <v>7.146703027946715</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.142086653806923</v>
+        <v>7.142173936404323</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.12248199024879</v>
+        <v>7.122554895558636</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.109345217626946</v>
+        <v>7.109441165699394</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.100501975253842</v>
+        <v>7.100608707498639</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.07250778173527</v>
+        <v>7.072624395707959</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.047841671295908</v>
+        <v>7.047961062239731</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.046010216280724</v>
+        <v>7.046138254617503</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.043786252454709</v>
+        <v>7.043948565071767</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.049859435546016</v>
+        <v>7.050060791872852</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.053638316346966</v>
+        <v>7.053919062246985</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.009604094911397</v>
+        <v>7.009865275269328</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.963255526477774</v>
+        <v>6.963461754466827</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.964029971398116</v>
+        <v>6.964226362143375</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.943152977966847</v>
+        <v>6.943386579643049</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.895262912660021</v>
+        <v>6.895386811817285</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.858599579612648</v>
+        <v>6.858727633400624</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.844905098507171</v>
+        <v>6.845002469573192</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.826404334033413</v>
+        <v>6.826291648328533</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.845763893862657</v>
+        <v>6.845622052105791</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.863264662488145</v>
+        <v>6.862991072287683</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.891100421442589</v>
+        <v>6.890968731548638</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.89238209282311</v>
+        <v>6.892301542185249</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.881319567262622</v>
+        <v>6.881178844987849</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.869600685020501</v>
+        <v>6.869703664277466</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.844714269439836</v>
+        <v>6.84476978920167</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.839771537464551</v>
+        <v>6.839865421324961</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.810714248502063</v>
+        <v>6.810586277145898</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823634968662203</v>
+        <v>6.823653850561624</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.816289664668476</v>
+        <v>6.816406392106996</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.81058383720646</v>
+        <v>6.810716256994794</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.804175850676231</v>
+        <v>6.804323985425716</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.799557029438347</v>
+        <v>6.799712312329083</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.797053605028847</v>
+        <v>6.797850713821386</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.779521776520699</v>
+        <v>6.78221895656158</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.778958631146105</v>
+        <v>6.781971335627526</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.767433360423687</v>
+        <v>6.772245047009195</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.7581718474663</v>
+        <v>6.764978711615342</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.747938067995594</v>
+        <v>6.757162412287087</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.734809647702434</v>
+        <v>6.747171085688848</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.717639964871759</v>
+        <v>6.733940886979809</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.695479248107272</v>
+        <v>6.716384075280172</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.671594926770631</v>
+        <v>6.701762414902145</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.653739931686742</v>
+        <v>6.689119628408656</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.640679947652846</v>
+        <v>6.676910144150282</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.639083002269436</v>
+        <v>6.679949516175432</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,15 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.687270502269435</v>
+        <v>6.727912016175432</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B106">
+        <v>6.775874516175431</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.14180858294025</v>
+        <v>7.141793525343767</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.152169636021226</v>
+        <v>7.152144626442849</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.15566942891965</v>
+        <v>7.155645158846404</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.169094526205975</v>
+        <v>7.169067373490945</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.184026661602775</v>
+        <v>7.184000888675621</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195938141049892</v>
+        <v>7.19591411812219</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198172863488166</v>
+        <v>7.198151135008615</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192659759211849</v>
+        <v>7.192640541154292</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.1752218596388</v>
+        <v>7.175234475153849</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179713671658104</v>
+        <v>7.179741725471198</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.183790282133746</v>
+        <v>7.183816558818269</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.188897688869136</v>
+        <v>7.188923617614719</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182220322572082</v>
+        <v>7.182267060728698</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.18121591570212</v>
+        <v>7.181269988294854</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182488666625885</v>
+        <v>7.182533903406969</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.167894630043236</v>
+        <v>7.167935122000717</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154073116111416</v>
+        <v>7.154132671319853</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.146703027946715</v>
+        <v>7.146770862342748</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.142173936404323</v>
+        <v>7.142257432882167</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.122554895558636</v>
+        <v>7.122624581426555</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.109441165699394</v>
+        <v>7.109532995939826</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.100608707498639</v>
+        <v>7.100710942935436</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.072624395707959</v>
+        <v>7.072736216979349</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.047961062239731</v>
+        <v>7.048075556444048</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.046138254617503</v>
+        <v>7.046260980398456</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.043948565071767</v>
+        <v>7.04410398864177</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.050060791872852</v>
+        <v>7.05025352954841</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.053919062246985</v>
+        <v>7.054187719323784</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.009865275269328</v>
+        <v>7.010115012564194</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.963461754466827</v>
+        <v>6.963659247039987</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.964226362143375</v>
+        <v>6.964414656483307</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.943386579643049</v>
+        <v>6.943611233769965</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.895386811817285</v>
+        <v>6.895506156369788</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.858727633400624</v>
+        <v>6.858851069021595</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.845002469573192</v>
+        <v>6.845096823483609</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.826291648328533</v>
+        <v>6.82618417077307</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.845622052105791</v>
+        <v>6.845486594962841</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.862991072287683</v>
+        <v>6.862728723370729</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.890968731548638</v>
+        <v>6.890842418211726</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.892301542185249</v>
+        <v>6.892223882318959</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.881178844987849</v>
+        <v>6.88104328144061</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.869703664277466</v>
+        <v>6.869802410747903</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.84476978920167</v>
+        <v>6.844823211616823</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.839865421324961</v>
+        <v>6.8399557045121</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.810586277145898</v>
+        <v>6.810462823757932</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823653850561624</v>
+        <v>6.823671523738201</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.816406392106996</v>
+        <v>6.816517847561978</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.810716256994794</v>
+        <v>6.810842750958357</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.804323985425716</v>
+        <v>6.804465677597342</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.799712312329083</v>
+        <v>6.799861101333462</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.797850713821386</v>
+        <v>6.798002105474979</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.78221895656158</v>
+        <v>6.78227815082762</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.781971335627526</v>
+        <v>6.78201633515361</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.772245047009195</v>
+        <v>6.773529666268829</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.764978711615342</v>
+        <v>6.767429981451018</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.757162412287087</v>
+        <v>6.761994307841689</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.747171085688848</v>
+        <v>6.754794233119762</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.733940886979809</v>
+        <v>6.744996437407785</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.716384075280172</v>
+        <v>6.731710792509631</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.701762414902145</v>
+        <v>6.723250742803982</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.689119628408656</v>
+        <v>6.716042654298721</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.676910144150282</v>
+        <v>6.709161122690994</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.679949516175432</v>
+        <v>6.717515074315503</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.727912016175432</v>
+        <v>6.840075627804006</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,15 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.775874516175431</v>
+        <v>6.840224282868691</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B107">
+        <v>6.862382443307848</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.773529666268829</v>
+        <v>6.773672855495386</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.767429981451018</v>
+        <v>6.767848757741247</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.761994307841689</v>
+        <v>6.76304784851036</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.754794233119762</v>
+        <v>6.756275917585981</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.744996437407785</v>
+        <v>6.746963910491811</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.731710792509631</v>
+        <v>6.734254237915451</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.723250742803982</v>
+        <v>6.726948409728763</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.716042654298721</v>
+        <v>6.720933300707783</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.709161122690994</v>
+        <v>6.716153826620036</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.717515074315503</v>
+        <v>6.726651360627614</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.840075627804006</v>
+        <v>6.859306523797436</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.840224282868691</v>
+        <v>6.874235045839866</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.862382443307848</v>
+        <v>6.918935045839866</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141793525343767</v>
+        <v>7.141779108199649</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.152144626442849</v>
+        <v>7.152120674220059</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155645158846404</v>
+        <v>7.155621900978703</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.169067373490945</v>
+        <v>7.169041350665075</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.184000888675621</v>
+        <v>7.183976189740084</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19591411812219</v>
+        <v>7.195891097681428</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198151135008615</v>
+        <v>7.198130313570882</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192640541154292</v>
+        <v>7.192622124970001</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175234475153849</v>
+        <v>7.175246501594184</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179741725471198</v>
+        <v>7.179768573005354</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.183816558818269</v>
+        <v>7.18384170748886</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.188923617614719</v>
+        <v>7.188948434628557</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182267060728698</v>
+        <v>7.182311798725256</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181269988294854</v>
+        <v>7.181321766690999</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182533903406969</v>
+        <v>7.182577218868553</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.167935122000717</v>
+        <v>7.167973852621935</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154132671319853</v>
+        <v>7.154189660675167</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.146770862342748</v>
+        <v>7.146835784651537</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.142257432882167</v>
+        <v>7.142337383827947</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.122624581426555</v>
+        <v>7.122691255936142</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.109532995939826</v>
+        <v>7.109620966826375</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.100710942935436</v>
+        <v>7.10080895838999</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.072736216979349</v>
+        <v>7.072843533427192</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.048075556444048</v>
+        <v>7.048185447298533</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.046260980398456</v>
+        <v>7.046378715880085</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.04410398864177</v>
+        <v>7.044252950850993</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.05025352954841</v>
+        <v>7.050438187578517</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.054187719323784</v>
+        <v>7.054445047001543</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.010115012564194</v>
+        <v>7.010354038571083</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.963659247039987</v>
+        <v>6.963848541536347</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.964414656483307</v>
+        <v>6.964595337827379</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.943611233769965</v>
+        <v>6.943827435248481</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.895506156369788</v>
+        <v>6.895621185426588</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.858851069021595</v>
+        <v>6.858970122873313</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.845096823483609</v>
+        <v>6.845188278755318</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.82618417077307</v>
+        <v>6.826081553264336</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.845486594962841</v>
+        <v>6.845357105908885</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.862728723370729</v>
+        <v>6.86247694215426</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.890842418211726</v>
+        <v>6.890721161706409</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.892223882318959</v>
+        <v>6.892148968076917</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.88104328144061</v>
+        <v>6.880912606871751</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.869802410747903</v>
+        <v>6.869897179770144</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.844823211616823</v>
+        <v>6.844874652305016</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.8399557045121</v>
+        <v>6.840042589642283</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.810462823757932</v>
+        <v>6.810343664239033</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823671523738201</v>
+        <v>6.823688087285257</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.816517847561978</v>
+        <v>6.816624376068214</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.810842750958357</v>
+        <v>6.810963702929525</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.804465677597342</v>
+        <v>6.804601333653789</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.799861101333462</v>
+        <v>6.800003790646409</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.798002105474979</v>
+        <v>6.798147661755525</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.78227815082762</v>
+        <v>6.782334947009497</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.78201633515361</v>
+        <v>6.782048946287889</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.773672855495386</v>
+        <v>6.774897009476232</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.767848757741247</v>
+        <v>6.770293900618469</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.76304784851036</v>
+        <v>6.768016523019579</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.756275917585981</v>
+        <v>6.76387498597451</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.746963910491811</v>
+        <v>6.757681871321598</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.734254237915451</v>
+        <v>6.748711576114255</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.726948409728763</v>
+        <v>6.746361783791084</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.720933300707783</v>
+        <v>6.744605191234996</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.716153826620036</v>
+        <v>6.745352613702671</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.726651360627614</v>
+        <v>6.759781247028686</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.859306523797436</v>
+        <v>6.881156114384726</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.874235045839866</v>
+        <v>6.897994757073985</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.918935045839866</v>
+        <v>6.934267989233711</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141779108199649</v>
+        <v>7.141765291503553</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.152120674220059</v>
+        <v>7.152097713708049</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155621900978703</v>
+        <v>7.155599593339073</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.169041350665075</v>
+        <v>7.169016388705671</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183976189740084</v>
+        <v>7.183952499092026</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195891097681428</v>
+        <v>7.195869018307793</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198130313570882</v>
+        <v>7.198110343581267</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192622124970001</v>
+        <v>7.192604461530736</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175246501594184</v>
+        <v>7.175257978927192</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179768573005354</v>
+        <v>7.179794290373414</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.18384170748886</v>
+        <v>7.183865799209112</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.188948434628557</v>
+        <v>7.188972209867335</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182311798725256</v>
+        <v>7.182354662133812</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181321766690999</v>
+        <v>7.181371393637505</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182577218868553</v>
+        <v>7.182618732757549</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.167973852621935</v>
+        <v>7.168010934156398</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154189660675167</v>
+        <v>7.154244246109501</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.146835784651537</v>
+        <v>7.146897977850649</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.142337383827947</v>
+        <v>7.142414009910851</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.122691255936142</v>
+        <v>7.122755109661144</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.109620966826375</v>
+        <v>7.109705315731076</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.10080895838999</v>
+        <v>7.100903008544626</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.072843533427192</v>
+        <v>7.072946610460369</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.048185447298533</v>
+        <v>7.048291005362257</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.046378715880085</v>
+        <v>7.046491757905947</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.044252950850993</v>
+        <v>7.044395844843491</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.050438187578517</v>
+        <v>7.050615261161581</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.054445047001543</v>
+        <v>7.054691742793414</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.010354038571083</v>
+        <v>7.010583024300617</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.963848541536347</v>
+        <v>6.964030132611666</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.964595337827379</v>
+        <v>6.964768852455</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.943827435248481</v>
+        <v>6.944035643957335</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.895621185426588</v>
+        <v>6.895732122314731</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.858970122873313</v>
+        <v>6.85908501629801</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.845188278755318</v>
+        <v>6.845276949859251</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.826081553264336</v>
+        <v>6.825983477697745</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.845357105908885</v>
+        <v>6.84523320350311</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.86247694215426</v>
+        <v>6.86223510738911</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.890721161706409</v>
+        <v>6.89060466692094</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.892148968076917</v>
+        <v>6.892076663130267</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.880912606871751</v>
+        <v>6.88078656921515</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.869897179770144</v>
+        <v>6.869988206573439</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.844874652305016</v>
+        <v>6.844924218610819</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.840042589642283</v>
+        <v>6.840126264438488</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.810343664239033</v>
+        <v>6.810228588057682</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823688087285257</v>
+        <v>6.823703630442859</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.816624376068214</v>
+        <v>6.816726293513713</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.810963702929525</v>
+        <v>6.811079464689678</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.804601333653789</v>
+        <v>6.804731326951903</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.800003790646409</v>
+        <v>6.800140743582515</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.798147661755525</v>
+        <v>6.79828770794995</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782334947009497</v>
+        <v>6.782389484843835</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.782048946287889</v>
+        <v>6.782136661242776</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.774897009476232</v>
+        <v>6.775727747784215</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.770293900618469</v>
+        <v>6.771835460637924</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768016523019579</v>
+        <v>6.770473980184267</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.76387498597451</v>
+        <v>6.768510372165584</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.757681871321598</v>
+        <v>6.76458756899306</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.748711576114255</v>
+        <v>6.758503826925985</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.746361783791084</v>
+        <v>6.759743580678336</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.744605191234996</v>
+        <v>6.760852567609076</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.745352613702671</v>
+        <v>6.7639291148312</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.759781247028686</v>
+        <v>6.783518531400604</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.881156114384726</v>
+        <v>6.894779287869525</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.897994757073985</v>
+        <v>6.914996246129851</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,15 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.934267989233711</v>
+        <v>6.946570201237801</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B108">
+        <v>6.991270201237801</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141765291503553</v>
+        <v>7.141752038514428</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.152097713708049</v>
+        <v>7.152075684584125</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155599593339073</v>
+        <v>7.155578178904591</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.169016388705671</v>
+        <v>7.168992424094592</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183952499092026</v>
+        <v>7.183929756275148</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195869018307793</v>
+        <v>7.195847823494594</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198110343581267</v>
+        <v>7.198091173895113</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192604461530736</v>
+        <v>7.192587505638576</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175257978927192</v>
+        <v>7.175268943609721</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179794290373414</v>
+        <v>7.179818947420844</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.183865799209112</v>
+        <v>7.183888899199711</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.188972209867335</v>
+        <v>7.188995007542239</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182354662133812</v>
+        <v>7.182395766240914</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181371393637505</v>
+        <v>7.181419000297326</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182618732757549</v>
+        <v>7.182658555081145</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168010934156398</v>
+        <v>7.168046469531299</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154244246109501</v>
+        <v>7.154296576239823</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.146897977850649</v>
+        <v>7.146957609949407</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.142414009910851</v>
+        <v>7.142487513897004</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.122755109661144</v>
+        <v>7.122816317465</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.109705315731076</v>
+        <v>7.109786261022787</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.100903008544626</v>
+        <v>7.100993328096735</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.072946610460369</v>
+        <v>7.073045693155525</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.048291005362257</v>
+        <v>7.048392480527077</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.046491757905947</v>
+        <v>7.046600380349968</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.044395844843491</v>
+        <v>7.044533032625461</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.050615261161581</v>
+        <v>7.050785206028865</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.054691742793414</v>
+        <v>7.054928448445771</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.010583024300617</v>
+        <v>7.010802586145689</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.964030132611666</v>
+        <v>6.964204476343339</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.964768852455</v>
+        <v>6.964935612950057</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.944035643957335</v>
+        <v>6.944236287710212</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.895732122314731</v>
+        <v>6.895839175785477</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.85908501629801</v>
+        <v>6.859195956670229</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.845276949859251</v>
+        <v>6.845362947076712</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825983477697745</v>
+        <v>6.825889652834881</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.84523320350311</v>
+        <v>6.845114537805765</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.86223510738911</v>
+        <v>6.862002645216736</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.89060466692094</v>
+        <v>6.89049266105834</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.892076663130267</v>
+        <v>6.892006839399881</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.88078656921515</v>
+        <v>6.880664932754078</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.869988206573439</v>
+        <v>6.870075708217708</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.844924218610819</v>
+        <v>6.844972010325423</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.840126264438488</v>
+        <v>6.840206903073422</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.810228588057682</v>
+        <v>6.810117397357708</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823703630442859</v>
+        <v>6.823718233742685</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.816726293513713</v>
+        <v>6.816823889623961</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.811079464689678</v>
+        <v>6.811190359208675</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.804731326951903</v>
+        <v>6.804856001009016</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.800140743582515</v>
+        <v>6.800272295502403</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.79828770794995</v>
+        <v>6.79842254608967</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782389484843835</v>
+        <v>6.78244189367324</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.782136661242776</v>
+        <v>6.782221309490231</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775727747784215</v>
+        <v>6.775466533875788</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771835460637924</v>
+        <v>6.771825648434254</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.770473980184267</v>
+        <v>6.771002204665049</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.768510372165584</v>
+        <v>6.77017409896081</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.76458756899306</v>
+        <v>6.76764724768003</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.758503826925985</v>
+        <v>6.763366662669628</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.759743580678336</v>
+        <v>6.766329265960748</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.760852567609076</v>
+        <v>6.768841688687452</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.7639291148312</v>
+        <v>6.773477903258144</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.783518531400604</v>
+        <v>6.794956191795523</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.894779287869525</v>
+        <v>6.891391962138215</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.914996246129851</v>
+        <v>6.908086591835784</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.946570201237801</v>
+        <v>6.931826209364473</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.991270201237801</v>
+        <v>6.944331281159414</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141752038514428</v>
+        <v>7.141739315428459</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.152075684584125</v>
+        <v>7.152054531319254</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155578178904591</v>
+        <v>7.155557605121911</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168992424094592</v>
+        <v>7.168969398280747</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183929756275148</v>
+        <v>7.183907905567755</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195847823494594</v>
+        <v>7.195827461166995</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198091173895113</v>
+        <v>7.198072757380785</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192587505638576</v>
+        <v>7.192571215640847</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175268943609721</v>
+        <v>7.175279428963013</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179818947420844</v>
+        <v>7.179842608357443</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.183888899199711</v>
+        <v>7.183911067426519</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.188995007542239</v>
+        <v>7.189016886696614</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182395766240914</v>
+        <v>7.182435217078571</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181419000297326</v>
+        <v>7.181464707399402</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182658555081145</v>
+        <v>7.18269678707647</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168046469531299</v>
+        <v>7.168080553297944</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154296576239823</v>
+        <v>7.154346787706058</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.146957609949407</v>
+        <v>7.147014835484336</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.142487513897004</v>
+        <v>7.142558082425409</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.122816317465</v>
+        <v>7.122875040083436</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.109786261022787</v>
+        <v>7.109864003924585</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.100993328096735</v>
+        <v>7.101080133671043</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.073045693155525</v>
+        <v>7.073141008156048</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.048392480527077</v>
+        <v>7.048490103941376</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.046600380349968</v>
+        <v>7.046704836284728</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.044533032625461</v>
+        <v>7.044664848076352</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.050785206028865</v>
+        <v>7.050948442281263</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.054928448445771</v>
+        <v>7.055155755369483</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.010802586145689</v>
+        <v>7.011013291300572</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.964204476343339</v>
+        <v>6.964371993876643</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.964935612950057</v>
+        <v>6.965096001269039</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.944236287710212</v>
+        <v>6.944429764929363</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.895839175785477</v>
+        <v>6.895942541121794</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.859195956670229</v>
+        <v>6.859303138404597</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.845362947076712</v>
+        <v>6.845446376434772</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825889652834881</v>
+        <v>6.825799811552571</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.845114537805765</v>
+        <v>6.845000787221651</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.862002645216736</v>
+        <v>6.861779024770906</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.89049266105834</v>
+        <v>6.89038489158742</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.892006839399881</v>
+        <v>6.89193937651685</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.880664932754078</v>
+        <v>6.880547476893531</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.870075708217708</v>
+        <v>6.870159885313097</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.844972010325423</v>
+        <v>6.845018120334634</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.840206903073422</v>
+        <v>6.840284667369638</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.810117397357708</v>
+        <v>6.810009906117824</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823718233742685</v>
+        <v>6.823731970001482</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.816823889623961</v>
+        <v>6.816917430590214</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.811190359208675</v>
+        <v>6.811296683503424</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.804856001009016</v>
+        <v>6.804975672394283</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.800272295502403</v>
+        <v>6.800398756417228</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.79842254608967</v>
+        <v>6.798552456942142</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.78244189367324</v>
+        <v>6.782492293368502</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.782221309490231</v>
+        <v>6.782303043875849</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775466533875788</v>
+        <v>6.774789583113725</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771825648434254</v>
+        <v>6.771257887193721</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.771002204665049</v>
+        <v>6.770870463950795</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.77017409896081</v>
+        <v>6.7709323800817</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.76764724768003</v>
+        <v>6.769542080381705</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.763366662669628</v>
+        <v>6.766709664448286</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.766329265960748</v>
+        <v>6.770884788101214</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.768841688687452</v>
+        <v>6.774341485054833</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.773477903258144</v>
+        <v>6.780260927861439</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.794956191795523</v>
+        <v>6.802887704530592</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.891391962138215</v>
+        <v>6.887659599853333</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.908086591835784</v>
+        <v>6.902076462178316</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.931826209364473</v>
+        <v>6.921333184760109</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.944331281159414</v>
+        <v>6.925985357415419</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141739315428459</v>
+        <v>7.141715336743735</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.152054531319254</v>
+        <v>7.152014651471649</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155557605121911</v>
+        <v>7.155518789119887</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168969398280747</v>
+        <v>7.168925950874531</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183907905567755</v>
+        <v>7.183866678593622</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195827461166995</v>
+        <v>7.195789045321754</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198072757380785</v>
+        <v>7.198038013135204</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192571215640847</v>
+        <v>7.192540482438435</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175279428963013</v>
+        <v>7.175299081217364</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179842608357443</v>
+        <v>7.179887173835326</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.183911067426519</v>
+        <v>7.183952825228838</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189016886696614</v>
+        <v>7.189058102775109</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182435217078571</v>
+        <v>7.182509542152832</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181464707399402</v>
+        <v>7.181550859654831</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.18269678707647</v>
+        <v>7.182768846219289</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168080553297944</v>
+        <v>7.168144707236567</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154346787706058</v>
+        <v>7.154441348265811</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147014835484336</v>
+        <v>7.147122625413824</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.142558082425409</v>
+        <v>7.14269108826435</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.122875040083436</v>
+        <v>7.122985610279262</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.109864003924585</v>
+        <v>7.110010611403711</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.101080133671043</v>
+        <v>7.101243989023017</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.073141008156048</v>
+        <v>7.073321159447057</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.048490103941376</v>
+        <v>7.048674636496753</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.046704836284728</v>
+        <v>7.046902168271616</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.044664848076352</v>
+        <v>7.04491357258963</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.050948442281263</v>
+        <v>7.051256311211716</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.055155755369483</v>
+        <v>7.055584315332473</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.011013291300572</v>
+        <v>7.011410182514627</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.964371993876643</v>
+        <v>6.964688079390046</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.965096001269039</v>
+        <v>6.965399052255487</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.944429764929363</v>
+        <v>6.944796680788555</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.895942541121794</v>
+        <v>6.896138927195834</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.859303138404597</v>
+        <v>6.859506944341422</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.845446376434772</v>
+        <v>6.845605934430957</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825799811552571</v>
+        <v>6.825631117561954</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.845000787221651</v>
+        <v>6.844786870329266</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.861779024770906</v>
+        <v>6.861356377444308</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.89038489158742</v>
+        <v>6.890181142238704</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.89193937651685</v>
+        <v>6.891811087344493</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.880547476893531</v>
+        <v>6.880324293518651</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.870159885313097</v>
+        <v>6.870318995049917</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845018120334634</v>
+        <v>6.845105635692525</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.840284667369638</v>
+        <v>6.840432164823019</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.810009906117824</v>
+        <v>6.809805332425988</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823731970001482</v>
+        <v>6.82375709916465</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.816917430590214</v>
+        <v>6.81709330784027</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.811296683503424</v>
+        <v>6.811496694606347</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.804975672394283</v>
+        <v>6.805201153790899</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.800398756417228</v>
+        <v>6.800637532216562</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.798552456942142</v>
+        <v>6.798798524141033</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782492293368502</v>
+        <v>6.782587502372165</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.782303043875849</v>
+        <v>6.782458335395344</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.774789583113725</v>
+        <v>6.774718269879363</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771257887193721</v>
+        <v>6.771589878486774</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.770870463950795</v>
+        <v>6.771799295030695</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.7709323800817</v>
+        <v>6.772711380246212</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.769542080381705</v>
+        <v>6.772219047032661</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.766709664448286</v>
+        <v>6.770562842271204</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.770884788101214</v>
+        <v>6.774656547908779</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.774341485054833</v>
+        <v>6.778373903601329</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.780260927861439</v>
+        <v>6.785044177759763</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.802887704530592</v>
+        <v>6.806342547040256</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.887659599853333</v>
+        <v>6.871447558928044</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.902076462178316</v>
+        <v>6.880685915444282</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.921333184760109</v>
+        <v>6.890949412606023</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.925985357415419</v>
+        <v>6.882397078448339</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141715336743735</v>
+        <v>7.141704025795445</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.152014651471649</v>
+        <v>7.151995833858635</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155518789119887</v>
+        <v>7.155500460515344</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168925950874531</v>
+        <v>7.168905432994308</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183866678593622</v>
+        <v>7.183847210718281</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195789045321754</v>
+        <v>7.195770906215783</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198038013135204</v>
+        <v>7.198021607946409</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192540482438435</v>
+        <v>7.192525970775888</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175299081217364</v>
+        <v>7.175308301840718</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179887173835326</v>
+        <v>7.17990818331448</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.183952825228838</v>
+        <v>7.183972512835466</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189058102775109</v>
+        <v>7.189077536243606</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182509542152832</v>
+        <v>7.182544589854737</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181550859654831</v>
+        <v>7.181591502672537</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182768846219289</v>
+        <v>7.182802839217731</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168144707236567</v>
+        <v>7.168174931660021</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154441348265811</v>
+        <v>7.154485920711447</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147122625413824</v>
+        <v>7.147173442659549</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.14269108826435</v>
+        <v>7.142753831465426</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.122985610279262</v>
+        <v>7.123037720460792</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110010611403711</v>
+        <v>7.110079806597242</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.101243989023017</v>
+        <v>7.10132139605781</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.073321159447057</v>
+        <v>7.073406371193943</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.048674636496753</v>
+        <v>7.048761928750453</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.046902168271616</v>
+        <v>7.046995462796966</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.04491357258963</v>
+        <v>7.0450310313554</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.051256311211716</v>
+        <v>7.051401634685174</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.055584315332473</v>
+        <v>7.055786540202728</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.011410182514627</v>
+        <v>7.011597297414614</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.964688079390046</v>
+        <v>6.964837342496493</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.965399052255487</v>
+        <v>6.965542349017054</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.944796680788555</v>
+        <v>6.944970789978186</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.896138927195834</v>
+        <v>6.896232279892923</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.859506944341422</v>
+        <v>6.859603900614848</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.845605934430957</v>
+        <v>6.845682254032317</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825631117561954</v>
+        <v>6.825551830762628</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.844786870329266</v>
+        <v>6.844686179022842</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.861356377444308</v>
+        <v>6.861156470538555</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.890181142238704</v>
+        <v>6.890084743099683</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891811087344493</v>
+        <v>6.89175005443966</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.880324293518651</v>
+        <v>6.880218190708831</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.870318995049917</v>
+        <v>6.87039425960025</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845105635692525</v>
+        <v>6.84514719724954</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.840432164823019</v>
+        <v>6.840502169007774</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.809805332425988</v>
+        <v>6.809707930259069</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.82375709916465</v>
+        <v>6.823768606371885</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.81709330784027</v>
+        <v>6.817176078419559</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.811496694606347</v>
+        <v>6.811590867040961</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.805201153790899</v>
+        <v>6.805307483898309</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.800637532216562</v>
+        <v>6.800750360071008</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.798798524141033</v>
+        <v>6.798915151020868</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782587502372165</v>
+        <v>6.782632511119517</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.782458335395344</v>
+        <v>6.782532153178127</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.774718269879363</v>
+        <v>6.774903412774475</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771589878486774</v>
+        <v>6.771983772705827</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.771799295030695</v>
+        <v>6.77234493164098</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.772711380246212</v>
+        <v>6.773219525695156</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.772219047032661</v>
+        <v>6.77254225781267</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.770562842271204</v>
+        <v>6.770637419395323</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.774656547908779</v>
+        <v>6.773497699730008</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.778373903601329</v>
+        <v>6.776506523668853</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.785044177759763</v>
+        <v>6.78189715626233</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.806342547040256</v>
+        <v>6.800509961846249</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.871447558928044</v>
+        <v>6.856537300457442</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.880685915444282</v>
+        <v>6.861970328659265</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.890949412606023</v>
+        <v>6.867056313152259</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.882397078448339</v>
+        <v>6.851001148926187</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141704025795445</v>
+        <v>7.141693133624773</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151995833858635</v>
+        <v>7.151977709350978</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155500460515344</v>
+        <v>7.155482799152114</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168905432994308</v>
+        <v>7.168885660625459</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183847210718281</v>
+        <v>7.183828451057584</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195770906215783</v>
+        <v>7.195753427783783</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198021607946409</v>
+        <v>7.198005800439212</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192525970775888</v>
+        <v>7.192511987584036</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175308301840718</v>
+        <v>7.175317151056376</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.17990818331448</v>
+        <v>7.179928407381831</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.183972512835466</v>
+        <v>7.183991465507432</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189077536243606</v>
+        <v>7.189096245033975</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182544589854737</v>
+        <v>7.182578332564817</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181591502672537</v>
+        <v>7.181630643370249</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182802839217731</v>
+        <v>7.182835574860378</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168174931660021</v>
+        <v>7.168204014208228</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154485920711447</v>
+        <v>7.154528822944332</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147173442659549</v>
+        <v>7.147222361001777</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.142753831465426</v>
+        <v>7.142814253321469</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123037720460792</v>
+        <v>7.123087872729387</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110079806597242</v>
+        <v>7.110146463088644</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.10132139605781</v>
+        <v>7.101396006180967</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.073406371193943</v>
+        <v>7.073488568718859</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.048761928750453</v>
+        <v>7.048846138076147</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.046995462796966</v>
+        <v>7.047085430668914</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.0450310313554</v>
+        <v>7.045144221195442</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.051401634685174</v>
+        <v>7.051541636219898</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.055786540202728</v>
+        <v>7.055981317202661</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.011597297414614</v>
+        <v>7.011777420427453</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.964837342496493</v>
+        <v>6.964981174558853</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.965542349017054</v>
+        <v>6.96568054598612</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.944970789978186</v>
+        <v>6.945139077526015</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.896232279892923</v>
+        <v>6.896322610014959</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.859603900614848</v>
+        <v>6.859697763922195</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.845682254032317</v>
+        <v>6.845756387877552</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825551830762628</v>
+        <v>6.825475655790765</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.844686179022842</v>
+        <v>6.84458934869714</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.861156470538555</v>
+        <v>6.860963639361012</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.890084743099683</v>
+        <v>6.889991739044758</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.89175005443966</v>
+        <v>6.891690968284237</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.880218190708831</v>
+        <v>6.880115516077852</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.87039425960025</v>
+        <v>6.870466865720719</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.84514719724954</v>
+        <v>6.845187390420362</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.840502169007774</v>
+        <v>6.84056984255689</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.809707930259069</v>
+        <v>6.809613586790904</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823768606371885</v>
+        <v>6.823779476381494</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817176078419559</v>
+        <v>6.817255665886437</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.811590867040961</v>
+        <v>6.81168144426845</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.805307483898309</v>
+        <v>6.805409855371455</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.800750360071008</v>
+        <v>6.800859126383008</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.798915151020868</v>
+        <v>6.799027794476025</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782632511119517</v>
+        <v>6.782675910889926</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.782532153178127</v>
+        <v>6.78260357961661</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.774903412774475</v>
+        <v>6.774929170568877</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771983772705827</v>
+        <v>6.771728480418616</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.77234493164098</v>
+        <v>6.771512933834129</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.773219525695156</v>
+        <v>6.771929297836461</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.77254225781267</v>
+        <v>6.76985494675854</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.770637419395323</v>
+        <v>6.766643326382141</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.773497699730008</v>
+        <v>6.767405610626085</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.776506523668853</v>
+        <v>6.768951502610345</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.78189715626233</v>
+        <v>6.772728803565485</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.800509961846249</v>
+        <v>6.78832434386104</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.856537300457442</v>
+        <v>6.832956358619212</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.861970328659265</v>
+        <v>6.835654388709556</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.867056313152259</v>
+        <v>6.835918577878843</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,15 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.851001148926187</v>
+        <v>6.81328568271929</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B109">
+        <v>6.76858568271929</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141693133624773</v>
+        <v>7.14168263739966</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151977709350978</v>
+        <v>7.151960240356954</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155482799152114</v>
+        <v>7.155465769268137</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168885660625459</v>
+        <v>7.16886659388978</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183828451057584</v>
+        <v>7.183810361681221</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195753427783783</v>
+        <v>7.195736574597472</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.198005800439212</v>
+        <v>7.197990558553316</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192511987584036</v>
+        <v>7.192498504525785</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175317151056376</v>
+        <v>7.175325650704959</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179928407381831</v>
+        <v>7.179947889248825</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.183991465507432</v>
+        <v>7.184009723623258</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189096245033975</v>
+        <v>7.189114268920529</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182578332564817</v>
+        <v>7.182610841779384</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181630643370249</v>
+        <v>7.181668363434579</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182835574860378</v>
+        <v>7.182867121593228</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168204014208228</v>
+        <v>7.168232018292018</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154528822944332</v>
+        <v>7.154570146946469</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147222361001777</v>
+        <v>7.147269484660686</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.142814253321469</v>
+        <v>7.142872480116027</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123087872729387</v>
+        <v>7.123136175179959</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110146463088644</v>
+        <v>7.110210717675036</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.101396006180967</v>
+        <v>7.101467967718192</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.073488568718859</v>
+        <v>7.073567908550228</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.048846138076147</v>
+        <v>7.048927424265987</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047085430668914</v>
+        <v>7.047172246058059</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.045144221195442</v>
+        <v>7.045253369989727</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.051541636219898</v>
+        <v>7.051676601843809</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.055981317202661</v>
+        <v>7.056169048451045</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.011777420427453</v>
+        <v>7.011950934676682</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.964981174558853</v>
+        <v>6.965119864332281</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.96568054598612</v>
+        <v>6.965813907940589</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.945139077526015</v>
+        <v>6.945301826977245</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.896322610014959</v>
+        <v>6.896410059172755</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.859697763922195</v>
+        <v>6.859788676518603</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.845756387877552</v>
+        <v>6.845828421416946</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825475655790765</v>
+        <v>6.825402414905687</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.84458934869714</v>
+        <v>6.844496163474361</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.860963639361012</v>
+        <v>6.860777516826024</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889991739044758</v>
+        <v>6.889901954951205</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891690968284237</v>
+        <v>6.891633740028762</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.880115516077852</v>
+        <v>6.880016109419994</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.870466865720719</v>
+        <v>6.870536951647244</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845187390420362</v>
+        <v>6.845226281245776</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.84056984255689</v>
+        <v>6.840635299640224</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.809613586790904</v>
+        <v>6.80952216432905</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823779476381494</v>
+        <v>6.823789754417069</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817255665886437</v>
+        <v>6.817332248722305</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.81168144426845</v>
+        <v>6.81176862624991</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.805409855371455</v>
+        <v>6.805508483330966</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.800859126383008</v>
+        <v>6.800964044727889</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.799027794476025</v>
+        <v>6.799136652690793</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782675910889926</v>
+        <v>6.782717785104601</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.78260357961661</v>
+        <v>6.782672726180252</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.774929170568877</v>
+        <v>6.774954285464947</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771728480418616</v>
+        <v>6.771526535895082</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.771512933834129</v>
+        <v>6.770829570512364</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.771929297836461</v>
+        <v>6.770884686048938</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.76985494675854</v>
+        <v>6.767701100564895</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.766643326382141</v>
+        <v>6.763414938885544</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.767405610626085</v>
+        <v>6.762476212951364</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.768951502610345</v>
+        <v>6.762886964717101</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.772728803565485</v>
+        <v>6.765398725577985</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.78832434386104</v>
+        <v>6.778606887392552</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.832956358619212</v>
+        <v>6.814681752848292</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.835654388709556</v>
+        <v>6.815507396063545</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.835918577878843</v>
+        <v>6.812628613047576</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.81328568271929</v>
+        <v>6.786876603680591</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.76858568271929</v>
+        <v>6.742176603680591</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.770829570512364</v>
+        <v>6.770834030998513</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.770884686048938</v>
+        <v>6.770884638840524</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.767701100564895</v>
+        <v>6.767739067393587</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.763414938885544</v>
+        <v>6.763493604105632</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.762476212951364</v>
+        <v>6.762619328376458</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.762886964717101</v>
+        <v>6.763000750370386</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.765398725577985</v>
+        <v>6.765595831908112</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.778606887392552</v>
+        <v>6.779409793503381</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.814681752848292</v>
+        <v>6.815531376729986</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.815507396063545</v>
+        <v>6.816013238823636</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.812628613047576</v>
+        <v>6.8131041021262</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.786876603680591</v>
+        <v>6.787297424848246</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.742176603680591</v>
+        <v>6.742597424848246</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.770834030998513</v>
+        <v>6.770828304163212</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.770884638840524</v>
+        <v>6.770858794972843</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.767739067393587</v>
+        <v>6.767702187008232</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.763493604105632</v>
+        <v>6.763474162150694</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.762619328376458</v>
+        <v>6.762566092069614</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.763000750370386</v>
+        <v>6.762952763506517</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.765595831908112</v>
+        <v>6.765158270423905</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.779409793503381</v>
+        <v>6.779106828850479</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.815531376729986</v>
+        <v>6.815172677452664</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.816013238823636</v>
+        <v>6.815432327998025</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.8131041021262</v>
+        <v>6.812919579670441</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.787297424848246</v>
+        <v>6.787132362345774</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.742597424848246</v>
+        <v>6.742432362345775</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.14168263739966</v>
+        <v>7.141672515918004</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151960240356954</v>
+        <v>7.151943391954376</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155465769268137</v>
+        <v>7.155449337610587</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.16886659388978</v>
+        <v>7.168848195701421</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183810361681221</v>
+        <v>7.183792907318248</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195736574597472</v>
+        <v>7.195720313715702</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197990558553316</v>
+        <v>7.19797585247991</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192498504525785</v>
+        <v>7.192485495253409</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175325650704959</v>
+        <v>7.175333820957512</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179947889248825</v>
+        <v>7.17996666901572</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184009723623258</v>
+        <v>7.184027324658082</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189114268920529</v>
+        <v>7.189131644820463</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182610841779384</v>
+        <v>7.182642183869661</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181668363434579</v>
+        <v>7.181704738742262</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182867121593228</v>
+        <v>7.182897542986241</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168232018292018</v>
+        <v>7.168259002719159</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154570146946469</v>
+        <v>7.154609978079051</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147269484660686</v>
+        <v>7.147314910384718</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.142872480116027</v>
+        <v>7.142928629149925</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123136175179959</v>
+        <v>7.123182728108758</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110210717675036</v>
+        <v>7.11027269752619</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.101467967718192</v>
+        <v>7.101537418729379</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.073567908550228</v>
+        <v>7.073644536606965</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.048927424265987</v>
+        <v>7.049005936305591</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047172246058059</v>
+        <v>7.047256071229685</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.045253369989727</v>
+        <v>7.045358689729939</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.051676601843809</v>
+        <v>7.05180679752185</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.056169048451045</v>
+        <v>7.056350107761208</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.011950934676682</v>
+        <v>7.0121181959054</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.965119864332281</v>
+        <v>6.96525368062343</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.965813907940589</v>
+        <v>6.96594268183486</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.945301826977245</v>
+        <v>6.945459304022914</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.896410059172755</v>
+        <v>6.896494760480581</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.859788676518603</v>
+        <v>6.859876772325714</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.845828421416946</v>
+        <v>6.845898436310969</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825402414905687</v>
+        <v>6.825331943528402</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.844496163474361</v>
+        <v>6.844406423145958</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.860777516826024</v>
+        <v>6.860597760666018</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889901954951205</v>
+        <v>6.88981522745673</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891633740028762</v>
+        <v>6.89157828592518</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.880016109419994</v>
+        <v>6.879919820106899</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.870536951647244</v>
+        <v>6.870604646204472</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845226281245776</v>
+        <v>6.845263931611662</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.840635299640224</v>
+        <v>6.840698647106097</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.80952216432905</v>
+        <v>6.809433533003825</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823789754417069</v>
+        <v>6.823799481798956</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817332248722305</v>
+        <v>6.817405992418969</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.81176862624991</v>
+        <v>6.811852598523112</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.805508483330966</v>
+        <v>6.805603567716447</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.800964044727889</v>
+        <v>6.801065314093952</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.799136652690793</v>
+        <v>6.799241911097541</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782717785104601</v>
+        <v>6.782758211611648</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.782672726180252</v>
+        <v>6.782739697736895</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.774954285464947</v>
+        <v>6.774978777341289</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771526535895082</v>
+        <v>6.771626448800066</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.770828304163212</v>
+        <v>6.770546913882578</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.770858794972843</v>
+        <v>6.770195499790484</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.767702187008232</v>
+        <v>6.765926045533472</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.763474162150694</v>
+        <v>6.760694486632729</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.762566092069614</v>
+        <v>6.758211359451684</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.762952763506517</v>
+        <v>6.757516008784734</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.765158270423905</v>
+        <v>6.758101002485205</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.779106828850479</v>
+        <v>6.769956124494746</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.815172677452664</v>
+        <v>6.798513329448832</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.815432327998025</v>
+        <v>6.797307148965865</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.812919579670441</v>
+        <v>6.79282775380638</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.787132362345774</v>
+        <v>6.76547544199867</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.742432362345775</v>
+        <v>6.609100157297622</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141672515918004</v>
+        <v>7.141662749464785</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151943391954376</v>
+        <v>7.151927131657841</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155449337610587</v>
+        <v>7.155433473219725</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168848195701421</v>
+        <v>7.168830431526859</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183792907318248</v>
+        <v>7.183776055128177</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195720313715702</v>
+        <v>7.195704614470099</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.19797585247991</v>
+        <v>7.197961654467544</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192485495253409</v>
+        <v>7.192472935237076</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175333820957512</v>
+        <v>7.175341680471268</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.17996666901572</v>
+        <v>7.179984783946484</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184027324658082</v>
+        <v>7.184044303439884</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189131644820463</v>
+        <v>7.189148407045759</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182642183869661</v>
+        <v>7.182672420532603</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181704738742262</v>
+        <v>7.18173983986707</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182897542986241</v>
+        <v>7.182926898159666</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168259002719159</v>
+        <v>7.168285022104021</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154609978079051</v>
+        <v>7.154648395666664</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147314910384718</v>
+        <v>7.147358728106852</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.142928629149925</v>
+        <v>7.142982809524795</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123182728108758</v>
+        <v>7.123227624702989</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11027269752619</v>
+        <v>7.11033252101447</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.101537418729379</v>
+        <v>7.101604487878216</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.073644536606965</v>
+        <v>7.073718589078573</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049005936305591</v>
+        <v>7.04908181326816</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047256071229685</v>
+        <v>7.047337057540072</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.045358689729939</v>
+        <v>7.045460377876456</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.05180679752185</v>
+        <v>7.051932470878587</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.056350107761208</v>
+        <v>7.056524843077431</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.0121181959054</v>
+        <v>7.01227953487013</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.96525368062343</v>
+        <v>6.96538287396961</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.96594268183486</v>
+        <v>6.966067098257435</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.945459304022914</v>
+        <v>6.945611757859393</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.896494760480581</v>
+        <v>6.896576839163956</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.859876772325714</v>
+        <v>6.859962177508626</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.845898436310969</v>
+        <v>6.845966510569421</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825331943528402</v>
+        <v>6.825264089055004</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.844406423145958</v>
+        <v>6.844319941786721</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.860597760666018</v>
+        <v>6.860424051381198</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.88981522745673</v>
+        <v>6.889731403995542</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.89157828592518</v>
+        <v>6.891524526988404</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.879919820106899</v>
+        <v>6.879826506406461</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.870604646204472</v>
+        <v>6.870670069592636</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845263931611662</v>
+        <v>6.845300399568665</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.840698647106097</v>
+        <v>6.840759985058127</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.809433533003825</v>
+        <v>6.809347570251568</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823799481798956</v>
+        <v>6.823808696339166</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817405992418969</v>
+        <v>6.817477050630382</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.811852598523112</v>
+        <v>6.811933533468837</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.805603567716447</v>
+        <v>6.805695294591665</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.801065314093952</v>
+        <v>6.801163120095737</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.799241911097541</v>
+        <v>6.799343743369767</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782758211611648</v>
+        <v>6.782797263135249</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.782739697736895</v>
+        <v>6.782804593013141</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.774978777341289</v>
+        <v>6.775002665611565</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771626448800066</v>
+        <v>6.771934116175945</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.770546913882578</v>
+        <v>6.770614099289131</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.770195499790484</v>
+        <v>6.7699756246656</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.765926045533472</v>
+        <v>6.764981328499324</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.760694486632729</v>
+        <v>6.758883195558045</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.758211359451684</v>
+        <v>6.755294212314116</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.757516008784734</v>
+        <v>6.753332700540362</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.758101002485205</v>
+        <v>6.753177917629009</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.769956124494746</v>
+        <v>6.762958979267021</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.798513329448832</v>
+        <v>6.786550375094371</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.797307148965865</v>
+        <v>6.784705439691013</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.79282775380638</v>
+        <v>6.77885069529331</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.76547544199867</v>
+        <v>6.751534717710176</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.609100157297622</v>
+        <v>6.616365962942586</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.770614099289131</v>
+        <v>6.770613001518036</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.7699756246656</v>
+        <v>6.769953152713333</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.764981328499324</v>
+        <v>6.764982309946226</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.758883195558045</v>
+        <v>6.758934288229268</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.755294212314116</v>
+        <v>6.755371026865069</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.753332700540362</v>
+        <v>6.753388617203971</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.753177917629009</v>
+        <v>6.75297423927201</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.762958979267021</v>
+        <v>6.763380950860368</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.786550375094371</v>
+        <v>6.786953854347321</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.784705439691013</v>
+        <v>6.78464514566156</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.77885069529331</v>
+        <v>6.779083515302467</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.751534717710176</v>
+        <v>6.751731486852096</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.616365962942586</v>
+        <v>6.616694486078997</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141662749464785</v>
+        <v>7.141653319683936</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151927131657841</v>
+        <v>7.151911429209854</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155433473219725</v>
+        <v>7.155418147234706</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168830431526859</v>
+        <v>7.16881326916918</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183776055128177</v>
+        <v>7.183759774495312</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195704614470099</v>
+        <v>7.195689448272492</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197961654467544</v>
+        <v>7.197947938647737</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192472935237076</v>
+        <v>7.192460801610788</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175341680471268</v>
+        <v>7.175349246528349</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.179984783946484</v>
+        <v>7.18000226871509</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184044303439884</v>
+        <v>7.184060692379067</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189148407045759</v>
+        <v>7.18916458752891</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182672420532603</v>
+        <v>7.182701609194958</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.18173983986707</v>
+        <v>7.181773732534639</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182926898159666</v>
+        <v>7.182955242166435</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168285022104021</v>
+        <v>7.168310127234315</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154648395666664</v>
+        <v>7.154685473520779</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147358728106852</v>
+        <v>7.147401021533032</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.142982809524795</v>
+        <v>7.143035122846134</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123227624702989</v>
+        <v>7.123270951658654</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11033252101447</v>
+        <v>7.110390298460611</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.101604487878216</v>
+        <v>7.101669295215189</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.073718589078573</v>
+        <v>7.073790193219438</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.04908181326816</v>
+        <v>7.049155185121698</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047337057540072</v>
+        <v>7.047415346334803</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.045460377876456</v>
+        <v>7.045558618578974</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.051932470878587</v>
+        <v>7.052053852746934</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.056524843077431</v>
+        <v>7.056693578665049</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.01227953487013</v>
+        <v>7.012435259488758</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.96538287396961</v>
+        <v>6.965507678152639</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.966067098257435</v>
+        <v>6.966187372749654</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.945611757859393</v>
+        <v>6.945759422428148</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.896576839163956</v>
+        <v>6.896656413118277</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.859962177508626</v>
+        <v>6.860045011008358</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.845966510569421</v>
+        <v>6.846032718695088</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825264089055004</v>
+        <v>6.825198709795279</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.844319941786721</v>
+        <v>6.844236546512397</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.860424051381198</v>
+        <v>6.860256090387947</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889731403995542</v>
+        <v>6.889650341927003</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891524526988404</v>
+        <v>6.891472388681668</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.879826506406461</v>
+        <v>6.879736034856279</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.870670069592636</v>
+        <v>6.870733334096816</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845300399568665</v>
+        <v>6.845335739622948</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.840759985058127</v>
+        <v>6.8408194073784</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.809347570251568</v>
+        <v>6.809264160334616</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823808696339166</v>
+        <v>6.82381743269065</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817477050630382</v>
+        <v>6.817545566204843</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.811933533468837</v>
+        <v>6.812011591447212</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.805695294591665</v>
+        <v>6.805783837318471</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.801163120095737</v>
+        <v>6.801257636069334</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.799343743369767</v>
+        <v>6.799442312325542</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782797263135249</v>
+        <v>6.782835007682991</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.782804593013141</v>
+        <v>6.782867505019226</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775002665611565</v>
+        <v>6.775025969192926</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771934116175945</v>
+        <v>6.772212964055061</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.770613001518036</v>
+        <v>6.770740467681588</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.769953152713333</v>
+        <v>6.769881678705172</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.764982309946226</v>
+        <v>6.764553242895191</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.758934288229268</v>
+        <v>6.757963407386393</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.755371026865069</v>
+        <v>6.753987411145129</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.753388617203971</v>
+        <v>6.751598326241012</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.75297423927201</v>
+        <v>6.750767903961451</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.763380950860368</v>
+        <v>6.75988015568983</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.786953854347321</v>
+        <v>6.779245749715769</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.78464514566156</v>
+        <v>6.775109884151379</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.779083515302467</v>
+        <v>6.767927280117885</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.751731486852096</v>
+        <v>6.740502563247276</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.616694486078997</v>
+        <v>6.620824016943715</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141653319683936</v>
+        <v>7.141635402830802</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151911429209854</v>
+        <v>7.151881586861435</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155418147234706</v>
+        <v>7.155389004501604</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.16881326916918</v>
+        <v>7.168780631653663</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183759774495312</v>
+        <v>7.183728815469612</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195689448272492</v>
+        <v>7.195660610046541</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197947938647737</v>
+        <v>7.197921858600342</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192460801610788</v>
+        <v>7.192437729565246</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175349246528349</v>
+        <v>7.175363561255236</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.18000226871509</v>
+        <v>7.180035474816002</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184060692379067</v>
+        <v>7.184091819499237</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.18916458752891</v>
+        <v>7.18919532029702</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182701609194958</v>
+        <v>7.18275705301499</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181773732534639</v>
+        <v>7.181838133572333</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182955242166435</v>
+        <v>7.183009098582777</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168310127234315</v>
+        <v>7.168357780689218</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154685473520779</v>
+        <v>7.154755880481958</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147401021533032</v>
+        <v>7.147481342305273</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143035122846134</v>
+        <v>7.143134520998894</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123270951658654</v>
+        <v>7.123353214254058</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110390298460611</v>
+        <v>7.110500120213564</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.101669295215189</v>
+        <v>7.101792565759158</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.073790193219438</v>
+        <v>7.07392652509149</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049155185121698</v>
+        <v>7.049294892158693</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047415346334803</v>
+        <v>7.047564351496508</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.045558618578974</v>
+        <v>7.045745434190237</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.052053852746934</v>
+        <v>7.052284589625071</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.056693578665049</v>
+        <v>7.057014240961642</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.012435259488758</v>
+        <v>7.012730994559426</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.965507678152639</v>
+        <v>6.965744978450382</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.966187372749654</v>
+        <v>6.966416289930455</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.945759422428148</v>
+        <v>6.946041249947042</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.896656413118277</v>
+        <v>6.896808484812041</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860045011008358</v>
+        <v>6.860203405513856</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846032718695088</v>
+        <v>6.846159817897146</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825198709795279</v>
+        <v>6.825074859114146</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.844236546512397</v>
+        <v>6.844078381303601</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.860256090387947</v>
+        <v>6.85993631363106</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889650341927003</v>
+        <v>6.889495976370961</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891472388681668</v>
+        <v>6.891372696319782</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.879736034856279</v>
+        <v>6.879563122291138</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.870733334096816</v>
+        <v>6.870853799799268</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845335739622948</v>
+        <v>6.845403237891473</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.8408194073784</v>
+        <v>6.840932852352929</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.809264160334616</v>
+        <v>6.809104567543406</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.82381743269065</v>
+        <v>6.823833595466775</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817545566204843</v>
+        <v>6.817675492275287</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812011591447212</v>
+        <v>6.812159663866231</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.805783837318471</v>
+        <v>6.805952006507062</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.801257636069334</v>
+        <v>6.801437435732771</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.799442312325542</v>
+        <v>6.799630262147815</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782835007682991</v>
+        <v>6.782906826483964</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.782867505019226</v>
+        <v>6.782987725002817</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775025969192926</v>
+        <v>6.775070895350792</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772212964055061</v>
+        <v>6.772215107597569</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.770740467681588</v>
+        <v>6.77018475263284</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.769881678705172</v>
+        <v>6.768931184978507</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.764553242895191</v>
+        <v>6.763133236355438</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.757963407386393</v>
+        <v>6.755227343336714</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.753987411145129</v>
+        <v>6.749862425794228</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.751598326241012</v>
+        <v>6.746179174350638</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.750767903961451</v>
+        <v>6.74419640781932</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.75988015568983</v>
+        <v>6.750996737899192</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.779245749715769</v>
+        <v>6.764319389730584</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.775109884151379</v>
+        <v>6.756432283462271</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.767927280117885</v>
+        <v>6.746955050848054</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.740502563247276</v>
+        <v>6.719712890822356</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,15 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.620824016943715</v>
+        <v>6.619121817391928</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B110">
+        <v>6.609467861918536</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141635402830802</v>
+        <v>7.141653319683936</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151881586861435</v>
+        <v>7.151911429209854</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155389004501604</v>
+        <v>7.155418147234706</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168780631653663</v>
+        <v>7.16881326916918</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183728815469612</v>
+        <v>7.183759774495312</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195660610046541</v>
+        <v>7.195689448272492</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197921858600342</v>
+        <v>7.197947938647737</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192437729565246</v>
+        <v>7.192460801610788</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175363561255236</v>
+        <v>7.175349246528349</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180035474816002</v>
+        <v>7.18000226871509</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184091819499237</v>
+        <v>7.184060692379067</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.18919532029702</v>
+        <v>7.18916458752891</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18275705301499</v>
+        <v>7.182701609194958</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181838133572333</v>
+        <v>7.181773732534639</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183009098582777</v>
+        <v>7.182955242166435</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168357780689218</v>
+        <v>7.168310127234315</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154755880481958</v>
+        <v>7.154685473520779</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147481342305273</v>
+        <v>7.147401021533032</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143134520998894</v>
+        <v>7.143035122846134</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123353214254058</v>
+        <v>7.123270951658654</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110500120213564</v>
+        <v>7.110390298460611</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.101792565759158</v>
+        <v>7.101669295215189</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.07392652509149</v>
+        <v>7.073790193219438</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049294892158693</v>
+        <v>7.049155185121698</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047564351496508</v>
+        <v>7.047415346334803</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.045745434190237</v>
+        <v>7.045558618578974</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.052284589625071</v>
+        <v>7.052053852746934</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.057014240961642</v>
+        <v>7.056693578665049</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.012730994559426</v>
+        <v>7.012435259488758</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.965744978450382</v>
+        <v>6.965507678152639</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.966416289930455</v>
+        <v>6.966187372749654</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.946041249947042</v>
+        <v>6.945759422428148</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.896808484812041</v>
+        <v>6.896656413118277</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860203405513856</v>
+        <v>6.860045011008358</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846159817897146</v>
+        <v>6.846032718695088</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825074859114146</v>
+        <v>6.825198709795279</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.844078381303601</v>
+        <v>6.844236546512397</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.85993631363106</v>
+        <v>6.860256090387947</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889495976370961</v>
+        <v>6.889650341927003</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891372696319782</v>
+        <v>6.891472388681668</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.879563122291138</v>
+        <v>6.879736034856279</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.870853799799268</v>
+        <v>6.870733334096816</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845403237891473</v>
+        <v>6.845335739622948</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.840932852352929</v>
+        <v>6.8408194073784</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.809104567543406</v>
+        <v>6.809264160334616</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823833595466775</v>
+        <v>6.82381743269065</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817675492275287</v>
+        <v>6.817545566204843</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812159663866231</v>
+        <v>6.812011591447212</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.805952006507062</v>
+        <v>6.805783837318471</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.801437435732771</v>
+        <v>6.801257636069334</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.799630262147815</v>
+        <v>6.799442312325542</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782906826483964</v>
+        <v>6.782835007682991</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.782987725002817</v>
+        <v>6.782867505019226</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775070895350792</v>
+        <v>6.775025969192926</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772215107597569</v>
+        <v>6.771937432213594</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.77018475263284</v>
+        <v>6.770280848664179</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.768931184978507</v>
+        <v>6.769381553905314</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.763133236355438</v>
+        <v>6.76417275323846</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.755227343336714</v>
+        <v>6.7566016433843</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.749862425794228</v>
+        <v>6.751212534247598</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.746179174350638</v>
+        <v>6.747607233819281</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.74419640781932</v>
+        <v>6.746596669371408</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.750996737899192</v>
+        <v>6.754829047587605</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.764319389730584</v>
+        <v>6.774394021937953</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.756432283462271</v>
+        <v>6.770053229022084</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.746955050848054</v>
+        <v>6.763826221840018</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.719712890822356</v>
+        <v>6.737392910441077</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.619121817391928</v>
+        <v>6.617822360784057</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.609467861918536</v>
+        <v>6.630360516078802</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.769381553905314</v>
+        <v>6.769386333201917</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.76417275323846</v>
+        <v>6.764184854963689</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.7566016433843</v>
+        <v>6.756620597586631</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.751212534247598</v>
+        <v>6.751590368574039</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.747607233819281</v>
+        <v>6.748304470074802</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.746596669371408</v>
+        <v>6.747099686924228</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.754829047587605</v>
+        <v>6.755231001102911</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.774394021937953</v>
+        <v>6.774637663584295</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.770053229022084</v>
+        <v>6.77067832186119</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.763826221840018</v>
+        <v>6.764083378481441</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.737392910441077</v>
+        <v>6.73762212632359</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.617822360784057</v>
+        <v>6.618179088716849</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.630360516078802</v>
+        <v>6.631659139943824</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141653319683936</v>
+        <v>7.141644209463252</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151911429209854</v>
+        <v>7.151896256393115</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155418147234706</v>
+        <v>7.155403332718763</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.16881326916918</v>
+        <v>7.168796678573874</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183759774495312</v>
+        <v>7.183744036843589</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195689448272492</v>
+        <v>7.195674788441558</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197947938647737</v>
+        <v>7.197934680877999</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192460801610788</v>
+        <v>7.192449073033729</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175349246528349</v>
+        <v>7.17535653515959</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.18000226871509</v>
+        <v>7.180019155626606</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184060692379067</v>
+        <v>7.184076521674569</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.18916458752891</v>
+        <v>7.189180216025603</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182701609194958</v>
+        <v>7.182729803376187</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181773732534639</v>
+        <v>7.18180647803131</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182955242166435</v>
+        <v>7.182982626335807</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168310127234315</v>
+        <v>7.16833436540006</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154685473520779</v>
+        <v>7.154721280409816</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147401021533032</v>
+        <v>7.147441868670839</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143035122846134</v>
+        <v>7.143085663855331</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123270951658654</v>
+        <v>7.123312789735149</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110390298460611</v>
+        <v>7.11044613280508</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.101669295215189</v>
+        <v>7.101731952883881</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.073790193219438</v>
+        <v>7.073859468066909</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049155185121698</v>
+        <v>7.049226173458973</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047415346334803</v>
+        <v>7.047491069760046</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.045558618578974</v>
+        <v>7.045653583776488</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.052053852746934</v>
+        <v>7.052171158563077</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.056693578665049</v>
+        <v>7.05685661708273</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.012435259488758</v>
+        <v>7.012585656771421</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.965507678152639</v>
+        <v>6.965628311565826</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.966187372749654</v>
+        <v>6.96630370700046</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.945759422428148</v>
+        <v>6.94590251754751</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.896656413118277</v>
+        <v>6.896733593422535</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860045011008358</v>
+        <v>6.860125385033436</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846032718695088</v>
+        <v>6.846097131829264</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825198709795279</v>
+        <v>6.825135674021467</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.844236546512397</v>
+        <v>6.844156076363931</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.860256090387947</v>
+        <v>6.860093598343997</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889650341927003</v>
+        <v>6.889571907746676</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891472388681668</v>
+        <v>6.891421800624219</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.879736034856279</v>
+        <v>6.879648279686974</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.870733334096816</v>
+        <v>6.87079454472738</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845335739622948</v>
+        <v>6.845370003001049</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.8408194073784</v>
+        <v>6.84087700220271</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.809264160334616</v>
+        <v>6.809183193895565</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.82381743269065</v>
+        <v>6.823825722656888</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817545566204843</v>
+        <v>6.817611672111763</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812011591447212</v>
+        <v>6.812086921819157</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.805783837318471</v>
+        <v>6.805869357614387</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.801257636069334</v>
+        <v>6.801349024062748</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.799442312325542</v>
+        <v>6.799537770750407</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782835007682991</v>
+        <v>6.782871508915749</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.782867505019226</v>
+        <v>6.782928521441161</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775025969192926</v>
+        <v>6.775048706484007</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771937432213594</v>
+        <v>6.771940790655631</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.770280848664179</v>
+        <v>6.770357076068589</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.769386333201917</v>
+        <v>6.769359217661311</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.764184854963689</v>
+        <v>6.764022819948991</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.756620597586631</v>
+        <v>6.755286294696162</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.751590368574039</v>
+        <v>6.749117800522872</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.748304470074802</v>
+        <v>6.74473613917952</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.747099686924228</v>
+        <v>6.742651291039265</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.755231001102911</v>
+        <v>6.749390683002517</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.774637663584295</v>
+        <v>6.765597241044599</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.77067832186119</v>
+        <v>6.760094439500552</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.764083378481441</v>
+        <v>6.753185185518601</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.73762212632359</v>
+        <v>6.72811240046981</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.618179088716849</v>
+        <v>6.623276092101992</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.631659139943824</v>
+        <v>6.643379687766304</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141644209463252</v>
+        <v>7.141626884861498</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151896256393115</v>
+        <v>7.151867395987212</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155403332718763</v>
+        <v>7.155375139036996</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168796678573874</v>
+        <v>7.168765102130236</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183744036843589</v>
+        <v>7.183714085391804</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195674788441558</v>
+        <v>7.19564688976607</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197934680877999</v>
+        <v>7.197909450713421</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192449073033729</v>
+        <v>7.192426752551917</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.17535653515959</v>
+        <v>7.175370338664161</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180019155626606</v>
+        <v>7.180051254427287</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184076521674569</v>
+        <v>7.184106612166874</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189180216025603</v>
+        <v>7.189209926274136</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182729803376187</v>
+        <v>7.182783404763648</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.18180647803131</v>
+        <v>7.181868752634045</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.182982626335807</v>
+        <v>7.183034703687152</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.16833436540006</v>
+        <v>7.168380414253877</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154721280409816</v>
+        <v>7.154789333646199</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147441868670839</v>
+        <v>7.14751951042775</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143085663855331</v>
+        <v>7.143181776942043</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123312789735149</v>
+        <v>7.123392295548551</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11044613280508</v>
+        <v>7.11055235062392</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.101731952883881</v>
+        <v>7.101851232024709</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.073859468066909</v>
+        <v>7.073991468786515</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049226173458973</v>
+        <v>7.049361447985271</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047491069760046</v>
+        <v>7.047635307424436</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.045653583776488</v>
+        <v>7.045834320221577</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.052171158563077</v>
+        <v>7.052394334230351</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.05685661708273</v>
+        <v>7.05716671461315</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.012585656771421</v>
+        <v>7.012871523094036</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.965628311565826</v>
+        <v>6.965857870015359</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.96630370700046</v>
+        <v>6.966525298676826</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.94590251754751</v>
+        <v>6.946175814213898</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.896733593422535</v>
+        <v>6.896881186113738</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860125385033436</v>
+        <v>6.860279172520528</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846097131829264</v>
+        <v>6.846220841751499</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825135674021467</v>
+        <v>6.825016150793967</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.844156076363931</v>
+        <v>6.844003321310247</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.860093598343997</v>
+        <v>6.859783990978082</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889571907746676</v>
+        <v>6.889422430487429</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891421800624219</v>
+        <v>6.89132501290446</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.879648279686974</v>
+        <v>6.879480450734016</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.87079454472738</v>
+        <v>6.870911191456836</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845370003001049</v>
+        <v>6.845435489665354</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.84087700220271</v>
+        <v>6.840987035730945</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.809183193895565</v>
+        <v>6.809028183469248</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823825722656888</v>
+        <v>6.823841078019242</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817611672111763</v>
+        <v>6.817737142325435</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812086921819157</v>
+        <v>6.812229947620358</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.805869357614387</v>
+        <v>6.806031925197024</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.801349024062748</v>
+        <v>6.801523013158378</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.799537770750407</v>
+        <v>6.799719921424269</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782871508915749</v>
+        <v>6.782941016333716</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.782928521441161</v>
+        <v>6.783045193800314</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775048706484007</v>
+        <v>6.775092553118836</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771940790655631</v>
+        <v>6.7722166696633</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.770357076068589</v>
+        <v>6.77026331139735</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.769359217661311</v>
+        <v>6.768929471036222</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.764022819948991</v>
+        <v>6.763050384915033</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.755286294696162</v>
+        <v>6.754466659290552</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.749117800522872</v>
+        <v>6.74817666687046</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.74473613917952</v>
+        <v>6.743584540746298</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.742651291039265</v>
+        <v>6.74085786302032</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.749390683002517</v>
+        <v>6.746761206329675</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.765597241044599</v>
+        <v>6.758226170703281</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.760094439500552</v>
+        <v>6.748538750198872</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.753185185518601</v>
+        <v>6.738495111685594</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.72811240046981</v>
+        <v>6.711687606192694</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.623276092101992</v>
+        <v>6.618527442962996</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.643379687766304</v>
+        <v>6.606498110605967</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141626884861498</v>
+        <v>7.141635402830802</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151867395987212</v>
+        <v>7.151881586861435</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155375139036996</v>
+        <v>7.155389004501604</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168765102130236</v>
+        <v>7.168780631653663</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183714085391804</v>
+        <v>7.183728815469612</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19564688976607</v>
+        <v>7.195660610046541</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197909450713421</v>
+        <v>7.197921858600342</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192426752551917</v>
+        <v>7.192437729565246</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175370338664161</v>
+        <v>7.175363561255236</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180051254427287</v>
+        <v>7.180035474816002</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184106612166874</v>
+        <v>7.184091819499237</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189209926274136</v>
+        <v>7.18919532029702</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182783404763648</v>
+        <v>7.18275705301499</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181868752634045</v>
+        <v>7.181838133572333</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183034703687152</v>
+        <v>7.183009098582777</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168380414253877</v>
+        <v>7.168357780689218</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154789333646199</v>
+        <v>7.154755880481958</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.14751951042775</v>
+        <v>7.147481342305273</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143181776942043</v>
+        <v>7.143134520998894</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123392295548551</v>
+        <v>7.123353214254058</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11055235062392</v>
+        <v>7.110500120213564</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.101851232024709</v>
+        <v>7.101792565759158</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.073991468786515</v>
+        <v>7.07392652509149</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049361447985271</v>
+        <v>7.049294892158693</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047635307424436</v>
+        <v>7.047564351496508</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.045834320221577</v>
+        <v>7.045745434190237</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.052394334230351</v>
+        <v>7.052284589625071</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.05716671461315</v>
+        <v>7.057014240961642</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.012871523094036</v>
+        <v>7.012730994559426</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.965857870015359</v>
+        <v>6.965744978450382</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.966525298676826</v>
+        <v>6.966416289930455</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.946175814213898</v>
+        <v>6.946041249947042</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.896881186113738</v>
+        <v>6.896808484812041</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860279172520528</v>
+        <v>6.860203405513856</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846220841751499</v>
+        <v>6.846159817897146</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825016150793967</v>
+        <v>6.825074859114146</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.844003321310247</v>
+        <v>6.844078381303601</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.859783990978082</v>
+        <v>6.85993631363106</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889422430487429</v>
+        <v>6.889495976370961</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.89132501290446</v>
+        <v>6.891372696319782</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.879480450734016</v>
+        <v>6.879563122291138</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.870911191456836</v>
+        <v>6.870853799799268</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845435489665354</v>
+        <v>6.845403237891473</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.840987035730945</v>
+        <v>6.840932852352929</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.809028183469248</v>
+        <v>6.809104567543406</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823841078019242</v>
+        <v>6.823833595466775</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817737142325435</v>
+        <v>6.817675492275287</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812229947620358</v>
+        <v>6.812159663866231</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806031925197024</v>
+        <v>6.805952006507062</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.801523013158378</v>
+        <v>6.801437435732771</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.799719921424269</v>
+        <v>6.799630262147815</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782941016333716</v>
+        <v>6.782906826483964</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783045193800314</v>
+        <v>6.782987725002817</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775092553118836</v>
+        <v>6.775070895350792</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.7722166696633</v>
+        <v>6.771944182983384</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.77026331139735</v>
+        <v>6.769874046777506</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.768929471036222</v>
+        <v>6.768601957473096</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.763050384915033</v>
+        <v>6.763083944253191</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.754466659290552</v>
+        <v>6.753180236229908</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.74817666687046</v>
+        <v>6.745926608221003</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.743584540746298</v>
+        <v>6.740580472481774</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.74085786302032</v>
+        <v>6.737683972002597</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.746761206329675</v>
+        <v>6.743306140344086</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.758226170703281</v>
+        <v>6.757264726531081</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.748538750198872</v>
+        <v>6.749606647938372</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.738495111685594</v>
+        <v>6.742290556405575</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.711687606192694</v>
+        <v>6.718188616114019</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.618527442962996</v>
+        <v>6.623177368815101</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.606498110605967</v>
+        <v>6.637992665352334</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141635402830802</v>
+        <v>7.141618641592739</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151881586861435</v>
+        <v>7.151853660723572</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155389004501604</v>
+        <v>7.155361714273941</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168780631653663</v>
+        <v>7.168750065391002</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183728815469612</v>
+        <v>7.183699823213901</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195660610046541</v>
+        <v>7.195633605760412</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197921858600342</v>
+        <v>7.197897437456887</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192437729565246</v>
+        <v>7.192416124525375</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175363561255236</v>
+        <v>7.175376880282931</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180035474816002</v>
+        <v>7.180066520775197</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184091819499237</v>
+        <v>7.184120924283039</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.18919532029702</v>
+        <v>7.189224058206045</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18275705301499</v>
+        <v>7.182808902253836</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181838133572333</v>
+        <v>7.181898385254104</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183009098582777</v>
+        <v>7.183059483545708</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168357780689218</v>
+        <v>7.168402304550358</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154755880481958</v>
+        <v>7.154821695916347</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147481342305273</v>
+        <v>7.147556436623591</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143134520998894</v>
+        <v>7.143227509032885</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123353214254058</v>
+        <v>7.123430099369014</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110500120213564</v>
+        <v>7.110602908241145</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.101792565759158</v>
+        <v>7.1019080436966</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.07392652509149</v>
+        <v>7.074054397203735</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049294892158693</v>
+        <v>7.049425941133746</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047564351496508</v>
+        <v>7.047704046227137</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.045745434190237</v>
+        <v>7.045920382765168</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.052284589625071</v>
+        <v>7.052500568705497</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.057014240961642</v>
+        <v>7.057314285483946</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.012730994559426</v>
+        <v>7.013007476434147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.965744978450382</v>
+        <v>6.965967165453717</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.966416289930455</v>
+        <v>6.966630899489475</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.946041249947042</v>
+        <v>6.946306393659611</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.896808484812041</v>
+        <v>6.896951790647295</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860203405513856</v>
+        <v>6.860352780652958</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846159817897146</v>
+        <v>6.846280265313501</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.825074859114146</v>
+        <v>6.824959442429337</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.844078381303601</v>
+        <v>6.843930765562444</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.85993631363106</v>
+        <v>6.859636400210173</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889495976370961</v>
+        <v>6.889351159964026</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891372696319782</v>
+        <v>6.8912786909126</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.879563122291138</v>
+        <v>6.879400159302325</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.870853799799268</v>
+        <v>6.870966806150103</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845403237891473</v>
+        <v>6.84546680107826</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.840932852352929</v>
+        <v>6.841039625678089</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.809104567543406</v>
+        <v>6.808953949089517</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823833595466775</v>
+        <v>6.823848195101263</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817675492275287</v>
+        <v>6.817796730276079</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812159663866231</v>
+        <v>6.81229789461349</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.805952006507062</v>
+        <v>6.806109245838769</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.801437435732771</v>
+        <v>6.801605889579514</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.799630262147815</v>
+        <v>6.799806875515601</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782906826483964</v>
+        <v>6.782974130985699</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.782987725002817</v>
+        <v>6.783101001610995</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775070895350792</v>
+        <v>6.775113696570672</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771944182983384</v>
+        <v>6.772218304488305</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.769874046777506</v>
+        <v>6.769100108572355</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.768601957473096</v>
+        <v>6.76722794158244</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.763083944253191</v>
+        <v>6.760986619236439</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.753180236229908</v>
+        <v>6.751218124523785</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.745926608221003</v>
+        <v>6.743350881816802</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.740580472481774</v>
+        <v>6.73754108724955</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.737683972002597</v>
+        <v>6.734277407432591</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.743306140344086</v>
+        <v>6.738969976950079</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.757264726531081</v>
+        <v>6.748277776150754</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.749606647938372</v>
+        <v>6.736317622434525</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.742290556405575</v>
+        <v>6.725486875379938</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.718188616114019</v>
+        <v>6.698568480711561</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.623177368815101</v>
+        <v>6.608804356539269</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.637992665352334</v>
+        <v>6.581829617478397</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141618641592739</v>
+        <v>7.141610659948047</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151853660723572</v>
+        <v>7.151840359479567</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155361714273941</v>
+        <v>7.155348709539897</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168750065391002</v>
+        <v>7.168735498359245</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183699823213901</v>
+        <v>7.183686007001241</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195633605760412</v>
+        <v>7.19562073755571</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197897437456887</v>
+        <v>7.197885800306576</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192416124525375</v>
+        <v>7.192405829109709</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175376880282931</v>
+        <v>7.175383198135946</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180066520775197</v>
+        <v>7.180081298491394</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184120924283039</v>
+        <v>7.184134778881404</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189224058206045</v>
+        <v>7.189237738794096</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182808902253836</v>
+        <v>7.182833586337045</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181898385254104</v>
+        <v>7.181927078303238</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183059483545708</v>
+        <v>7.183083477400411</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168402304550358</v>
+        <v>7.168423487556137</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154821695916347</v>
+        <v>7.154853019722108</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147556436623591</v>
+        <v>7.147592180422579</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143227509032885</v>
+        <v>7.143271789722618</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123430099369014</v>
+        <v>7.123466687249786</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110602908241145</v>
+        <v>7.110651871985956</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.1019080436966</v>
+        <v>7.101963087098582</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074054397203735</v>
+        <v>7.07411540244048</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049425941133746</v>
+        <v>7.049488465725545</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047704046227137</v>
+        <v>7.047770669939471</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.045920382765168</v>
+        <v>7.046003753946668</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.052500568705497</v>
+        <v>7.052603458339918</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.057314285483946</v>
+        <v>7.057457185475148</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.013007476434147</v>
+        <v>7.013139073739537</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.965967165453717</v>
+        <v>6.966073032865427</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.966630899489475</v>
+        <v>6.966733248547376</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.946306393659611</v>
+        <v>6.946433161114815</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.896951790647295</v>
+        <v>6.897020386594976</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860352780652958</v>
+        <v>6.860424319397789</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846280265313501</v>
+        <v>6.846338147709876</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824959442429337</v>
+        <v>6.824904634411538</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843930765562444</v>
+        <v>6.843860591699844</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.859636400210173</v>
+        <v>6.859493325110133</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889351159964026</v>
+        <v>6.889282061311016</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.8912786909126</v>
+        <v>6.891233674059407</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.879400159302325</v>
+        <v>6.879322148088011</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.870966806150103</v>
+        <v>6.871020725067618</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.84546680107826</v>
+        <v>6.845497212454996</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841039625678089</v>
+        <v>6.841090691303551</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808953949089517</v>
+        <v>6.808881776714572</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823848195101263</v>
+        <v>6.823854969582568</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817796730276079</v>
+        <v>6.817854357137894</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.81229789461349</v>
+        <v>6.812363618556042</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806109245838769</v>
+        <v>6.806184092249012</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.801605889579514</v>
+        <v>6.801686190069066</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.799806875515601</v>
+        <v>6.79989124396007</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.782974130985699</v>
+        <v>6.783006219789758</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783101001610995</v>
+        <v>6.783155218179052</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775113696570672</v>
+        <v>6.775134341947394</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772218304488305</v>
+        <v>6.77222000386196</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.769100108572355</v>
+        <v>6.768130802890142</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.76722794158244</v>
+        <v>6.765754308028556</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.760986619236439</v>
+        <v>6.759171836104841</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.751218124523785</v>
+        <v>6.748313354301271</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.743350881816802</v>
+        <v>6.739273454284464</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.73754108724955</v>
+        <v>6.732373230297773</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.734277407432591</v>
+        <v>6.72836893215487</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.738969976950079</v>
+        <v>6.732015258741915</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.748277776150754</v>
+        <v>6.739540820012043</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.736317622434525</v>
+        <v>6.725660928392745</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.725486875379938</v>
+        <v>6.714308823152444</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.698568480711561</v>
+        <v>6.687597063595209</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.608804356539269</v>
+        <v>6.601817815740558</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.581829617478397</v>
+        <v>6.571516410245268</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.77222000386196</v>
+        <v>6.77195449092779</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768130802890142</v>
+        <v>6.767738069848409</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.765754308028556</v>
+        <v>6.765243751217909</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.759171836104841</v>
+        <v>6.759335101063056</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.748313354301271</v>
+        <v>6.748286638345425</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.739273454284464</v>
+        <v>6.738189557847722</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.732373230297773</v>
+        <v>6.730808288212078</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.72836893215487</v>
+        <v>6.726383159796193</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.732015258741915</v>
+        <v>6.729452378953793</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.739540820012043</v>
+        <v>6.73782959236768</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.725660928392745</v>
+        <v>6.726169632452323</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.714308823152444</v>
+        <v>6.716304173166955</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.687597063595209</v>
+        <v>6.694096865651241</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.601817815740558</v>
+        <v>6.619267016167095</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,15 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.571516410245268</v>
+        <v>6.626781506768622</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B111">
+        <v>6.671144006768622</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141610659948047</v>
+        <v>7.141602927667885</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151840359479567</v>
+        <v>7.151827472007025</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155348709539897</v>
+        <v>7.155336105434768</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168735498359245</v>
+        <v>7.168721379376223</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183686007001241</v>
+        <v>7.183672616168422</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19562073755571</v>
+        <v>7.195608265938886</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197885800306576</v>
+        <v>7.19787452187936</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192405829109709</v>
+        <v>7.192395850937407</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175383198135946</v>
+        <v>7.175389303447605</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180081298491394</v>
+        <v>7.180095610656837</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184134778881404</v>
+        <v>7.18414819754725</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189237738794096</v>
+        <v>7.189250989313393</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182833586337045</v>
+        <v>7.182857495302423</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181927078303238</v>
+        <v>7.181954875731683</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183083477400411</v>
+        <v>7.183106722045314</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168423487556137</v>
+        <v>7.168443996966199</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154853019722108</v>
+        <v>7.154883354190858</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147592180422579</v>
+        <v>7.147626797616632</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143271789722618</v>
+        <v>7.143314686946574</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123466687249786</v>
+        <v>7.123502116841274</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110651871985956</v>
+        <v>7.110699315902005</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.101963087098582</v>
+        <v>7.102016443294229</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.07411540244048</v>
+        <v>7.074174571083438</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049488465725545</v>
+        <v>7.049549110260212</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047770669939471</v>
+        <v>7.047835274447104</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046003753946668</v>
+        <v>7.046084557792925</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.052603458339918</v>
+        <v>7.052703158233749</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.057457185475148</v>
+        <v>7.057595632139948</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.013139073739537</v>
+        <v>7.013266520434279</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.966073032865427</v>
+        <v>6.96617563009735</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.966733248547376</v>
+        <v>6.966832492703318</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.946433161114815</v>
+        <v>6.946556279658727</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897020386594976</v>
+        <v>6.897087057342955</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860424319397789</v>
+        <v>6.86049387346058</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846338147709876</v>
+        <v>6.84639454540574</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824904634411538</v>
+        <v>6.824851633589745</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843860591699844</v>
+        <v>6.843792685154168</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.859493325110133</v>
+        <v>6.859354562380997</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889282061311016</v>
+        <v>6.889215037190338</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891233674059407</v>
+        <v>6.891189909039038</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.879322148088011</v>
+        <v>6.879246322603944</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871020725067618</v>
+        <v>6.871073024530414</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845497212454996</v>
+        <v>6.845526761859025</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841090691303551</v>
+        <v>6.841140297784827</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808881776714572</v>
+        <v>6.808811583240884</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823854969582568</v>
+        <v>6.823861422589808</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817854357137894</v>
+        <v>6.817910117473386</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812363618556042</v>
+        <v>6.812427225951799</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806184092249012</v>
+        <v>6.806256580549861</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.801686190069066</v>
+        <v>6.801764032144888</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.79989124396007</v>
+        <v>6.799973139423385</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783006219789758</v>
+        <v>6.783037329157408</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783155218179052</v>
+        <v>6.783207909479676</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775134341947394</v>
+        <v>6.775154504953565</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.77195449092779</v>
+        <v>6.772221760315542</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.767738069848409</v>
+        <v>6.768139256998399</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.765243751217909</v>
+        <v>6.765342187709274</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.759335101063056</v>
+        <v>6.758744519804778</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.748286638345425</v>
+        <v>6.748006736385856</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.738189557847722</v>
+        <v>6.737728790771695</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.730808288212078</v>
+        <v>6.730016582659531</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.726383159796193</v>
+        <v>6.725074259255791</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.729452378953793</v>
+        <v>6.727646678677815</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.73782959236768</v>
+        <v>6.733474546455378</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.726169632452323</v>
+        <v>6.719188890315268</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.716304173166955</v>
+        <v>6.705097914136507</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.694096865651241</v>
+        <v>6.677916218271538</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.619267016167095</v>
+        <v>6.594983219658128</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.626781506768622</v>
+        <v>6.561462777756533</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.671144006768622</v>
+        <v>6.518294195333607</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772221760315542</v>
+        <v>6.771957950124616</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768139256998399</v>
+        <v>6.767747701895344</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.765342187709274</v>
+        <v>6.764858498059061</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.758744519804778</v>
+        <v>6.759090685146539</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.748006736385856</v>
+        <v>6.748334032658473</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.737728790771695</v>
+        <v>6.737667802934785</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.730016582659531</v>
+        <v>6.730133124423534</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.725074259255791</v>
+        <v>6.725509896144125</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.727646678677815</v>
+        <v>6.728035907160316</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.733474546455378</v>
+        <v>6.735256828883932</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.719188890315268</v>
+        <v>6.723424139028118</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.705097914136507</v>
+        <v>6.712149338943238</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.677916218271538</v>
+        <v>6.690560845382824</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.594983219658128</v>
+        <v>6.622116233777685</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.561462777756533</v>
+        <v>6.631475698424809</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.518294195333607</v>
+        <v>6.674769565632866</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141602927667885</v>
+        <v>7.141595433246842</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151827472007025</v>
+        <v>7.151814979297773</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155336105434768</v>
+        <v>7.155323883734534</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168721379376223</v>
+        <v>7.168707688093967</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183672616168422</v>
+        <v>7.183659631377193</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195608265938886</v>
+        <v>7.195596172862123</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.19787452187936</v>
+        <v>7.197863585846676</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192395850937407</v>
+        <v>7.192386175572948</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175389303447605</v>
+        <v>7.175395206707492</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180095610656837</v>
+        <v>7.180109478921892</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.18414819754725</v>
+        <v>7.184161200529523</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189250989313393</v>
+        <v>7.189263829723039</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182857495302423</v>
+        <v>7.18288066507445</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181954875731683</v>
+        <v>7.181981818792961</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183106722045314</v>
+        <v>7.183129252014393</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168443996966199</v>
+        <v>7.168463864371036</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154883354190858</v>
+        <v>7.154912745403285</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147626797616632</v>
+        <v>7.14766034054813</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143314686946574</v>
+        <v>7.143356264470254</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123502116841274</v>
+        <v>7.123536442211212</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110699315902005</v>
+        <v>7.110745309526095</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102016443294229</v>
+        <v>7.102068188480448</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074174571083438</v>
+        <v>7.074231984613453</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049549110260212</v>
+        <v>7.049607958027549</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047835274447104</v>
+        <v>7.047897949941568</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046084557792925</v>
+        <v>7.046162910841783</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.052703158233749</v>
+        <v>7.052799814068983</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.057595632139948</v>
+        <v>7.057729829772612</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.013266520434279</v>
+        <v>7.013390009263119</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.96617563009735</v>
+        <v>6.966275105508444</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.966832492703318</v>
+        <v>6.966928770164104</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.946556279658727</v>
+        <v>6.946675903289369</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897087057342955</v>
+        <v>6.897151881796487</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.86049387346058</v>
+        <v>6.860561523072954</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.84639454540574</v>
+        <v>6.846449512332729</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824851633589745</v>
+        <v>6.824800352759413</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843792685154168</v>
+        <v>6.84372693854232</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.859354562380997</v>
+        <v>6.859219920699314</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889215037190338</v>
+        <v>6.889149995967536</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891189909039038</v>
+        <v>6.891147345337033</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.879246322603944</v>
+        <v>6.879172593428855</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871073024530414</v>
+        <v>6.871123776351149</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845526761859025</v>
+        <v>6.845555485247997</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841140297784827</v>
+        <v>6.841188506642975</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808811583240884</v>
+        <v>6.808743289864994</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823861422589808</v>
+        <v>6.823867573662614</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817910117473386</v>
+        <v>6.817964099900266</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812427225951799</v>
+        <v>6.812488816656086</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806256580549861</v>
+        <v>6.806326819753711</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.801764032144888</v>
+        <v>6.801839526328012</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.799973139423385</v>
+        <v>6.800052668180239</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783037329157408</v>
+        <v>6.783067502774506</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783207909479676</v>
+        <v>6.78325913796352</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775154504953565</v>
+        <v>6.775174200764784</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771957950124616</v>
+        <v>6.772223567052556</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.767747701895344</v>
+        <v>6.768147421016526</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.764858498059061</v>
+        <v>6.764962759560502</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.759090685146539</v>
+        <v>6.758349934393289</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.748334032658473</v>
+        <v>6.74774379778963</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.737667802934785</v>
+        <v>6.736385604648958</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.730133124423534</v>
+        <v>6.727710131061977</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.725509896144125</v>
+        <v>6.722131659767911</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.728035907160316</v>
+        <v>6.723741732848056</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.735256828883932</v>
+        <v>6.72809177845035</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.723424139028118</v>
+        <v>6.713476562107045</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.712149338943238</v>
+        <v>6.696999553139666</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.690560845382824</v>
+        <v>6.669521227742176</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.622116233777685</v>
+        <v>6.589524918939489</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.631475698424809</v>
+        <v>6.555162920919726</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.674769565632866</v>
+        <v>6.519374577608913</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772223567052556</v>
+        <v>6.771961412292813</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768147421016526</v>
+        <v>6.767757010407788</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.764962759560502</v>
+        <v>6.764001478021442</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.758349934393289</v>
+        <v>6.758251613085926</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.74774379778963</v>
+        <v>6.747683663330589</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.736385604648958</v>
+        <v>6.736428386763964</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.727710131061977</v>
+        <v>6.728640177134579</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.722131659767911</v>
+        <v>6.723851939668656</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.723741732848056</v>
+        <v>6.72581744785105</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.72809177845035</v>
+        <v>6.731894467345979</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.713476562107045</v>
+        <v>6.719869040319374</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.696999553139666</v>
+        <v>6.707288375661223</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.669521227742176</v>
+        <v>6.68617028473596</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.589524918939489</v>
+        <v>6.622664808724377</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.555162920919726</v>
+        <v>6.632310081302118</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.519374577608913</v>
+        <v>6.667802144791306</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141595433246842</v>
+        <v>7.141588165876521</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151814979297773</v>
+        <v>7.151802863490162</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155323883734534</v>
+        <v>7.155312027303504</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168707688093967</v>
+        <v>7.168694405377648</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183659631377193</v>
+        <v>7.183647034443452</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195596172862123</v>
+        <v>7.195584441355868</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197863585846676</v>
+        <v>7.197852976855765</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192386175572948</v>
+        <v>7.192376789443228</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175395206707492</v>
+        <v>7.17540091772929</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180109478921892</v>
+        <v>7.180122923615441</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184161200529523</v>
+        <v>7.184173806842633</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189263829723039</v>
+        <v>7.189276278766304</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18288066507445</v>
+        <v>7.182903129392622</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.181981818792961</v>
+        <v>7.18200794624742</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183129252014393</v>
+        <v>7.183151099752383</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168463864371036</v>
+        <v>7.168483119418235</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154912745403285</v>
+        <v>7.154941236625671</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.14766034054813</v>
+        <v>7.147692858372007</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143356264470254</v>
+        <v>7.143396582204065</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123536442211212</v>
+        <v>7.123569714118346</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110745309526095</v>
+        <v>7.110789918225234</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102068188480448</v>
+        <v>7.102118394346253</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074231984613453</v>
+        <v>7.074287719775283</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049607958027549</v>
+        <v>7.049665087484151</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047897949941568</v>
+        <v>7.047958781335613</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046162910841783</v>
+        <v>7.04623892269772</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.052799814068983</v>
+        <v>7.052893562811794</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.057729829772612</v>
+        <v>7.057859970400083</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.013390009263119</v>
+        <v>7.013509721252123</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.966275105508444</v>
+        <v>6.966371598667877</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.966928770164104</v>
+        <v>6.967022211112598</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.946675903289369</v>
+        <v>6.946792177540016</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897151881796487</v>
+        <v>6.897214934671215</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860561523072954</v>
+        <v>6.860627344277186</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846449512332729</v>
+        <v>6.846503100012152</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824800352759413</v>
+        <v>6.82475071019826</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.84372693854232</v>
+        <v>6.843663251115056</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.859219920699314</v>
+        <v>6.859089219850096</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889149995967536</v>
+        <v>6.889086851302102</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891147345337033</v>
+        <v>6.891105935056045</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.879172593428855</v>
+        <v>6.879100875879066</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871123776351149</v>
+        <v>6.871173048161906</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845555485247997</v>
+        <v>6.845583416616671</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841188506642975</v>
+        <v>6.841235375995073</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808743289864994</v>
+        <v>6.80867682181762</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823867573662614</v>
+        <v>6.82387344089368</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.817964099900266</v>
+        <v>6.818016387548661</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812488816656086</v>
+        <v>6.812548484383183</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806326819753711</v>
+        <v>6.806394912295923</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.801839526328012</v>
+        <v>6.801912776652408</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800052668180239</v>
+        <v>6.800129930556417</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783067502774506</v>
+        <v>6.783096781795964</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.78325913796352</v>
+        <v>6.783308962783024</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775174200764784</v>
+        <v>6.775193444037331</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771961412292813</v>
+        <v>6.772225417886096</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.767757010407788</v>
+        <v>6.768155309978793</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.764001478021442</v>
+        <v>6.764122638198595</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.758251613085926</v>
+        <v>6.757365851681653</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.747683663330589</v>
+        <v>6.746804187473272</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.736428386763964</v>
+        <v>6.734393387318732</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.728640177134579</v>
+        <v>6.72475189715523</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.723851939668656</v>
+        <v>6.718515015800534</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.72581744785105</v>
+        <v>6.719138454881967</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.731894467345979</v>
+        <v>6.72199148042524</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.719869040319374</v>
+        <v>6.706958565915782</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.707288375661223</v>
+        <v>6.688103496539044</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.68617028473596</v>
+        <v>6.660182770429754</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.622664808724377</v>
+        <v>6.582204055168858</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.632310081302118</v>
+        <v>6.54568466756753</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.667802144791306</v>
+        <v>6.507904709351322</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772225417886096</v>
+        <v>6.77196487306794</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768155309978793</v>
+        <v>6.767766011815112</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.764122638198595</v>
+        <v>6.763235058634756</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.757365851681653</v>
+        <v>6.757511135528171</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.746804187473272</v>
+        <v>6.747139776363338</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.734393387318732</v>
+        <v>6.735324403104862</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.72475189715523</v>
+        <v>6.727284654965096</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.718515015800534</v>
+        <v>6.722322243874197</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.719138454881967</v>
+        <v>6.723754384395267</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.72199148042524</v>
+        <v>6.728783069402573</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.706958565915782</v>
+        <v>6.716573207245215</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.688103496539044</v>
+        <v>6.702787070910234</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.660182770429754</v>
+        <v>6.682079826623334</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.582204055168858</v>
+        <v>6.622756692168023</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.54568466756753</v>
+        <v>6.632230289553955</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.507904709351322</v>
+        <v>6.662227181438876</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141588165876521</v>
+        <v>7.141574272232239</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151802863490162</v>
+        <v>7.151779696362518</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155312027303504</v>
+        <v>7.155289346674776</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168694405377648</v>
+        <v>7.168668994642705</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183647034443452</v>
+        <v>7.183622936681354</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195584441355868</v>
+        <v>7.195562000099049</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197852976855765</v>
+        <v>7.197832683042771</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192376789443228</v>
+        <v>7.192358834532558</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.17540091772929</v>
+        <v>7.175411799249036</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180122923615441</v>
+        <v>7.180148617582919</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184173806842633</v>
+        <v>7.184197899893936</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189276278766304</v>
+        <v>7.189300072186485</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182903129392622</v>
+        <v>7.182946066667189</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.18200794624742</v>
+        <v>7.182057898007397</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183151099752383</v>
+        <v>7.183192868787471</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168483119418235</v>
+        <v>7.168519902184224</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154941236625671</v>
+        <v>7.154995679342894</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147692858372007</v>
+        <v>7.147755000789849</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143396582204065</v>
+        <v>7.14347366036314</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123569714118346</v>
+        <v>7.123633285506065</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110789918225234</v>
+        <v>7.110875223284914</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102118394346253</v>
+        <v>7.102214454270838</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074287719775283</v>
+        <v>7.074394440293535</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049665087484151</v>
+        <v>7.049774483163301</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.047958781335613</v>
+        <v>7.048075227325054</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.04623892269772</v>
+        <v>7.046384329580137</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.052893562811794</v>
+        <v>7.053072847093588</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.057859970400083</v>
+        <v>7.058108792757469</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.013509721252123</v>
+        <v>7.013738485393539</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.966371598667877</v>
+        <v>6.966556156331491</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967022211112598</v>
+        <v>6.967201067454473</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.946792177540016</v>
+        <v>6.94701522107155</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897214934671215</v>
+        <v>6.897336005195004</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860627344277186</v>
+        <v>6.860753786247137</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846503100012152</v>
+        <v>6.846606332364927</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.82475071019826</v>
+        <v>6.82465603791487</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843663251115056</v>
+        <v>6.843541681021484</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.859089219850096</v>
+        <v>6.858838970649291</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889086851302102</v>
+        <v>6.888965930532092</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891105935056045</v>
+        <v>6.891026395292593</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.879100875879066</v>
+        <v>6.878963158808805</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871173048161906</v>
+        <v>6.871267403151397</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845583416616671</v>
+        <v>6.845637030236305</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841235375995073</v>
+        <v>6.841325313001978</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.80867682181762</v>
+        <v>6.808549081335879</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.82387344089368</v>
+        <v>6.823884389709615</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818016387548661</v>
+        <v>6.818116186050736</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812548484383183</v>
+        <v>6.812662397788467</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806394912295923</v>
+        <v>6.806525037124111</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.801912776652408</v>
+        <v>6.802052932183061</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800129930556417</v>
+        <v>6.800278030130876</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783096781795964</v>
+        <v>6.783152809073155</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783308962783024</v>
+        <v>6.783404622790658</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775193444037331</v>
+        <v>6.775230629063598</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.77196487306794</v>
+        <v>6.772229229810669</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.767766011815112</v>
+        <v>6.768170317812695</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.763235058634756</v>
+        <v>6.762672099504449</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.757511135528171</v>
+        <v>6.75570672825644</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.747139776363338</v>
+        <v>6.745308644788658</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.735324403104862</v>
+        <v>6.731472326384829</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.727284654965096</v>
+        <v>6.720042435280389</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.722322243874197</v>
+        <v>6.71259353557431</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.723754384395267</v>
+        <v>6.711537704797107</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.728783069402573</v>
+        <v>6.712005982895812</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.716573207245215</v>
+        <v>6.696505860915678</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.702787070910234</v>
+        <v>6.67425740146243</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.682079826623334</v>
+        <v>6.646479732102245</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.622756692168023</v>
+        <v>6.574142203516111</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.632230289553955</v>
+        <v>6.539527949263502</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.662227181438876</v>
+        <v>6.510671605247788</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141574272232239</v>
+        <v>7.141581115393567</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151779696362518</v>
+        <v>7.15179110778393</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155289346674776</v>
+        <v>7.155300520014292</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168668994642705</v>
+        <v>7.168681513216539</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183622936681354</v>
+        <v>7.183634808252448</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195562000099049</v>
+        <v>7.195573055449524</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197832683042771</v>
+        <v>7.197842680457887</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192358834532558</v>
+        <v>7.192367679774116</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175411799249036</v>
+        <v>7.175406445704134</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180148617582919</v>
+        <v>7.180135963844145</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184197899893936</v>
+        <v>7.184186034359087</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189300072186485</v>
+        <v>7.189288354061781</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182946066667189</v>
+        <v>7.182924919974976</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182057898007397</v>
+        <v>7.182033294547606</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183192868787471</v>
+        <v>7.183172295770327</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168519902184224</v>
+        <v>7.168501789959451</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.154995679342894</v>
+        <v>7.15496886852126</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147755000789849</v>
+        <v>7.147724397294337</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.14347366036314</v>
+        <v>7.143435696489996</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123633285506065</v>
+        <v>7.123601980261417</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110875223284914</v>
+        <v>7.110833203503956</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102214454270838</v>
+        <v>7.10216712840039</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074394440293535</v>
+        <v>7.074341848915768</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049774483163301</v>
+        <v>7.049720572597867</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048075227325054</v>
+        <v>7.04801784864283</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046384329580137</v>
+        <v>7.046312696538845</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053072847093588</v>
+        <v>7.052984533353099</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.058108792757469</v>
+        <v>7.057986234686224</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.013738485393539</v>
+        <v>7.013625826583521</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.966556156331491</v>
+        <v>6.966465240992759</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967201067454473</v>
+        <v>6.9671129382773</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.94701522107155</v>
+        <v>6.946905240046759</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897336005195004</v>
+        <v>6.897276286762542</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860753786247137</v>
+        <v>6.860691409189972</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846606332364927</v>
+        <v>6.84655535767302</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.82465603791487</v>
+        <v>6.824702629244786</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843541681021484</v>
+        <v>6.843601528255368</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.858838970649291</v>
+        <v>6.858962289935397</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888965930532092</v>
+        <v>6.889025521772439</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891026395292593</v>
+        <v>6.891065632753827</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878963158808805</v>
+        <v>6.879031089704771</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871267403151397</v>
+        <v>6.871220903713839</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845637030236305</v>
+        <v>6.845610588128412</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841325313001978</v>
+        <v>6.841280960786071</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808549081335879</v>
+        <v>6.808612108116407</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823884389709615</v>
+        <v>6.823879041054673</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818116186050736</v>
+        <v>6.818067058476977</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812662397788467</v>
+        <v>6.812606317168258</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806525037124111</v>
+        <v>6.806460954520587</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802052932183061</v>
+        <v>6.801983881131128</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800278030130876</v>
+        <v>6.800205021335127</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783152809073155</v>
+        <v>6.783125205024247</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783404622790658</v>
+        <v>6.783357440002128</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775230629063598</v>
+        <v>6.775212248919407</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772229229810669</v>
+        <v>6.77196832855458</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768170317812695</v>
+        <v>6.767774721440865</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762672099504449</v>
+        <v>6.762291349532736</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.75570672825644</v>
+        <v>6.756544228842869</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.745308644788658</v>
+        <v>6.746344479168953</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.731472326384829</v>
+        <v>6.734201840156375</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.720042435280389</v>
+        <v>6.725905523199476</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.71259353557431</v>
+        <v>6.720706387105289</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.711537704797107</v>
+        <v>6.72159590044888</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.712005982895812</v>
+        <v>6.725626499259548</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.696505860915678</v>
+        <v>6.713212669222198</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.67425740146243</v>
+        <v>6.698342029727495</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.646479732102245</v>
+        <v>6.678034721546757</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.574142203516111</v>
+        <v>6.622448825218413</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.539527949263502</v>
+        <v>6.631939604361838</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.510671605247788</v>
+        <v>6.65913365330819</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141581115393567</v>
+        <v>7.141567627381137</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.15179110778393</v>
+        <v>7.151768614322132</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155300520014292</v>
+        <v>7.155278492961276</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168681513216539</v>
+        <v>7.168656833656648</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183634808252448</v>
+        <v>7.183611404528458</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195573055449524</v>
+        <v>7.195551261120739</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197842680457887</v>
+        <v>7.197822971778689</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192367679774116</v>
+        <v>7.192350242373602</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175406445704134</v>
+        <v>7.175416986450828</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180135963844145</v>
+        <v>7.180160901757476</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184186034359087</v>
+        <v>7.184209419281798</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189288354061781</v>
+        <v>7.189311448751674</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182924919974976</v>
+        <v>7.182966597578642</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182033294547606</v>
+        <v>7.182081788956432</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183172295770327</v>
+        <v>7.183212845860824</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168501789959451</v>
+        <v>7.168537480742036</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.15496886852126</v>
+        <v>7.155021705108808</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147724397294337</v>
+        <v>7.147784709800486</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143435696489996</v>
+        <v>7.143510523790536</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123601980261417</v>
+        <v>7.123663672091819</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110833203503956</v>
+        <v>7.110916032165394</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.10216712840039</v>
+        <v>7.102260431979021</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074341848915768</v>
+        <v>7.074445558362958</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049720572597867</v>
+        <v>7.04982688509118</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.04801784864283</v>
+        <v>7.048130988610713</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046312696538845</v>
+        <v>7.046453913497277</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.052984533353099</v>
+        <v>7.053158618478745</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.057986234686224</v>
+        <v>7.058227804957749</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.013625826583521</v>
+        <v>7.013847848501003</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.966465240992759</v>
+        <v>6.966644461497982</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.9671129382773</v>
+        <v>6.967286707987332</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.946905240046759</v>
+        <v>6.947122243984714</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897276286762542</v>
+        <v>6.897394153653218</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860691409189972</v>
+        <v>6.860814540430727</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.84655535767302</v>
+        <v>6.846656069065732</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824702629244786</v>
+        <v>6.824610868552524</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843601528255368</v>
+        <v>6.843483625729909</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.858962289935397</v>
+        <v>6.858719110612924</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.889025521772439</v>
+        <v>6.888908004994286</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.891065632753827</v>
+        <v>6.890988181698874</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.879031089704771</v>
+        <v>6.878897010986093</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871220903713839</v>
+        <v>6.871312603263672</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845610588128412</v>
+        <v>6.845662771794829</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841280960786071</v>
+        <v>6.841368481866095</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808612108116407</v>
+        <v>6.808487677393346</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823879041054673</v>
+        <v>6.823889501317106</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818067058476977</v>
+        <v>6.818163839288106</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812606317168258</v>
+        <v>6.812716804147353</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806460954520587</v>
+        <v>6.806587245560805</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.801983881131128</v>
+        <v>6.802120017024141</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800205021335127</v>
+        <v>6.800349041733798</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783125205024247</v>
+        <v>6.783179628518293</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783357440002128</v>
+        <v>6.783450561604667</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775212248919407</v>
+        <v>6.775248597640219</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.77196832855458</v>
+        <v>6.772231181096219</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.767774721440865</v>
+        <v>6.768177461943463</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762291349532736</v>
+        <v>6.761800072074482</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.756544228842869</v>
+        <v>6.754674851578334</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.746344479168953</v>
+        <v>6.744249453109454</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.734201840156375</v>
+        <v>6.729668070455205</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.725905523199476</v>
+        <v>6.717401758205721</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.720706387105289</v>
+        <v>6.709392201793832</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.72159590044888</v>
+        <v>6.707583070038458</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.725626499259548</v>
+        <v>6.707010951335084</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.713212669222198</v>
+        <v>6.691360203460548</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.698342029727495</v>
+        <v>6.667764283018556</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.678034721546757</v>
+        <v>6.640297790743833</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.622448825218413</v>
+        <v>6.570760990248431</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.631939604361838</v>
+        <v>6.537530316994991</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.65913365330819</v>
+        <v>6.511924274239945</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141567627381137</v>
+        <v>7.141561172343613</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151768614322132</v>
+        <v>7.151757847606838</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155278492961276</v>
+        <v>7.155267945357421</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168656833656648</v>
+        <v>7.168645015159205</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183611404528458</v>
+        <v>7.18360019744833</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195551261120739</v>
+        <v>7.195540825130615</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197822971778689</v>
+        <v>7.197813534557578</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192350242373602</v>
+        <v>7.192341892591933</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175416986450828</v>
+        <v>7.175422014906181</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180160901757476</v>
+        <v>7.180172832319744</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184209419281798</v>
+        <v>7.184220607447275</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189311448751674</v>
+        <v>7.18932249847214</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182966597578642</v>
+        <v>7.182986539206812</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182081788956432</v>
+        <v>7.182104997881407</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183212845860824</v>
+        <v>7.183232252503645</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168537480742036</v>
+        <v>7.168554548853766</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155021705108808</v>
+        <v>7.155046979763259</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147784709800486</v>
+        <v>7.147813562916934</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143510523790536</v>
+        <v>7.143546333889661</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123663672091819</v>
+        <v>7.123693179821245</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110916032165394</v>
+        <v>7.110955681652153</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102260431979021</v>
+        <v>7.102305118191137</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074445558362958</v>
+        <v>7.074495264034861</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.04982688509118</v>
+        <v>7.049877840674017</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048130988610713</v>
+        <v>7.048185199786871</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046453913497277</v>
+        <v>7.046521534814874</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053158618478745</v>
+        <v>7.053241955488761</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.058227804957749</v>
+        <v>7.058343422539608</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.013847848501003</v>
+        <v>7.013954058073569</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.966644461497982</v>
+        <v>6.966730266761518</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967286707987332</v>
+        <v>6.967369963206327</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947122243984714</v>
+        <v>6.947226425710491</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897394153653218</v>
+        <v>6.897450792595987</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860814540430727</v>
+        <v>6.860873733479961</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846656069065732</v>
+        <v>6.846704610784202</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824610868552524</v>
+        <v>6.824567057511299</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843483625729909</v>
+        <v>6.843427283574543</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.858719110612924</v>
+        <v>6.858602566763889</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888908004994286</v>
+        <v>6.888851676542061</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890988181698874</v>
+        <v>6.890950953033076</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878897010986093</v>
+        <v>6.878832577682003</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871312603263672</v>
+        <v>6.871356557714985</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845662771794829</v>
+        <v>6.84568784016292</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841368481866095</v>
+        <v>6.84141051401985</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808487677393346</v>
+        <v>6.808427835349518</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823889501317106</v>
+        <v>6.823894389322653</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818163839288106</v>
+        <v>6.818210083175511</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812716804147353</v>
+        <v>6.812769609626206</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806587245560805</v>
+        <v>6.806647660414209</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802120017024141</v>
+        <v>6.802185218026354</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800349041733798</v>
+        <v>6.800418136427108</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783179628518293</v>
+        <v>6.783205696035441</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783450561604667</v>
+        <v>6.783495304353815</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775248597640219</v>
+        <v>6.77526616735129</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772231181096219</v>
+        <v>6.772233156780318</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768177461943463</v>
+        <v>6.768184381684919</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.761800072074482</v>
+        <v>6.761822405823658</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.754674851578334</v>
+        <v>6.754349967429585</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.744249453109454</v>
+        <v>6.74419264737121</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.729668070455205</v>
+        <v>6.730160683752544</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.717401758205721</v>
+        <v>6.717635026464906</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.709392201793832</v>
+        <v>6.709449837168423</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.707583070038458</v>
+        <v>6.706958138609153</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707010951335084</v>
+        <v>6.705778380059178</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.691360203460548</v>
+        <v>6.690195660698307</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.667764283018556</v>
+        <v>6.667109559737121</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.640297790743833</v>
+        <v>6.639339890447868</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.570760990248431</v>
+        <v>6.573512380940477</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.537530316994991</v>
+        <v>6.543859795951947</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,15 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.511924274239945</v>
+        <v>6.524140014501011</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B112">
+        <v>6.566027514501012</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141561172343613</v>
+        <v>7.141567627381137</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151757847606838</v>
+        <v>7.151768614322132</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155267945357421</v>
+        <v>7.155278492961276</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168645015159205</v>
+        <v>7.168656833656648</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.18360019744833</v>
+        <v>7.183611404528458</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195540825130615</v>
+        <v>7.195551261120739</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197813534557578</v>
+        <v>7.197822971778689</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192341892591933</v>
+        <v>7.192350242373602</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175422014906181</v>
+        <v>7.175416986450828</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180172832319744</v>
+        <v>7.180160901757476</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184220607447275</v>
+        <v>7.184209419281798</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.18932249847214</v>
+        <v>7.189311448751674</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182986539206812</v>
+        <v>7.182966597578642</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182104997881407</v>
+        <v>7.182081788956432</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183232252503645</v>
+        <v>7.183212845860824</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168554548853766</v>
+        <v>7.168537480742036</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155046979763259</v>
+        <v>7.155021705108808</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147813562916934</v>
+        <v>7.147784709800486</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143546333889661</v>
+        <v>7.143510523790536</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123693179821245</v>
+        <v>7.123663672091819</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110955681652153</v>
+        <v>7.110916032165394</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102305118191137</v>
+        <v>7.102260431979021</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074495264034861</v>
+        <v>7.074445558362958</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049877840674017</v>
+        <v>7.04982688509118</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048185199786871</v>
+        <v>7.048130988610713</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046521534814874</v>
+        <v>7.046453913497277</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053241955488761</v>
+        <v>7.053158618478745</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.058343422539608</v>
+        <v>7.058227804957749</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.013954058073569</v>
+        <v>7.013847848501003</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.966730266761518</v>
+        <v>6.966644461497982</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967369963206327</v>
+        <v>6.967286707987332</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947226425710491</v>
+        <v>6.947122243984714</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897450792595987</v>
+        <v>6.897394153653218</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860873733479961</v>
+        <v>6.860814540430727</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846704610784202</v>
+        <v>6.846656069065732</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824567057511299</v>
+        <v>6.824610868552524</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843427283574543</v>
+        <v>6.843483625729909</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.858602566763889</v>
+        <v>6.858719110612924</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888851676542061</v>
+        <v>6.888908004994286</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890950953033076</v>
+        <v>6.890988181698874</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878832577682003</v>
+        <v>6.878897010986093</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871356557714985</v>
+        <v>6.871312603263672</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.84568784016292</v>
+        <v>6.845662771794829</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.84141051401985</v>
+        <v>6.841368481866095</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808427835349518</v>
+        <v>6.808487677393346</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823894389322653</v>
+        <v>6.823889501317106</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818210083175511</v>
+        <v>6.818163839288106</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812769609626206</v>
+        <v>6.812716804147353</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806647660414209</v>
+        <v>6.806587245560805</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802185218026354</v>
+        <v>6.802120017024141</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800418136427108</v>
+        <v>6.800349041733798</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783205696035441</v>
+        <v>6.783179628518293</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783495304353815</v>
+        <v>6.783450561604667</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.77526616735129</v>
+        <v>6.775248597640219</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772233156780318</v>
+        <v>6.771975210150758</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768184381684919</v>
+        <v>6.767791321653488</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.761822405823658</v>
+        <v>6.762329761340206</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.754349967429585</v>
+        <v>6.755733357254099</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.74419264737121</v>
+        <v>6.74615872758417</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.730160683752544</v>
+        <v>6.735393423363746</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.717635026464906</v>
+        <v>6.72824302204308</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.709449837168423</v>
+        <v>6.723106628852289</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.706958138609153</v>
+        <v>6.724784613399146</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.705778380059178</v>
+        <v>6.728231914981563</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.690195660698307</v>
+        <v>6.715817536095472</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.667109559737121</v>
+        <v>6.700714979141697</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.639339890447868</v>
+        <v>6.680128727072741</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.573512380940477</v>
+        <v>6.630654718250488</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.543859795951947</v>
+        <v>6.638552423189021</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.524140014501011</v>
+        <v>6.660170196391963</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.566027514501012</v>
+        <v>6.662420847432549</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141567627381137</v>
+        <v>7.141554899101543</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151768614322132</v>
+        <v>7.151747382949136</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155278492961276</v>
+        <v>7.155257691098061</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168656833656648</v>
+        <v>7.168633524889152</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183611404528458</v>
+        <v>7.183589301892408</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195551261120739</v>
+        <v>7.195530679488875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197822971778689</v>
+        <v>7.197804359944772</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192350242373602</v>
+        <v>7.192333775077435</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175416986450828</v>
+        <v>7.175426891758051</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180160901757476</v>
+        <v>7.180184424316898</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184209419281798</v>
+        <v>7.184231478469387</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189311448751674</v>
+        <v>7.18933323522964</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182966597578642</v>
+        <v>7.183005916551137</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182081788956432</v>
+        <v>7.182127553555443</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183212845860824</v>
+        <v>7.183251112793958</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168537480742036</v>
+        <v>7.168571128413606</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155021705108808</v>
+        <v>7.155071535323543</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147784709800486</v>
+        <v>7.147841596544763</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143510523790536</v>
+        <v>7.143581135128498</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123663672091819</v>
+        <v>7.123721846232995</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110916032165394</v>
+        <v>7.110994220376657</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102260431979021</v>
+        <v>7.102348566448825</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074445558362958</v>
+        <v>7.074543614916091</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.04982688509118</v>
+        <v>7.049927408830357</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048130988610713</v>
+        <v>7.048237924467508</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046453913497277</v>
+        <v>7.046587275262606</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053158618478745</v>
+        <v>7.053322960087703</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.058227804957749</v>
+        <v>7.058455788297733</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.013847848501003</v>
+        <v>7.014057248237778</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.966644461497982</v>
+        <v>6.966813676296466</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967286707987332</v>
+        <v>6.967450930834122</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947122243984714</v>
+        <v>6.947327877138822</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897394153653218</v>
+        <v>6.89750597945492</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860814540430727</v>
+        <v>6.860931424087281</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846656069065732</v>
+        <v>6.846751998657634</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824610868552524</v>
+        <v>6.8245245448633</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843483625729909</v>
+        <v>6.843372580278247</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.858719110612924</v>
+        <v>6.858489203794873</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888908004994286</v>
+        <v>6.888796880261696</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890988181698874</v>
+        <v>6.890914672268043</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878897010986093</v>
+        <v>6.878769793768159</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871312603263672</v>
+        <v>6.871399317256772</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845662771794829</v>
+        <v>6.84571226129923</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841368481866095</v>
+        <v>6.841451453689637</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808487677393346</v>
+        <v>6.808369497222754</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823889501317106</v>
+        <v>6.823899066242141</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818163839288106</v>
+        <v>6.818254978956277</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812716804147353</v>
+        <v>6.812820883405622</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806587245560805</v>
+        <v>6.806706357737454</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802120017024141</v>
+        <v>6.802248613047614</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800349041733798</v>
+        <v>6.800485390280077</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783179628518293</v>
+        <v>6.783231042527928</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783450561604667</v>
+        <v>6.783538896556844</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775248597640219</v>
+        <v>6.775283350444904</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771975210150758</v>
+        <v>6.77223515298237</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.767791321653488</v>
+        <v>6.768191087708566</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762329761340206</v>
+        <v>6.761843995665768</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.755733357254099</v>
+        <v>6.754076517869155</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.74615872758417</v>
+        <v>6.744181978336171</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.735393423363746</v>
+        <v>6.730674412077713</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.72824302204308</v>
+        <v>6.717912819771822</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.723106628852289</v>
+        <v>6.709431686639228</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.724784613399146</v>
+        <v>6.706492813898765</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.728231914981563</v>
+        <v>6.704771533376213</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.715817536095472</v>
+        <v>6.689251463091768</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.700714979141697</v>
+        <v>6.666632514003581</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.680128727072741</v>
+        <v>6.638648229706995</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.630654718250488</v>
+        <v>6.57623972002132</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.638552423189021</v>
+        <v>6.549666858529639</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.660170196391963</v>
+        <v>6.534315030750059</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.662420847432549</v>
+        <v>6.576202530750059</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141554899101543</v>
+        <v>7.141561172343613</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151747382949136</v>
+        <v>7.151757847606838</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155257691098061</v>
+        <v>7.155267945357421</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168633524889152</v>
+        <v>7.168645015159205</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183589301892408</v>
+        <v>7.18360019744833</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195530679488875</v>
+        <v>7.195540825130615</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197804359944772</v>
+        <v>7.197813534557578</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192333775077435</v>
+        <v>7.192341892591933</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175426891758051</v>
+        <v>7.175422014906181</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180184424316898</v>
+        <v>7.180172832319744</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184231478469387</v>
+        <v>7.184220607447275</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.18933323522964</v>
+        <v>7.18932249847214</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183005916551137</v>
+        <v>7.182986539206812</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182127553555443</v>
+        <v>7.182104997881407</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183251112793958</v>
+        <v>7.183232252503645</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168571128413606</v>
+        <v>7.168554548853766</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155071535323543</v>
+        <v>7.155046979763259</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147841596544763</v>
+        <v>7.147813562916934</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143581135128498</v>
+        <v>7.143546333889661</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123721846232995</v>
+        <v>7.123693179821245</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110994220376657</v>
+        <v>7.110955681652153</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102348566448825</v>
+        <v>7.102305118191137</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074543614916091</v>
+        <v>7.074495264034861</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049927408830357</v>
+        <v>7.049877840674017</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048237924467508</v>
+        <v>7.048185199786871</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046587275262606</v>
+        <v>7.046521534814874</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053322960087703</v>
+        <v>7.053241955488761</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.058455788297733</v>
+        <v>7.058343422539608</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.014057248237778</v>
+        <v>7.013954058073569</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.966813676296466</v>
+        <v>6.966730266761518</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967450930834122</v>
+        <v>6.967369963206327</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947327877138822</v>
+        <v>6.947226425710491</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.89750597945492</v>
+        <v>6.897450792595987</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860931424087281</v>
+        <v>6.860873733479961</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846751998657634</v>
+        <v>6.846704610784202</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.8245245448633</v>
+        <v>6.824567057511299</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843372580278247</v>
+        <v>6.843427283574543</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.858489203794873</v>
+        <v>6.858602566763889</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888796880261696</v>
+        <v>6.888851676542061</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890914672268043</v>
+        <v>6.890950953033076</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878769793768159</v>
+        <v>6.878832577682003</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871399317256772</v>
+        <v>6.871356557714985</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.84571226129923</v>
+        <v>6.84568784016292</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841451453689637</v>
+        <v>6.84141051401985</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808369497222754</v>
+        <v>6.808427835349518</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823899066242141</v>
+        <v>6.823894389322653</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818254978956277</v>
+        <v>6.818210083175511</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812820883405622</v>
+        <v>6.812769609626206</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806706357737454</v>
+        <v>6.806647660414209</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802248613047614</v>
+        <v>6.802185218026354</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800485390280077</v>
+        <v>6.800418136427108</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783231042527928</v>
+        <v>6.783205696035441</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783538896556844</v>
+        <v>6.783495304353815</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775283350444904</v>
+        <v>6.77526616735129</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.77223515298237</v>
+        <v>6.771978630418409</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768191087708566</v>
+        <v>6.767799238139279</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.761843995665768</v>
+        <v>6.762347962169354</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.754076517869155</v>
+        <v>6.755225788636888</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.744181978336171</v>
+        <v>6.745812533120665</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.730674412077713</v>
+        <v>6.735575495977002</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.717912819771822</v>
+        <v>6.728537110967967</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.709431686639228</v>
+        <v>6.723214459356166</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.706492813898765</v>
+        <v>6.724911558011878</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.704771533376213</v>
+        <v>6.72787345466323</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.689251463091768</v>
+        <v>6.715394675454386</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.666632514003581</v>
+        <v>6.700187555063158</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.638648229706995</v>
+        <v>6.679202520255691</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.57623972002132</v>
+        <v>6.631873506131183</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.549666858529639</v>
+        <v>6.638619483996614</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.534315030750059</v>
+        <v>6.657019700781541</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.576202530750059</v>
+        <v>6.654346425268539</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141561172343613</v>
+        <v>7.141548800082107</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151757847606838</v>
+        <v>7.15173720781543</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155267945357421</v>
+        <v>7.155247718117831</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168645015159205</v>
+        <v>7.168622349365859</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.18360019744833</v>
+        <v>7.183578705054433</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195540825130615</v>
+        <v>7.195520812248883</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197813534557578</v>
+        <v>7.197795437132825</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192341892591933</v>
+        <v>7.192325880274391</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175422014906181</v>
+        <v>7.175431623728926</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180172832319744</v>
+        <v>7.180195691954574</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184220607447275</v>
+        <v>7.184242045640596</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.18932249847214</v>
+        <v>7.189343672131006</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.182986539206812</v>
+        <v>7.183024753217345</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182104997881407</v>
+        <v>7.182149483156737</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183232252503645</v>
+        <v>7.18326944947403</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168554548853766</v>
+        <v>7.168587240082408</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155046979763259</v>
+        <v>7.155095402014663</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147813562916934</v>
+        <v>7.14786884505671</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143546333889661</v>
+        <v>7.143614969509023</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123693179821245</v>
+        <v>7.123749706760329</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.110955681652153</v>
+        <v>7.11103169429262</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102305118191137</v>
+        <v>7.102390827381086</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074495264034861</v>
+        <v>7.07459066553002</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.049877840674017</v>
+        <v>7.04997564532952</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048185199786871</v>
+        <v>7.048289222840212</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046521534814874</v>
+        <v>7.046651212102203</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053241955488761</v>
+        <v>7.053401728635837</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.058343422539608</v>
+        <v>7.058565037150366</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.013954058073569</v>
+        <v>7.014157545638279</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.966730266761518</v>
+        <v>6.966894788595585</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967369963206327</v>
+        <v>6.967529703358517</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947226425710491</v>
+        <v>6.947426703506284</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897450792595987</v>
+        <v>6.897559768818805</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860873733479961</v>
+        <v>6.860987668080666</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846704610784202</v>
+        <v>6.846798272044678</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824567057511299</v>
+        <v>6.824483274133025</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843427283574543</v>
+        <v>6.843319445773729</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.858602566763889</v>
+        <v>6.858378893637007</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888851676542061</v>
+        <v>6.888743554697184</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890950953033076</v>
+        <v>6.89087930417589</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878832577682003</v>
+        <v>6.878708597334223</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871356557714985</v>
+        <v>6.871440929922427</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.84568784016292</v>
+        <v>6.845736059850181</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.84141051401985</v>
+        <v>6.841491342840898</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808427835349518</v>
+        <v>6.808312607815887</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823894389322653</v>
+        <v>6.823903543737439</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818210083175511</v>
+        <v>6.818298584394936</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812769609626206</v>
+        <v>6.812870690760155</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806647660414209</v>
+        <v>6.806763409365615</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802185218026354</v>
+        <v>6.802310275735179</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800418136427108</v>
+        <v>6.800550875418638</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783205696035441</v>
+        <v>6.783255697244014</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783495304353815</v>
+        <v>6.783581381486087</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.77526616735129</v>
+        <v>6.775300158729837</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771978630418409</v>
+        <v>6.772237166166333</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.767799238139279</v>
+        <v>6.768197590012605</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762347962169354</v>
+        <v>6.761864876657642</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.755225788636888</v>
+        <v>6.753668125508995</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.745812533120665</v>
+        <v>6.743988134792113</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.735575495977002</v>
+        <v>6.730976462823468</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.728537110967967</v>
+        <v>6.717933436108114</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.723214459356166</v>
+        <v>6.70920072858106</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.724911558011878</v>
+        <v>6.705870473828314</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.72787345466323</v>
+        <v>6.703657040715885</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.715394675454386</v>
+        <v>6.688194991559266</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.700187555063158</v>
+        <v>6.665994647421612</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.679202520255691</v>
+        <v>6.637838992388736</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.631873506131183</v>
+        <v>6.57846811299779</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.638619483996614</v>
+        <v>6.554333154670646</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.657019700781541</v>
+        <v>6.541973675826416</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.654346425268539</v>
+        <v>6.590378278515491</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141548800082107</v>
+        <v>7.141542868127301</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.15173720781543</v>
+        <v>7.151727310356005</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155247718117831</v>
+        <v>7.155238015003855</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168622349365859</v>
+        <v>7.168611475836659</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183578705054433</v>
+        <v>7.183568394820323</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195520812248883</v>
+        <v>7.195511212110326</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197795437132825</v>
+        <v>7.197786755899116</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192325880274391</v>
+        <v>7.192318199144029</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175431623728926</v>
+        <v>7.175436217151213</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180195691954574</v>
+        <v>7.180206648654885</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184242045640596</v>
+        <v>7.184252321520969</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189343672131006</v>
+        <v>7.189353821561456</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183024753217345</v>
+        <v>7.183043071513207</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182149483156737</v>
+        <v>7.182170812377482</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.18326944947403</v>
+        <v>7.183287284041697</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168587240082408</v>
+        <v>7.168602903373243</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155095402014663</v>
+        <v>7.155118608392891</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.14786884505671</v>
+        <v>7.147895340932416</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143614969509023</v>
+        <v>7.143647876735655</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123749706760329</v>
+        <v>7.123776794876514</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11103169429262</v>
+        <v>7.111068146857489</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102390827381086</v>
+        <v>7.102431948899242</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.07459066553002</v>
+        <v>7.074636467519612</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.04997564532952</v>
+        <v>7.050022602998721</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048289222840212</v>
+        <v>7.048339151893305</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046651212102203</v>
+        <v>7.046713418428148</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053401728635837</v>
+        <v>7.053478352268569</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.058565037150366</v>
+        <v>7.058671296673546</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.014157545638279</v>
+        <v>7.014255069951162</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.966894788595585</v>
+        <v>6.966973696850332</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967529703358517</v>
+        <v>6.967606368376188</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947426703506284</v>
+        <v>6.947523004748828</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897559768818805</v>
+        <v>6.89761221260494</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860987668080666</v>
+        <v>6.861042518593328</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846798272044678</v>
+        <v>6.846843468613448</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824483274133025</v>
+        <v>6.824443192053646</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843319445773729</v>
+        <v>6.843267813910909</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.858378893637007</v>
+        <v>6.858271514983796</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888743554697184</v>
+        <v>6.888691641623949</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.89087930417589</v>
+        <v>6.890844815222547</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878708597334223</v>
+        <v>6.878648929494416</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871440929922427</v>
+        <v>6.871481441206756</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845736059850181</v>
+        <v>6.845759259231522</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841491342840898</v>
+        <v>6.841530221320557</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808312607815887</v>
+        <v>6.808257114554738</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823903543737439</v>
+        <v>6.823907832684959</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818298584394936</v>
+        <v>6.818340954019563</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812870690760155</v>
+        <v>6.812919093328656</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806763409365615</v>
+        <v>6.806818883202713</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802310275735179</v>
+        <v>6.802370275805051</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800550875418638</v>
+        <v>6.800614660275632</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783255697244014</v>
+        <v>6.783279687885162</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783581381486087</v>
+        <v>6.783622800301862</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775300158729837</v>
+        <v>6.775316603590223</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772237166166333</v>
+        <v>6.772239193110227</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768197590012605</v>
+        <v>6.768203897974274</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.761864876657642</v>
+        <v>6.761885081757082</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.753668125508995</v>
+        <v>6.75321155124114</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.743988134792113</v>
+        <v>6.743719244938844</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.730976462823468</v>
+        <v>6.731169847049213</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.717933436108114</v>
+        <v>6.717678613112355</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.70920072858106</v>
+        <v>6.708711087915785</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.705870473828314</v>
+        <v>6.70500943482242</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.703657040715885</v>
+        <v>6.702318092572144</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.688194991559266</v>
+        <v>6.68689494977764</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.665994647421612</v>
+        <v>6.665059001271699</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.637838992388736</v>
+        <v>6.636669297181585</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.57846811299779</v>
+        <v>6.579903732866594</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.554333154670646</v>
+        <v>6.557516166835589</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.541973675826416</v>
+        <v>6.546925690058472</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.590378278515491</v>
+        <v>6.588085817394314</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141542868127301</v>
+        <v>7.141537096465917</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151727310356005</v>
+        <v>7.151717679359002</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155238015003855</v>
+        <v>7.155228570952236</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168611475836659</v>
+        <v>7.168600892228367</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183568394820323</v>
+        <v>7.183558359722049</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195511212110326</v>
+        <v>7.195501868376095</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197786755899116</v>
+        <v>7.197778306566818</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192318199144029</v>
+        <v>7.192310723130021</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175436217151213</v>
+        <v>7.175440677995025</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180206648654885</v>
+        <v>7.180217307109674</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184252321520969</v>
+        <v>7.184262317987916</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189353821561456</v>
+        <v>7.189363695233569</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183043071513207</v>
+        <v>7.183060892536488</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182170812377482</v>
+        <v>7.182191565523986</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183287284041697</v>
+        <v>7.183304636834288</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168602903373243</v>
+        <v>7.168618136729935</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155118608392891</v>
+        <v>7.155141181459246</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147895340932416</v>
+        <v>7.147921114886808</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143647876735655</v>
+        <v>7.143679894370094</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123776794876514</v>
+        <v>7.123803142228351</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111068146857489</v>
+        <v>7.11110361919941</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102431948899242</v>
+        <v>7.102471976376485</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074636467519612</v>
+        <v>7.074681069834729</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050022602998721</v>
+        <v>7.050068331914042</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048339151893305</v>
+        <v>7.048387765625187</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046713418428148</v>
+        <v>7.046773963444397</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053478352268569</v>
+        <v>7.053552917245117</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.058671296673546</v>
+        <v>7.058774687592564</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.014255069951162</v>
+        <v>7.014349934355685</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.966973696850332</v>
+        <v>6.967050489301149</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967606368376188</v>
+        <v>6.967681008909875</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947523004748828</v>
+        <v>6.947616875828672</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.89761221260494</v>
+        <v>6.897663360218399</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861042518593328</v>
+        <v>6.861096026221711</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846843468613448</v>
+        <v>6.846887624425158</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824443192053646</v>
+        <v>6.824404248343546</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843267813910909</v>
+        <v>6.843217622188257</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.858271514983796</v>
+        <v>6.858166952852061</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888691641623949</v>
+        <v>6.888641085839998</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890844815222547</v>
+        <v>6.890811173469385</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878648929494416</v>
+        <v>6.87859073420757</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871481441206756</v>
+        <v>6.871520894231372</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845759259231522</v>
+        <v>6.845781881703886</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841530221320557</v>
+        <v>6.841568126988854</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808257114554738</v>
+        <v>6.808202967337394</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823907832684959</v>
+        <v>6.823911943237895</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818340954019563</v>
+        <v>6.818382139344222</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812919093328656</v>
+        <v>6.812966149362553</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806818883202713</v>
+        <v>6.806872843485692</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802370275805051</v>
+        <v>6.802428679299552</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800614660275632</v>
+        <v>6.800676809822368</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783279687885162</v>
+        <v>6.783303040706001</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783622800301862</v>
+        <v>6.783663192177553</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775316603590223</v>
+        <v>6.775332696000209</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772239193110227</v>
+        <v>6.772241230878547</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768203897974274</v>
+        <v>6.768210020397389</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.761885081757082</v>
+        <v>6.761904641973525</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.75321155124114</v>
+        <v>6.752784227593532</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.743719244938844</v>
+        <v>6.743499769335</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.731169847049213</v>
+        <v>6.731440920895136</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.717678613112355</v>
+        <v>6.717799400463077</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.708711087915785</v>
+        <v>6.708923063575844</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.70500943482242</v>
+        <v>6.705301255947242</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.702318092572144</v>
+        <v>6.702709096990115</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.68689494977764</v>
+        <v>6.687770907701471</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.665059001271699</v>
+        <v>6.666684112327018</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.636669297181585</v>
+        <v>6.639317825204444</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.579903732866594</v>
+        <v>6.586555604663948</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.557516166835589</v>
+        <v>6.568705502922759</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.546925690058472</v>
+        <v>6.564376236693077</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.588085817394314</v>
+        <v>6.620218195323352</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141537096465917</v>
+        <v>7.141531478687769</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151717679359002</v>
+        <v>7.151708304208079</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155228570952236</v>
+        <v>7.155219375727998</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168600892228367</v>
+        <v>7.168590587102639</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183558359722049</v>
+        <v>7.18354858889515</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195501868376095</v>
+        <v>7.195492770912585</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197778306566818</v>
+        <v>7.197770079968977</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192310723130021</v>
+        <v>7.192303444126742</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175440677995025</v>
+        <v>7.175445011893641</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180217307109674</v>
+        <v>7.180227679329516</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184262317987916</v>
+        <v>7.18427204628194</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189363695233569</v>
+        <v>7.189373304232331</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183060892536488</v>
+        <v>7.183078236255866</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182191565523986</v>
+        <v>7.182211765608838</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183304636834288</v>
+        <v>7.183321527105882</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168618136729935</v>
+        <v>7.168632957599276</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155141181459246</v>
+        <v>7.155163146763854</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147921114886808</v>
+        <v>7.147946195988181</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143679894370094</v>
+        <v>7.143711057973821</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123803142228351</v>
+        <v>7.123828778758951</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11110361919941</v>
+        <v>7.111138150270982</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102471976376485</v>
+        <v>7.102510952813386</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074681069834729</v>
+        <v>7.074724518905023</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050068331914042</v>
+        <v>7.050112879576796</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048387765625187</v>
+        <v>7.048435115237467</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046773963444397</v>
+        <v>7.046832912719421</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053552917245117</v>
+        <v>7.053625505269673</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.058774687592564</v>
+        <v>7.058875324234547</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.014349934355685</v>
+        <v>7.014442245968266</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967050489301149</v>
+        <v>6.967125249560496</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967681008909875</v>
+        <v>6.967753703701364</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947616875828672</v>
+        <v>6.94770840703751</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897663360218399</v>
+        <v>6.897713258700232</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861096026221711</v>
+        <v>6.861148239172752</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846887624425158</v>
+        <v>6.846930774013418</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824404248343546</v>
+        <v>6.824366395501178</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843217622188257</v>
+        <v>6.843168811505832</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.858166952852061</v>
+        <v>6.858065098176487</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888641085839998</v>
+        <v>6.888591834973023</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890811173469385</v>
+        <v>6.890778348481447</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.87859073420757</v>
+        <v>6.878533958109676</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871520894231372</v>
+        <v>6.871559329897369</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845781881703886</v>
+        <v>6.845803948442875</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841568126988854</v>
+        <v>6.841605095841452</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808202967337394</v>
+        <v>6.808150118393488</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823911943237895</v>
+        <v>6.823915884882815</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818382139344222</v>
+        <v>6.818422189073397</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812966149362553</v>
+        <v>6.813011913954202</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806872843485692</v>
+        <v>6.806925351027525</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802428679299552</v>
+        <v>6.802485548824982</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800676809822368</v>
+        <v>6.800737385783156</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783303040706001</v>
+        <v>6.78332578060673</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783663192177553</v>
+        <v>6.783702594416093</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775332696000209</v>
+        <v>6.775348446538452</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772241230878547</v>
+        <v>6.772243276797227</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768210020397389</v>
+        <v>6.768215965555606</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.761904641973525</v>
+        <v>6.761923586506179</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752784227593532</v>
+        <v>6.752411730706446</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.743499769335</v>
+        <v>6.743324447696388</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.731440920895136</v>
+        <v>6.731723917041052</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.717799400463077</v>
+        <v>6.717886585719798</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.708923063575844</v>
+        <v>6.709046230784922</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.705301255947242</v>
+        <v>6.70543573688839</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.702709096990115</v>
+        <v>6.70285341452297</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.687770907701471</v>
+        <v>6.688292747772055</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.666684112327018</v>
+        <v>6.667836750599522</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.639317825204444</v>
+        <v>6.641265442851486</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.586555604663948</v>
+        <v>6.591962164161966</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.568705502922759</v>
+        <v>6.577678790121316</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.564376236693077</v>
+        <v>6.577881996934698</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.620218195323352</v>
+        <v>6.639687250419231</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141531478687769</v>
+        <v>7.141548800082107</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151708304208079</v>
+        <v>7.15173720781543</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155219375727998</v>
+        <v>7.155247718117831</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168590587102639</v>
+        <v>7.168622349365859</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.18354858889515</v>
+        <v>7.183578705054433</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195492770912585</v>
+        <v>7.195520812248883</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197770079968977</v>
+        <v>7.197795437132825</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192303444126742</v>
+        <v>7.192325880274391</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175445011893641</v>
+        <v>7.175431623728926</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180227679329516</v>
+        <v>7.180195691954574</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.18427204628194</v>
+        <v>7.184242045640596</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189373304232331</v>
+        <v>7.189343672131006</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183078236255866</v>
+        <v>7.183024753217345</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182211765608838</v>
+        <v>7.182149483156737</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183321527105882</v>
+        <v>7.18326944947403</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168632957599276</v>
+        <v>7.168587240082408</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155163146763854</v>
+        <v>7.155095402014663</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147946195988181</v>
+        <v>7.14786884505671</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143711057973821</v>
+        <v>7.143614969509023</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123828778758951</v>
+        <v>7.123749706760329</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111138150270982</v>
+        <v>7.11103169429262</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102510952813386</v>
+        <v>7.102390827381086</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074724518905023</v>
+        <v>7.07459066553002</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050112879576796</v>
+        <v>7.04997564532952</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048435115237467</v>
+        <v>7.048289222840212</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046832912719421</v>
+        <v>7.046651212102203</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053625505269673</v>
+        <v>7.053401728635837</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.058875324234547</v>
+        <v>7.058565037150366</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.014442245968266</v>
+        <v>7.014157545638279</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967125249560496</v>
+        <v>6.966894788595585</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967753703701364</v>
+        <v>6.967529703358517</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.94770840703751</v>
+        <v>6.947426703506284</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897713258700232</v>
+        <v>6.897559768818805</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861148239172752</v>
+        <v>6.860987668080666</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846930774013418</v>
+        <v>6.846798272044678</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824366395501178</v>
+        <v>6.824483274133025</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843168811505832</v>
+        <v>6.843319445773729</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.858065098176487</v>
+        <v>6.858378893637007</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888591834973023</v>
+        <v>6.888743554697184</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890778348481447</v>
+        <v>6.89087930417589</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878533958109676</v>
+        <v>6.878708597334223</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871559329897369</v>
+        <v>6.871440929922427</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845803948442875</v>
+        <v>6.845736059850181</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841605095841452</v>
+        <v>6.841491342840898</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808150118393488</v>
+        <v>6.808312607815887</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823915884882815</v>
+        <v>6.823903543737439</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818422189073397</v>
+        <v>6.818298584394936</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813011913954202</v>
+        <v>6.812870690760155</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806925351027525</v>
+        <v>6.806763409365615</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802485548824982</v>
+        <v>6.802310275735179</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800737385783156</v>
+        <v>6.800550875418638</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.78332578060673</v>
+        <v>6.783255697244014</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783702594416093</v>
+        <v>6.783581381486087</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775348446538452</v>
+        <v>6.775300158729837</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772243276797227</v>
+        <v>6.771985417662679</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768215965555606</v>
+        <v>6.76781436259159</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.761923586506179</v>
+        <v>6.762382515474533</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752411730706446</v>
+        <v>6.75469801976407</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.743324447696388</v>
+        <v>6.745459444674797</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.731723917041052</v>
+        <v>6.736150559958077</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.717886585719798</v>
+        <v>6.729781767396731</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.709046230784922</v>
+        <v>6.726124489954862</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.70543573688839</v>
+        <v>6.728350815256995</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.70285341452297</v>
+        <v>6.731953848385546</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.688292747772055</v>
+        <v>6.720312776407493</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.667836750599522</v>
+        <v>6.705549919886312</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.641265442851486</v>
+        <v>6.685107413041315</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.591962164161966</v>
+        <v>6.643798994467185</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.577678790121316</v>
+        <v>6.650204827196905</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.577881996934698</v>
+        <v>6.667972069139862</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,15 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.639687250419231</v>
+        <v>6.674991448278375</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B113">
+        <v>6.716878948278375</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141548800082107</v>
+        <v>7.141526008719952</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.15173720781543</v>
+        <v>7.151699174843395</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155247718117831</v>
+        <v>7.155210419628133</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168622349365859</v>
+        <v>7.168580549614804</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183578705054433</v>
+        <v>7.183539072039546</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195520812248883</v>
+        <v>7.195483910113075</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197795437132825</v>
+        <v>7.197762067415364</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192325880274391</v>
+        <v>7.19229635444998</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175431623728926</v>
+        <v>7.175449224166845</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180195691954574</v>
+        <v>7.180237776688799</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184242045640596</v>
+        <v>7.184281517048749</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189343672131006</v>
+        <v>7.189382659056594</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183024753217345</v>
+        <v>7.183095121585427</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182149483156737</v>
+        <v>7.182231434435761</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.18326944947403</v>
+        <v>7.183337973098433</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168587240082408</v>
+        <v>7.168647382497419</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155095402014663</v>
+        <v>7.155184528502007</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.14786884505671</v>
+        <v>7.147970611766951</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143614969509023</v>
+        <v>7.143741401239375</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123749706760329</v>
+        <v>7.12385373282074</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11103169429262</v>
+        <v>7.111171776990997</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102390827381086</v>
+        <v>7.10254891899066</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.07459066553002</v>
+        <v>7.07476685879971</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.04997564532952</v>
+        <v>7.050156291076515</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048289222840212</v>
+        <v>7.048481249313367</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046651212102203</v>
+        <v>7.046890328421451</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053401728635837</v>
+        <v>7.053696193787575</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.058565037150366</v>
+        <v>7.058973314945758</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.014157545638279</v>
+        <v>7.014532106242239</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.966894788595585</v>
+        <v>6.967198056911011</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967529703358517</v>
+        <v>6.967824527482358</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947426703506284</v>
+        <v>6.947797684278024</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897559768818805</v>
+        <v>6.897761952865462</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.860987668080666</v>
+        <v>6.86119920340118</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846798272044678</v>
+        <v>6.846972950459403</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824483274133025</v>
+        <v>6.824329588616536</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843319445773729</v>
+        <v>6.843121325938039</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.858378893637007</v>
+        <v>6.857965847434905</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888743554697184</v>
+        <v>6.888543839302013</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.89087930417589</v>
+        <v>6.890746311241751</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878708597334223</v>
+        <v>6.878478550357924</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871440929922427</v>
+        <v>6.871596787026333</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845736059850181</v>
+        <v>6.845825479604112</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841491342840898</v>
+        <v>6.841641162122661</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808312607815887</v>
+        <v>6.808098522152738</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823903543737439</v>
+        <v>6.82391966649117</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818298584394936</v>
+        <v>6.818461149290075</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812870690760155</v>
+        <v>6.813056439247066</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806763409365615</v>
+        <v>6.806976463441307</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802310275735179</v>
+        <v>6.802540943771183</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800550875418638</v>
+        <v>6.800796446834184</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783255697244014</v>
+        <v>6.78334793121858</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783581381486087</v>
+        <v>6.783741042558516</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775300158729837</v>
+        <v>6.775363865402435</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771985417662679</v>
+        <v>6.772245328430957</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.76781436259159</v>
+        <v>6.768221741231825</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762382515474533</v>
+        <v>6.761941942870855</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.75469801976407</v>
+        <v>6.752440086664318</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.745459444674797</v>
+        <v>6.743434124759897</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.736150559958077</v>
+        <v>6.732271362042573</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.729781767396731</v>
+        <v>6.719242417788234</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.726124489954862</v>
+        <v>6.711368552970484</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.728350815256995</v>
+        <v>6.708035953994262</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.731953848385546</v>
+        <v>6.705578963291332</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.720312776407493</v>
+        <v>6.691187088285887</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.705549919886312</v>
+        <v>6.670948859654969</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.685107413041315</v>
+        <v>6.644939086991692</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.643798994467185</v>
+        <v>6.597833322912703</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.650204827196905</v>
+        <v>6.585407843524981</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.667972069139862</v>
+        <v>6.587207955720588</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.674991448278375</v>
+        <v>6.646347051468167</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.716878948278375</v>
+        <v>6.681730981790087</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141526008719952</v>
+        <v>7.141542868127301</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151699174843395</v>
+        <v>7.151727310356005</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155210419628133</v>
+        <v>7.155238015003855</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168580549614804</v>
+        <v>7.168611475836659</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183539072039546</v>
+        <v>7.183568394820323</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195483910113075</v>
+        <v>7.195511212110326</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197762067415364</v>
+        <v>7.197786755899116</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.19229635444998</v>
+        <v>7.192318199144029</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175449224166845</v>
+        <v>7.175436217151213</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180237776688799</v>
+        <v>7.180206648654885</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184281517048749</v>
+        <v>7.184252321520969</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189382659056594</v>
+        <v>7.189353821561456</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183095121585427</v>
+        <v>7.183043071513207</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182231434435761</v>
+        <v>7.182170812377482</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183337973098433</v>
+        <v>7.183287284041697</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168647382497419</v>
+        <v>7.168602903373243</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155184528502007</v>
+        <v>7.155118608392891</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147970611766951</v>
+        <v>7.147895340932416</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143741401239375</v>
+        <v>7.143647876735655</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.12385373282074</v>
+        <v>7.123776794876514</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111171776990997</v>
+        <v>7.111068146857489</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.10254891899066</v>
+        <v>7.102431948899242</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.07476685879971</v>
+        <v>7.074636467519612</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050156291076515</v>
+        <v>7.050022602998721</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048481249313367</v>
+        <v>7.048339151893305</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046890328421451</v>
+        <v>7.046713418428148</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053696193787575</v>
+        <v>7.053478352268569</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.058973314945758</v>
+        <v>7.058671296673546</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.014532106242239</v>
+        <v>7.014255069951162</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967198056911011</v>
+        <v>6.966973696850332</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967824527482358</v>
+        <v>6.967606368376188</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947797684278024</v>
+        <v>6.947523004748828</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897761952865462</v>
+        <v>6.89761221260494</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.86119920340118</v>
+        <v>6.861042518593328</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846972950459403</v>
+        <v>6.846843468613448</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824329588616536</v>
+        <v>6.824443192053646</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843121325938039</v>
+        <v>6.843267813910909</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.857965847434905</v>
+        <v>6.858271514983796</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888543839302013</v>
+        <v>6.888691641623949</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890746311241751</v>
+        <v>6.890844815222547</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878478550357924</v>
+        <v>6.878648929494416</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871596787026333</v>
+        <v>6.871481441206756</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845825479604112</v>
+        <v>6.845759259231522</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841641162122661</v>
+        <v>6.841530221320557</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808098522152738</v>
+        <v>6.808257114554738</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.82391966649117</v>
+        <v>6.823907832684959</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818461149290075</v>
+        <v>6.818340954019563</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813056439247066</v>
+        <v>6.812919093328656</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806976463441307</v>
+        <v>6.806818883202713</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802540943771183</v>
+        <v>6.802370275805051</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800796446834184</v>
+        <v>6.800614660275632</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.78334793121858</v>
+        <v>6.783279687885162</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783741042558516</v>
+        <v>6.783622800301862</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775363865402435</v>
+        <v>6.775316603590223</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772245328430957</v>
+        <v>6.771988780569684</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768221741231825</v>
+        <v>6.767821591895164</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.761941942870855</v>
+        <v>6.762398926725354</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752440086664318</v>
+        <v>6.754720063392112</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.743434124759897</v>
+        <v>6.745233660952289</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.732271362042573</v>
+        <v>6.736198903249623</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.719242417788234</v>
+        <v>6.730411333822902</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.711368552970484</v>
+        <v>6.727872636645666</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.708035953994262</v>
+        <v>6.730431437008161</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.705578963291332</v>
+        <v>6.734909153061826</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.691187088285887</v>
+        <v>6.723996940826437</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.670948859654969</v>
+        <v>6.709685168979709</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.644939086991692</v>
+        <v>6.68985792718674</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.597833322912703</v>
+        <v>6.651754007668936</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.585407843524981</v>
+        <v>6.658198723824706</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.587207955720588</v>
+        <v>6.676133437713153</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.646347051468167</v>
+        <v>6.68669394311453</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.681730981790087</v>
+        <v>6.728581443114531</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141542868127301</v>
+        <v>7.141520680804939</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151727310356005</v>
+        <v>7.151690281725625</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155238015003855</v>
+        <v>7.15520169344749</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168611475836659</v>
+        <v>7.168570769475858</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183568394820323</v>
+        <v>7.183529799383389</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195511212110326</v>
+        <v>7.195475276863945</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197786755899116</v>
+        <v>7.197754260661899</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192318199144029</v>
+        <v>7.192289446809909</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175436217151213</v>
+        <v>7.175453319842372</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180206648654885</v>
+        <v>7.180247609967292</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184252321520969</v>
+        <v>7.184290740378078</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189353821561456</v>
+        <v>7.189391769657318</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183043071513207</v>
+        <v>7.18311156645335</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182170812377482</v>
+        <v>7.182250592677944</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183287284041697</v>
+        <v>7.183353992107408</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168602903373243</v>
+        <v>7.168661427071086</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155118608392891</v>
+        <v>7.155205349602717</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147895340932416</v>
+        <v>7.147994388315895</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143647876735655</v>
+        <v>7.143770956111445</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123776794876514</v>
+        <v>7.123878031279591</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111068146857489</v>
+        <v>7.111204534375284</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102431948899242</v>
+        <v>7.10258591361031</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074636467519612</v>
+        <v>7.074808131375383</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050022602998721</v>
+        <v>7.05019860924175</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048339151893305</v>
+        <v>7.048526213982671</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046713418428148</v>
+        <v>7.046946269535723</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053478352268569</v>
+        <v>7.053765056258702</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.058671296673546</v>
+        <v>7.059068762476695</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.014255069951162</v>
+        <v>7.01461961133644</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.966973696850332</v>
+        <v>6.967268986581014</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967606368376188</v>
+        <v>6.967893551225171</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947523004748828</v>
+        <v>6.947884789325421</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.89761221260494</v>
+        <v>6.897809485431661</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861042518593328</v>
+        <v>6.861248962737637</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846843468613448</v>
+        <v>6.847014185463085</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824443192053646</v>
+        <v>6.824293785197697</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843267813910909</v>
+        <v>6.843075112524286</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.858271514983796</v>
+        <v>6.857869102301587</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888691641623949</v>
+        <v>6.888497051592162</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890844815222547</v>
+        <v>6.890715034071236</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878648929494416</v>
+        <v>6.87842446248535</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871481441206756</v>
+        <v>6.871633302490776</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845759259231522</v>
+        <v>6.845846494383713</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841530221320557</v>
+        <v>6.841676358430519</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808257114554738</v>
+        <v>6.808048135122068</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823907832684959</v>
+        <v>6.82392329636625</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818340954019563</v>
+        <v>6.818499063628987</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812919093328656</v>
+        <v>6.813099774629436</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806818883202713</v>
+        <v>6.807026235347056</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802370275805051</v>
+        <v>6.802594920514543</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800614660275632</v>
+        <v>6.800854048788088</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783279687885162</v>
+        <v>6.783369514982949</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783622800301862</v>
+        <v>6.783778570485186</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775316603590223</v>
+        <v>6.775378962422511</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771988780569684</v>
+        <v>6.772247383562572</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.767821591895164</v>
+        <v>6.768227354754171</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762398926725354</v>
+        <v>6.761959737016513</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.754720063392112</v>
+        <v>6.752467632634575</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.745233660952289</v>
+        <v>6.743310961627009</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.736198903249623</v>
+        <v>6.732482474755008</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.730411333822902</v>
+        <v>6.720202343069401</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.727872636645666</v>
+        <v>6.71285972854858</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.730431437008161</v>
+        <v>6.709817542085367</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.734909153061826</v>
+        <v>6.707458505185805</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.723996940826437</v>
+        <v>6.693219560546988</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.709685168979709</v>
+        <v>6.673159824016841</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.68985792718674</v>
+        <v>6.647605875293797</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.651754007668936</v>
+        <v>6.602217161334439</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.658198723824706</v>
+        <v>6.59097834464454</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.676133437713153</v>
+        <v>6.593522049478377</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.68669394311453</v>
+        <v>6.648480893602138</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.728581443114531</v>
+        <v>6.67044276948887</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141520680804939</v>
+        <v>7.141537096465917</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151690281725625</v>
+        <v>7.151717679359002</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.15520169344749</v>
+        <v>7.155228570952236</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168570769475858</v>
+        <v>7.168600892228367</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183529799383389</v>
+        <v>7.183558359722049</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195475276863945</v>
+        <v>7.195501868376095</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197754260661899</v>
+        <v>7.197778306566818</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192289446809909</v>
+        <v>7.192310723130021</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175453319842372</v>
+        <v>7.175440677995025</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180247609967292</v>
+        <v>7.180217307109674</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184290740378078</v>
+        <v>7.184262317987916</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189391769657318</v>
+        <v>7.189363695233569</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18311156645335</v>
+        <v>7.183060892536488</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182250592677944</v>
+        <v>7.182191565523986</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183353992107408</v>
+        <v>7.183304636834288</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168661427071086</v>
+        <v>7.168618136729935</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155205349602717</v>
+        <v>7.155141181459246</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147994388315895</v>
+        <v>7.147921114886808</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143770956111445</v>
+        <v>7.143679894370094</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123878031279591</v>
+        <v>7.123803142228351</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111204534375284</v>
+        <v>7.11110361919941</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.10258591361031</v>
+        <v>7.102471976376485</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074808131375383</v>
+        <v>7.074681069834729</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.05019860924175</v>
+        <v>7.050068331914042</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048526213982671</v>
+        <v>7.048387765625187</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046946269535723</v>
+        <v>7.046773963444397</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053765056258702</v>
+        <v>7.053552917245117</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.059068762476695</v>
+        <v>7.058774687592564</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.01461961133644</v>
+        <v>7.014349934355685</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967268986581014</v>
+        <v>6.967050489301149</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967893551225171</v>
+        <v>6.967681008909875</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947884789325421</v>
+        <v>6.947616875828672</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897809485431661</v>
+        <v>6.897663360218399</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861248962737637</v>
+        <v>6.861096026221711</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847014185463085</v>
+        <v>6.846887624425158</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824293785197697</v>
+        <v>6.824404248343546</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843075112524286</v>
+        <v>6.843217622188257</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.857869102301587</v>
+        <v>6.858166952852061</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888497051592162</v>
+        <v>6.888641085839998</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890715034071236</v>
+        <v>6.890811173469385</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.87842446248535</v>
+        <v>6.87859073420757</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871633302490776</v>
+        <v>6.871520894231372</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845846494383713</v>
+        <v>6.845781881703886</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841676358430519</v>
+        <v>6.841568126988854</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808048135122068</v>
+        <v>6.808202967337394</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.82392329636625</v>
+        <v>6.823911943237895</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818499063628987</v>
+        <v>6.818382139344222</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813099774629436</v>
+        <v>6.812966149362553</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807026235347056</v>
+        <v>6.806872843485692</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802594920514543</v>
+        <v>6.802428679299552</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800854048788088</v>
+        <v>6.800676809822368</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783369514982949</v>
+        <v>6.783303040706001</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783778570485186</v>
+        <v>6.783663192177553</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775378962422511</v>
+        <v>6.775332696000209</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772247383562572</v>
+        <v>6.771992120682376</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768227354754171</v>
+        <v>6.767828612406034</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.761959737016513</v>
+        <v>6.762414797261806</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752467632634575</v>
+        <v>6.754741394026652</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.743310961627009</v>
+        <v>6.74446168556998</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.732482474755008</v>
+        <v>6.735438103278147</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.720202343069401</v>
+        <v>6.730052484728477</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.71285972854858</v>
+        <v>6.728003330997143</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709817542085367</v>
+        <v>6.730603579491343</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707458505185805</v>
+        <v>6.735637032568525</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.693219560546988</v>
+        <v>6.725173842052663</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.673159824016841</v>
+        <v>6.711098833755354</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.647605875293797</v>
+        <v>6.691595018539889</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.602217161334439</v>
+        <v>6.655306100087938</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.59097834464454</v>
+        <v>6.660784696944887</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.593522049478377</v>
+        <v>6.676687489006368</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.648480893602138</v>
+        <v>6.6844352552157</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.67044276948887</v>
+        <v>6.714629274746157</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141537096465917</v>
+        <v>7.141515489480387</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151717679359002</v>
+        <v>7.151681615802724</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155228570952236</v>
+        <v>7.155193188447261</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168600892228367</v>
+        <v>7.168561236917338</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183558359722049</v>
+        <v>7.183520761649627</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195501868376095</v>
+        <v>7.195466862513447</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197778306566818</v>
+        <v>7.19774665188239</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192310723130021</v>
+        <v>7.192282714286118</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175440677995025</v>
+        <v>7.175457303675609</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180217307109674</v>
+        <v>7.180257189388493</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184262317987916</v>
+        <v>7.184299725839512</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189363695233569</v>
+        <v>7.189400645472829</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183060892536488</v>
+        <v>7.183127587865298</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182191565523986</v>
+        <v>7.182269259950322</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183304636834288</v>
+        <v>7.183369600542351</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168618136729935</v>
+        <v>7.168675106153975</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155141181459246</v>
+        <v>7.155225631810413</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147921114886808</v>
+        <v>7.148017550382669</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143679894370094</v>
+        <v>7.143799752898673</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123803142228351</v>
+        <v>7.123901699610916</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11110361919941</v>
+        <v>7.11123645565758</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102471976376485</v>
+        <v>7.102621973426141</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074681069834729</v>
+        <v>7.074848376412862</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050068331914042</v>
+        <v>7.050239874779713</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048387765625187</v>
+        <v>7.048570053074359</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046773963444397</v>
+        <v>7.047000792065311</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053552917245117</v>
+        <v>7.05383216241012</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.058774687592564</v>
+        <v>7.059161764337905</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.014349934355685</v>
+        <v>7.014704852455441</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967050489301149</v>
+        <v>6.967338109999345</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967681008909875</v>
+        <v>6.967960842374944</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947616875828672</v>
+        <v>6.947969800070657</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897663360218399</v>
+        <v>6.89785589713884</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861096026221711</v>
+        <v>6.861297559008307</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.846887624425158</v>
+        <v>6.847054509410691</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824404248343546</v>
+        <v>6.824258945011035</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843217622188257</v>
+        <v>6.843030121075904</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.858166952852061</v>
+        <v>6.857774769326168</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888641085839998</v>
+        <v>6.888451426941904</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890811173469385</v>
+        <v>6.890684490553953</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.87859073420757</v>
+        <v>6.878371648265294</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871520894231372</v>
+        <v>6.87166891133485</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845781881703886</v>
+        <v>6.845867011074486</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841568126988854</v>
+        <v>6.841710715814416</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808202967337394</v>
+        <v>6.807998915770659</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823911943237895</v>
+        <v>6.823926782286004</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818382139344222</v>
+        <v>6.818535973436361</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.812966149362553</v>
+        <v>6.813141966913147</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.806872843485692</v>
+        <v>6.807074718562757</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802428679299552</v>
+        <v>6.802647532605901</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800676809822368</v>
+        <v>6.800910244765372</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783303040706001</v>
+        <v>6.783390553224757</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783663192177553</v>
+        <v>6.783815210510246</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775332696000209</v>
+        <v>6.775393747075617</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.771992120682376</v>
+        <v>6.772249440174329</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.767828612406034</v>
+        <v>6.768232813028842</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762414797261806</v>
+        <v>6.761976993432476</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.754741394026652</v>
+        <v>6.752494401354737</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.74446168556998</v>
+        <v>6.742676421477915</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.735438103278147</v>
+        <v>6.731926928285254</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.730052484728477</v>
+        <v>6.720156120159359</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.728003330997143</v>
+        <v>6.712965400169743</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.730603579491343</v>
+        <v>6.710078749709365</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.735637032568525</v>
+        <v>6.70764598632431</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.725173842052663</v>
+        <v>6.693503420393776</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.711098833755354</v>
+        <v>6.673602322689256</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.691595018539889</v>
+        <v>6.648417261582222</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.655306100087938</v>
+        <v>6.604135619489428</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.660784696944887</v>
+        <v>6.59325734436317</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.676687489006368</v>
+        <v>6.595495278531255</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.6844352552157</v>
+        <v>6.644292140310406</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.714629274746157</v>
+        <v>6.649112750326884</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141515489480387</v>
+        <v>7.141510429560441</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151681615802724</v>
+        <v>7.151673168479217</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155193188447261</v>
+        <v>7.155184896325826</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168561236917338</v>
+        <v>7.168551942658812</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183520761649627</v>
+        <v>7.183511950025094</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195466862513447</v>
+        <v>7.19545865884281</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.19774665188239</v>
+        <v>7.19773923364239</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192282714286118</v>
+        <v>7.192276150304505</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175457303675609</v>
+        <v>7.175461180167725</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180257189388493</v>
+        <v>7.180266524655029</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184299725839512</v>
+        <v>7.184308482515553</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189400645472829</v>
+        <v>7.189409295461404</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183127587865298</v>
+        <v>7.183143201962972</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182269259950322</v>
+        <v>7.18228745487639</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183369600542351</v>
+        <v>7.183384813982887</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168675106153975</v>
+        <v>7.168688433818871</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155225631810413</v>
+        <v>7.15524539576039</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148017550382669</v>
+        <v>7.148040121455281</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143799752898673</v>
+        <v>7.143827820376975</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123901699610916</v>
+        <v>7.123924761988357</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11123645565758</v>
+        <v>7.111267572401303</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102621973426141</v>
+        <v>7.102657133364594</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074848376412862</v>
+        <v>7.074887631744037</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050239874779713</v>
+        <v>7.050280126405724</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048570053074359</v>
+        <v>7.048612808258037</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047000792065311</v>
+        <v>7.047053949216959</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.05383216241012</v>
+        <v>7.053897578469783</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.059161764337905</v>
+        <v>7.05925241312905</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.014704852455441</v>
+        <v>7.014787916163931</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967338109999345</v>
+        <v>6.967405495031283</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967960842374944</v>
+        <v>6.968026465064964</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947969800070657</v>
+        <v>6.948052790746801</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.89785589713884</v>
+        <v>6.897901226861328</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861297559008307</v>
+        <v>6.861345032146674</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847054509410691</v>
+        <v>6.847093951438616</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824258945011035</v>
+        <v>6.824225029933896</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843030121075904</v>
+        <v>6.84298630399793</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.857774769326168</v>
+        <v>6.857682759636019</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888451426941904</v>
+        <v>6.888406922641071</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890684490553953</v>
+        <v>6.890654655467092</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878371648265294</v>
+        <v>6.878320063584877</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.87166891133485</v>
+        <v>6.871703646886233</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845867011074486</v>
+        <v>6.845887047118275</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841710715814416</v>
+        <v>6.841744263865844</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807998915770659</v>
+        <v>6.807950824422412</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823926782286004</v>
+        <v>6.823930131542188</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818535973436361</v>
+        <v>6.818571917917343</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813141966913147</v>
+        <v>6.813183060498615</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807074718562757</v>
+        <v>6.807121962281004</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802647532605901</v>
+        <v>6.8026988309446</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800910244765372</v>
+        <v>6.800965085353733</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783390553224757</v>
+        <v>6.783411066220456</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783815210510246</v>
+        <v>6.783850993469825</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775393747075617</v>
+        <v>6.775408228498654</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772249440174329</v>
+        <v>6.772251496430898</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768232813028842</v>
+        <v>6.768238122570159</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.761976993432476</v>
+        <v>6.761993735247145</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752494401354737</v>
+        <v>6.752520423885434</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.742676421477915</v>
+        <v>6.741825125674239</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.731926928285254</v>
+        <v>6.731117567527933</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.720156120159359</v>
+        <v>6.719783367576049</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712965400169743</v>
+        <v>6.712579575865684</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.710078749709365</v>
+        <v>6.709933589612106</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.70764598632431</v>
+        <v>6.707351602026544</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.693503420393776</v>
+        <v>6.693225926609105</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.673602322689256</v>
+        <v>6.673392901649815</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.648417261582222</v>
+        <v>6.648453017098635</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.604135619489428</v>
+        <v>6.604935203138521</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.59325734436317</v>
+        <v>6.594049810779209</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.595495278531255</v>
+        <v>6.59565034894794</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.644292140310406</v>
+        <v>6.638524818775531</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.649112750326884</v>
+        <v>6.632584416079229</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141510429560441</v>
+        <v>7.141505496118477</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151673168479217</v>
+        <v>7.15166493158776</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155184896325826</v>
+        <v>7.155176809191762</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168551942658812</v>
+        <v>7.168542877877812</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183511950025094</v>
+        <v>7.183503356131876</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19545865884281</v>
+        <v>7.195450658039508</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.19773923364239</v>
+        <v>7.197731998875</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192276150304505</v>
+        <v>7.19226974861589</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175461180167725</v>
+        <v>7.175464953582399</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180266524655029</v>
+        <v>7.180275624981424</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184308482515553</v>
+        <v>7.184317019032235</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189409295461404</v>
+        <v>7.189417728131411</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183143201962972</v>
+        <v>7.183158424078275</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.18228745487639</v>
+        <v>7.182305195150041</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183384813982887</v>
+        <v>7.183399647230492</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168688433818871</v>
+        <v>7.168701423425762</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.15524539576039</v>
+        <v>7.155264661048582</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148040121455281</v>
+        <v>7.148062123841145</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143827820376975</v>
+        <v>7.14385518588516</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123924761988357</v>
+        <v>7.123947241365849</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111267572401303</v>
+        <v>7.111297914603064</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102657133364594</v>
+        <v>7.102691426636719</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074887631744037</v>
+        <v>7.074925933369552</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050280126405724</v>
+        <v>7.050319400963321</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048612808258037</v>
+        <v>7.048654519175057</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047053949216959</v>
+        <v>7.047105791573209</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053897578469783</v>
+        <v>7.053961367382925</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.05925241312905</v>
+        <v>7.059340796843532</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.014787916163931</v>
+        <v>7.014868884677496</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967405495031283</v>
+        <v>6.967471206197175</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968026465064964</v>
+        <v>6.968090480316476</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.948052790746801</v>
+        <v>6.948133832139857</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897901226861328</v>
+        <v>6.897945511712234</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861345032146674</v>
+        <v>6.861391420298027</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847093951438616</v>
+        <v>6.84713253949392</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824225029933896</v>
+        <v>6.824192003818599</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.84298630399793</v>
+        <v>6.842943616124392</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.857682759636019</v>
+        <v>6.857592988660079</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888406922641071</v>
+        <v>6.888363498039234</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890654655467092</v>
+        <v>6.890625504715498</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878320063584877</v>
+        <v>6.878269666326865</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871703646886233</v>
+        <v>6.87173754085988</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845887047118275</v>
+        <v>6.84590661915469</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841744263865844</v>
+        <v>6.841777030802863</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807950824422412</v>
+        <v>6.807903823155227</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823930131542188</v>
+        <v>6.823933350976138</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818571917917343</v>
+        <v>6.818606934272256</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813183060498615</v>
+        <v>6.813223097527416</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807121962281004</v>
+        <v>6.807168013232517</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.8026988309446</v>
+        <v>6.802748863939926</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800965085353733</v>
+        <v>6.801018618756309</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783411066220456</v>
+        <v>6.783431073261203</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783850993469825</v>
+        <v>6.78388594880443</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775408228498654</v>
+        <v>6.775422415501501</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772251496430898</v>
+        <v>6.77225355066386</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768238122570159</v>
+        <v>6.768243289528099</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.761993735247145</v>
+        <v>6.762009984318983</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752520423885434</v>
+        <v>6.752545729712825</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.741825125674239</v>
+        <v>6.74102414269721</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.731117567527933</v>
+        <v>6.730243321410644</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.719783367576049</v>
+        <v>6.719227730600622</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712579575865684</v>
+        <v>6.711748737768627</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709933589612106</v>
+        <v>6.709001632358142</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707351602026544</v>
+        <v>6.706198007429823</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.693225926609105</v>
+        <v>6.692250855347195</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.673392901649815</v>
+        <v>6.672851729537035</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.648453017098635</v>
+        <v>6.648575746428902</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.604935203138521</v>
+        <v>6.60622210629203</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.594049810779209</v>
+        <v>6.595525186112557</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.59565034894794</v>
+        <v>6.596342191708322</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.638524818775531</v>
+        <v>6.633807996907906</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.632584416079229</v>
+        <v>6.62101503873423</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141505496118477</v>
+        <v>7.141500684471096</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.15166493158776</v>
+        <v>7.15165689736283</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155176809191762</v>
+        <v>7.15516891953882</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168542877877812</v>
+        <v>7.168534034181917</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183503356131876</v>
+        <v>7.183494972000787</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195450658039508</v>
+        <v>7.195442852672472</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197731998875</v>
+        <v>7.197724940858433</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.19226974861589</v>
+        <v>7.192263503276187</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175464953582399</v>
+        <v>7.17546862796121</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180275624981424</v>
+        <v>7.180284499124386</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184317019032235</v>
+        <v>7.184325343587424</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189417728131411</v>
+        <v>7.189425951569187</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183158424078275</v>
+        <v>7.183173268783442</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182305195150041</v>
+        <v>7.182322497592805</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183399647230492</v>
+        <v>7.183414114356484</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168701423425762</v>
+        <v>7.168714087666388</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155264661048582</v>
+        <v>7.155283446296128</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148062123841145</v>
+        <v>7.148083578740232</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.14385518588516</v>
+        <v>7.143881875413463</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123947241365849</v>
+        <v>7.123969159553484</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111297914603064</v>
+        <v>7.111327510788545</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102691426636719</v>
+        <v>7.102724884842003</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074925933369552</v>
+        <v>7.074963315568066</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050319400963321</v>
+        <v>7.05035773353579</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048654519175057</v>
+        <v>7.048695223560238</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047105791573209</v>
+        <v>7.047156367251985</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053961367382925</v>
+        <v>7.054023589012619</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.059340796843532</v>
+        <v>7.059426999150785</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.014868884677496</v>
+        <v>7.014947836131862</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967471206197175</v>
+        <v>6.967535304875231</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968090480316476</v>
+        <v>6.968152946224277</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.948133832139857</v>
+        <v>6.948212991785276</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897945511712234</v>
+        <v>6.897988787141051</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861391420298027</v>
+        <v>6.861436759917193</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.84713253949392</v>
+        <v>6.847170300391632</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824192003818599</v>
+        <v>6.824159832366784</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842943616124392</v>
+        <v>6.842902014565934</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.857592988660079</v>
+        <v>6.85750537587242</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888363498039234</v>
+        <v>6.888321114423402</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890625504715498</v>
+        <v>6.890597015270382</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878269666326865</v>
+        <v>6.878220416259252</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.87173754085988</v>
+        <v>6.871770623454358</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.84590661915469</v>
+        <v>6.845925743066559</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841777030802863</v>
+        <v>6.841809043548759</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807903823155227</v>
+        <v>6.807857875706667</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823933350976138</v>
+        <v>6.823936447011544</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818606934272256</v>
+        <v>6.818641057822589</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813223097527416</v>
+        <v>6.81326211802348</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807168013232517</v>
+        <v>6.807212915837625</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802748863939926</v>
+        <v>6.802797677660909</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801018618756309</v>
+        <v>6.801070890929688</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783431073261203</v>
+        <v>6.783450592711534</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.78388594880443</v>
+        <v>6.783920104635999</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775422415501501</v>
+        <v>6.775436316579611</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.77225355066386</v>
+        <v>6.7722556013576</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768243289528099</v>
+        <v>6.768248319713539</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762009984318983</v>
+        <v>6.762025761320428</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752545729712825</v>
+        <v>6.752570346843862</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.74102414269721</v>
+        <v>6.740318949630582</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.730243321410644</v>
+        <v>6.729427401846797</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.719227730600622</v>
+        <v>6.718701747247597</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.711748737768627</v>
+        <v>6.711057389237021</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709001632358142</v>
+        <v>6.708125508056055</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.706198007429823</v>
+        <v>6.705103046360864</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.692250855347195</v>
+        <v>6.691303415648447</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.672851729537035</v>
+        <v>6.672289868903691</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.648575746428902</v>
+        <v>6.648630526043817</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.60622210629203</v>
+        <v>6.607342141656685</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.595525186112557</v>
+        <v>6.596877922410477</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.596342191708322</v>
+        <v>6.597145710216902</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.633807996907906</v>
+        <v>6.630440410143147</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.62101503873423</v>
+        <v>6.614898162025781</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141500684471096</v>
+        <v>7.141520680804939</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.15165689736283</v>
+        <v>7.151690281725625</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.15516891953882</v>
+        <v>7.15520169344749</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168534034181917</v>
+        <v>7.168570769475858</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183494972000787</v>
+        <v>7.183529799383389</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195442852672472</v>
+        <v>7.195475276863945</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197724940858433</v>
+        <v>7.197754260661899</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192263503276187</v>
+        <v>7.192289446809909</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.17546862796121</v>
+        <v>7.175453319842372</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180284499124386</v>
+        <v>7.180247609967292</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184325343587424</v>
+        <v>7.184290740378078</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189425951569187</v>
+        <v>7.189391769657318</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183173268783442</v>
+        <v>7.18311156645335</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182322497592805</v>
+        <v>7.182250592677944</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183414114356484</v>
+        <v>7.183353992107408</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168714087666388</v>
+        <v>7.168661427071086</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155283446296128</v>
+        <v>7.155205349602717</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148083578740232</v>
+        <v>7.147994388315895</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143881875413463</v>
+        <v>7.143770956111445</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123969159553484</v>
+        <v>7.123878031279591</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111327510788545</v>
+        <v>7.111204534375284</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102724884842003</v>
+        <v>7.10258591361031</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074963315568066</v>
+        <v>7.074808131375383</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.05035773353579</v>
+        <v>7.05019860924175</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048695223560238</v>
+        <v>7.048526213982671</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047156367251985</v>
+        <v>7.046946269535723</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054023589012619</v>
+        <v>7.053765056258702</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.059426999150785</v>
+        <v>7.059068762476695</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.014947836131862</v>
+        <v>7.01461961133644</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967535304875231</v>
+        <v>6.967268986581014</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968152946224277</v>
+        <v>6.967893551225171</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.948212991785276</v>
+        <v>6.947884789325421</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897988787141051</v>
+        <v>6.897809485431661</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861436759917193</v>
+        <v>6.861248962737637</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847170300391632</v>
+        <v>6.847014185463085</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824159832366784</v>
+        <v>6.824293785197697</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842902014565934</v>
+        <v>6.843075112524286</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.85750537587242</v>
+        <v>6.857869102301587</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888321114423402</v>
+        <v>6.888497051592162</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890597015270382</v>
+        <v>6.890715034071236</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878220416259252</v>
+        <v>6.87842446248535</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871770623454358</v>
+        <v>6.871633302490776</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845925743066559</v>
+        <v>6.845846494383713</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841809043548759</v>
+        <v>6.841676358430519</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807857875706667</v>
+        <v>6.808048135122068</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823936447011544</v>
+        <v>6.82392329636625</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818641057822589</v>
+        <v>6.818499063628987</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.81326211802348</v>
+        <v>6.813099774629436</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807212915837625</v>
+        <v>6.807026235347056</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802797677660909</v>
+        <v>6.802594920514543</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801070890929688</v>
+        <v>6.800854048788088</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783450592711534</v>
+        <v>6.783369514982949</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783920104635999</v>
+        <v>6.783778570485186</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775436316579611</v>
+        <v>6.775378962422511</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.7722556013576</v>
+        <v>6.772001990406532</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768248319713539</v>
+        <v>6.767848509922792</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762025761320428</v>
+        <v>6.762459408632599</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752570346843862</v>
+        <v>6.754801419857018</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740318949630582</v>
+        <v>6.74261557860048</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.729427401846797</v>
+        <v>6.733006378093252</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718701747247597</v>
+        <v>6.728274338320615</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.711057389237021</v>
+        <v>6.726600164842742</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.708125508056055</v>
+        <v>6.729983479956741</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.705103046360864</v>
+        <v>6.735152105093068</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.691303415648447</v>
+        <v>6.726100378563736</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.672289868903691</v>
+        <v>6.713049719386769</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.648630526043817</v>
+        <v>6.694935001106533</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.607342141656685</v>
+        <v>6.663168461602186</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.596877922410477</v>
+        <v>6.6673148901579</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.597145710216902</v>
+        <v>6.679385473026201</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.630440410143147</v>
+        <v>6.683709749428818</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,15 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.614898162025781</v>
+        <v>6.693991565872097</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B114">
+        <v>6.733480940872098</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141520680804939</v>
+        <v>7.1414959901633</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151690281725625</v>
+        <v>7.151649058416314</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.15520169344749</v>
+        <v>7.155161220222719</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168570769475858</v>
+        <v>7.168525403582885</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183529799383389</v>
+        <v>7.183486790046745</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195475276863945</v>
+        <v>7.195435235669089</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197754260661899</v>
+        <v>7.19771805319521</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192289446809909</v>
+        <v>7.192257408628022</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175453319842372</v>
+        <v>7.175472207137888</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180247609967292</v>
+        <v>7.180293155410896</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184290740378078</v>
+        <v>7.184333463977059</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189391769657318</v>
+        <v>7.189433973464887</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18311156645335</v>
+        <v>7.183187749937495</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182250592677944</v>
+        <v>7.182339378206939</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183353992107408</v>
+        <v>7.183428228746473</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168661427071086</v>
+        <v>7.168726438605473</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155205349602717</v>
+        <v>7.155301769209196</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.147994388315895</v>
+        <v>7.148104506312889</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143770956111445</v>
+        <v>7.143907913685632</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123878031279591</v>
+        <v>7.123990537287838</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111204534375284</v>
+        <v>7.111356388101466</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.10258591361031</v>
+        <v>7.102757538064799</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074808131375383</v>
+        <v>7.074999810997807</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.05019860924175</v>
+        <v>7.050395157549848</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048526213982671</v>
+        <v>7.048734957354919</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.046946269535723</v>
+        <v>7.047205722054702</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.053765056258702</v>
+        <v>7.054084300325829</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.059068762476695</v>
+        <v>7.059511099658065</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.01461961133644</v>
+        <v>7.015024844832394</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967268986581014</v>
+        <v>6.967597849489803</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967893551225171</v>
+        <v>6.968213918129255</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947884789325421</v>
+        <v>6.948290334151292</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.897809485431661</v>
+        <v>6.898031087024924</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861248962737637</v>
+        <v>6.861481085860055</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847014185463085</v>
+        <v>6.847207259868995</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824293785197697</v>
+        <v>6.824128483013173</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843075112524286</v>
+        <v>6.842861458568753</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.857869102301587</v>
+        <v>6.857419844553851</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888497051592162</v>
+        <v>6.888279734904293</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890715034071236</v>
+        <v>6.890569165111888</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.87842446248535</v>
+        <v>6.878172274932005</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871633302490776</v>
+        <v>6.871802923441352</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845846494383713</v>
+        <v>6.845944434022325</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841676358430519</v>
+        <v>6.841840327805357</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.808048135122068</v>
+        <v>6.807812947385502</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.82392329636625</v>
+        <v>6.82393942568447</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818499063628987</v>
+        <v>6.818674322127664</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813099774629436</v>
+        <v>6.813300160023852</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807026235347056</v>
+        <v>6.807256712346753</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802594920514543</v>
+        <v>6.802845315975503</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800854048788088</v>
+        <v>6.801121945712509</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783369514982949</v>
+        <v>6.783469642063939</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783778570485186</v>
+        <v>6.783953487839963</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775378962422511</v>
+        <v>6.775449939926244</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772001990406532</v>
+        <v>6.772257647136463</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.767848509922792</v>
+        <v>6.768253218621422</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762459408632599</v>
+        <v>6.762041085815413</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.754801419857018</v>
+        <v>6.752594301894925</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.74261557860048</v>
+        <v>6.740352256136051</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.733006378093252</v>
+        <v>6.729108038479935</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.728274338320615</v>
+        <v>6.718722870429617</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.726600164842742</v>
+        <v>6.711509687288483</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.729983479956741</v>
+        <v>6.708591534499911</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.735152105093068</v>
+        <v>6.705864838202304</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.726100378563736</v>
+        <v>6.692334591395906</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.713049719386769</v>
+        <v>6.67376131600845</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.694935001106533</v>
+        <v>6.65079819475534</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.663168461602186</v>
+        <v>6.611330254567813</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.6673148901579</v>
+        <v>6.601732864579758</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.679385473026201</v>
+        <v>6.60244079209293</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.683709749428818</v>
+        <v>6.634396301927363</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.693991565872097</v>
+        <v>6.623214074228552</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.733480940872098</v>
+        <v>6.662503936600718</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.1414959901633</v>
+        <v>7.141515489480387</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151649058416314</v>
+        <v>7.151681615802724</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155161220222719</v>
+        <v>7.155193188447261</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168525403582885</v>
+        <v>7.168561236917338</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183486790046745</v>
+        <v>7.183520761649627</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195435235669089</v>
+        <v>7.195466862513447</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.19771805319521</v>
+        <v>7.19774665188239</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192257408628022</v>
+        <v>7.192282714286118</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175472207137888</v>
+        <v>7.175457303675609</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180293155410896</v>
+        <v>7.180257189388493</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184333463977059</v>
+        <v>7.184299725839512</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189433973464887</v>
+        <v>7.189400645472829</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183187749937495</v>
+        <v>7.183127587865298</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182339378206939</v>
+        <v>7.182269259950322</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183428228746473</v>
+        <v>7.183369600542351</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168726438605473</v>
+        <v>7.168675106153975</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155301769209196</v>
+        <v>7.155225631810413</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148104506312889</v>
+        <v>7.148017550382669</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143907913685632</v>
+        <v>7.143799752898673</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123990537287838</v>
+        <v>7.123901699610916</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111356388101466</v>
+        <v>7.11123645565758</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102757538064799</v>
+        <v>7.102621973426141</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074999810997807</v>
+        <v>7.074848376412862</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050395157549848</v>
+        <v>7.050239874779713</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048734957354919</v>
+        <v>7.048570053074359</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047205722054702</v>
+        <v>7.047000792065311</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054084300325829</v>
+        <v>7.05383216241012</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.059511099658065</v>
+        <v>7.059161764337905</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.015024844832394</v>
+        <v>7.014704852455441</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967597849489803</v>
+        <v>6.967338109999345</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968213918129255</v>
+        <v>6.967960842374944</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.948290334151292</v>
+        <v>6.947969800070657</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898031087024924</v>
+        <v>6.89785589713884</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861481085860055</v>
+        <v>6.861297559008307</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847207259868995</v>
+        <v>6.847054509410691</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824128483013173</v>
+        <v>6.824258945011035</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842861458568753</v>
+        <v>6.843030121075904</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.857419844553851</v>
+        <v>6.857774769326168</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888279734904293</v>
+        <v>6.888451426941904</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890569165111888</v>
+        <v>6.890684490553953</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878172274932005</v>
+        <v>6.878371648265294</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871802923441352</v>
+        <v>6.87166891133485</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845944434022325</v>
+        <v>6.845867011074486</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841840327805357</v>
+        <v>6.841710715814416</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807812947385502</v>
+        <v>6.807998915770659</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.82393942568447</v>
+        <v>6.823926782286004</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818674322127664</v>
+        <v>6.818535973436361</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813300160023852</v>
+        <v>6.813141966913147</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807256712346753</v>
+        <v>6.807074718562757</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802845315975503</v>
+        <v>6.802647532605901</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801121945712509</v>
+        <v>6.800910244765372</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783469642063939</v>
+        <v>6.783390553224757</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783953487839963</v>
+        <v>6.783815210510246</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775449939926244</v>
+        <v>6.775393747075617</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772257647136463</v>
+        <v>6.772005226352026</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768253218621422</v>
+        <v>6.767854781490062</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762041085815413</v>
+        <v>6.762473353352352</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752594301894925</v>
+        <v>6.754820201805117</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740352256136051</v>
+        <v>6.742644345240722</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.729108038479935</v>
+        <v>6.732528077143745</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718722870429617</v>
+        <v>6.727851598288339</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.711509687288483</v>
+        <v>6.726263378861619</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.708591534499911</v>
+        <v>6.72957971135769</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.705864838202304</v>
+        <v>6.734790608961418</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.692334591395906</v>
+        <v>6.726385980435225</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.67376131600845</v>
+        <v>6.713949937502123</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.65079819475534</v>
+        <v>6.6966726818256</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.611330254567813</v>
+        <v>6.666697064462825</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.601732864579758</v>
+        <v>6.67145197475265</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.60244079209293</v>
+        <v>6.683694674961047</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.634396301927363</v>
+        <v>6.68937179180084</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.623214074228552</v>
+        <v>6.701044248529495</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.662503936600718</v>
+        <v>6.740533623529496</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141515489480387</v>
+        <v>7.141491408954731</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151681615802724</v>
+        <v>7.151641407714853</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155193188447261</v>
+        <v>7.15515370443959</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168561236917338</v>
+        <v>7.168516978472616</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183520761649627</v>
+        <v>7.183478803045911</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195466862513447</v>
+        <v>7.195427800293862</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.19774665188239</v>
+        <v>7.197711329792839</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192282714286118</v>
+        <v>7.192251459283647</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175457303675609</v>
+        <v>7.17547569475146</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180257189388493</v>
+        <v>7.180301601764233</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184299725839512</v>
+        <v>7.184341387619477</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189400645472829</v>
+        <v>7.189441801136438</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183127587865298</v>
+        <v>7.183201880729343</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182269259950322</v>
+        <v>7.182355852224676</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183369600542351</v>
+        <v>7.183442003141612</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168675106153975</v>
+        <v>7.168738487718942</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155225631810413</v>
+        <v>7.15531964663445</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148017550382669</v>
+        <v>7.148124925742723</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143799752898673</v>
+        <v>7.143933324235085</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.123901699610916</v>
+        <v>7.124011394297167</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11123645565758</v>
+        <v>7.111384572386163</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102621973426141</v>
+        <v>7.102789414963894</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.074848376412862</v>
+        <v>7.075035450791032</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050239874779713</v>
+        <v>7.050431704872071</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048570053074359</v>
+        <v>7.048773754812087</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047000792065311</v>
+        <v>7.047253899603817</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.05383216241012</v>
+        <v>7.054143555566172</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.059161764337905</v>
+        <v>7.059593174153552</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.014704852455441</v>
+        <v>7.01509998148555</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967338109999345</v>
+        <v>6.967658895686321</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.967960842374944</v>
+        <v>6.968273448778922</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.947969800070657</v>
+        <v>6.948365920810049</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.89785589713884</v>
+        <v>6.898072443754037</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861297559008307</v>
+        <v>6.86152443146925</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847054509410691</v>
+        <v>6.847243442636836</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824258945011035</v>
+        <v>6.824097924817973</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.843030121075904</v>
+        <v>6.842821909383824</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.857774769326168</v>
+        <v>6.857336321570174</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888451426941904</v>
+        <v>6.888239324310508</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890684490553953</v>
+        <v>6.890541933175266</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878371648265294</v>
+        <v>6.878125205580446</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.87166891133485</v>
+        <v>6.871834468248906</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845867011074486</v>
+        <v>6.845962706515634</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841710715814416</v>
+        <v>6.841870908121439</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807998915770659</v>
+        <v>6.807769004988771</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823926782286004</v>
+        <v>6.82394229267091</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818535973436361</v>
+        <v>6.818706759092734</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813141966913147</v>
+        <v>6.813337259699939</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807074718562757</v>
+        <v>6.8072994429708</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802647532605901</v>
+        <v>6.802891820679983</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.800910244765372</v>
+        <v>6.801171824945392</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783390553224757</v>
+        <v>6.78348823798965</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783815210510246</v>
+        <v>6.783986124112729</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775393747075617</v>
+        <v>6.775463293444243</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772005226352026</v>
+        <v>6.772259686753021</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.767854781490062</v>
+        <v>6.768257991452064</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762473353352352</v>
+        <v>6.762055976330973</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.754820201805117</v>
+        <v>6.752617620174376</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.742644345240722</v>
+        <v>6.740384717935228</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.732528077143745</v>
+        <v>6.728818950296047</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.727851598288339</v>
+        <v>6.718750178923695</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.726263378861619</v>
+        <v>6.711927947093887</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.72957971135769</v>
+        <v>6.708866544729402</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.734790608961418</v>
+        <v>6.706420328991521</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.726385980435225</v>
+        <v>6.693195005703187</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.713949937502123</v>
+        <v>6.675084052363635</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.6966726818256</v>
+        <v>6.652821178926822</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.666697064462825</v>
+        <v>6.615083176483929</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.67145197475265</v>
+        <v>6.606327748652786</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.683694674961047</v>
+        <v>6.607494621665796</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.68937179180084</v>
+        <v>6.638359434490164</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.701044248529495</v>
+        <v>6.630644937873999</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.740533623529496</v>
+        <v>6.667775950803078</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141491408954731</v>
+        <v>7.141486936806912</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151641407714853</v>
+        <v>7.151633938558806</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.15515370443959</v>
+        <v>7.155146365705947</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168516978472616</v>
+        <v>7.168508751600812</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183478803045911</v>
+        <v>7.183471004114451</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195427800293862</v>
+        <v>7.19542054012855</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197711329792839</v>
+        <v>7.197704764845859</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192251459283647</v>
+        <v>7.192245650109078</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.17547569475146</v>
+        <v>7.175479094258413</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180301601764233</v>
+        <v>7.180309845728154</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184341387619477</v>
+        <v>7.184349121578001</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189441801136438</v>
+        <v>7.1894494415518</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183201880729343</v>
+        <v>7.18321567371778</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182355852224676</v>
+        <v>7.182371934153966</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183442003141612</v>
+        <v>7.183455449676912</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168738487718942</v>
+        <v>7.168750245929393</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.15531964663445</v>
+        <v>7.155337094610537</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148124925742723</v>
+        <v>7.14814485529498</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143933324235085</v>
+        <v>7.143958129475646</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124011394297167</v>
+        <v>7.124031749361886</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111384572386163</v>
+        <v>7.111412088264315</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102789414963894</v>
+        <v>7.10282054285582</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075035450791032</v>
+        <v>7.075070264641973</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050431704872071</v>
+        <v>7.050467405898705</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048773754812087</v>
+        <v>7.048811648594205</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047253899603817</v>
+        <v>7.047300941470708</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054143555566172</v>
+        <v>7.054201406414483</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.059593174153552</v>
+        <v>7.059673294832158</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.01509998148555</v>
+        <v>7.01517331341379</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967658895686321</v>
+        <v>6.967718496494006</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968273448778922</v>
+        <v>6.968331588476897</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.948365920810049</v>
+        <v>6.948439810597491</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898072443754037</v>
+        <v>6.89811288831157</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.86152443146925</v>
+        <v>6.861566828654505</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847243442636836</v>
+        <v>6.847278872428212</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824097924817973</v>
+        <v>6.824068128367154</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842821909383824</v>
+        <v>6.842783330145611</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.857336321570174</v>
+        <v>6.857254737165704</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888239324310508</v>
+        <v>6.888199849089963</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890541933175266</v>
+        <v>6.890515299300395</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878125205580446</v>
+        <v>6.878079173034779</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871834468248906</v>
+        <v>6.871865284038916</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845962706515634</v>
+        <v>6.845980574402327</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841870908121439</v>
+        <v>6.841900807956589</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807769004988771</v>
+        <v>6.80772601672393</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.82394229267091</v>
+        <v>6.823945053312083</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818706759092734</v>
+        <v>6.818738399069254</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813337259699939</v>
+        <v>6.81337345147002</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.8072994429708</v>
+        <v>6.807341146002298</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802891820679983</v>
+        <v>6.802937231619353</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801171824945392</v>
+        <v>6.801220568582853</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.78348823798965</v>
+        <v>6.783506396385945</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.783986124112729</v>
+        <v>6.784018038034858</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775463293444243</v>
+        <v>6.775476384757434</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772259686753021</v>
+        <v>6.772261719077378</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768257991452064</v>
+        <v>6.768262643130758</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762055976330973</v>
+        <v>6.762070450423492</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752617620174376</v>
+        <v>6.752640325759478</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740384717935228</v>
+        <v>6.740416365436213</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728818950296047</v>
+        <v>6.728512467060865</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718750178923695</v>
+        <v>6.718725791447302</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.711927947093887</v>
+        <v>6.712247203029022</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.708866544729402</v>
+        <v>6.709001716584439</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.706420328991521</v>
+        <v>6.706808401936112</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.693195005703187</v>
+        <v>6.693852524820543</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.675084052363635</v>
+        <v>6.676161210108571</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.652821178926822</v>
+        <v>6.654539867541539</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.615083176483929</v>
+        <v>6.618371107144724</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.606327748652786</v>
+        <v>6.610285398303444</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.607494621665796</v>
+        <v>6.611793133053832</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.638359434490164</v>
+        <v>6.641500963118586</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.630644937873999</v>
+        <v>6.636041547737975</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.667775950803078</v>
+        <v>6.668620782017001</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141486936806912</v>
+        <v>7.141482569871362</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151633938558806</v>
+        <v>7.151626644562694</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155146365705947</v>
+        <v>7.155139197840049</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168508751600812</v>
+        <v>7.168500716054192</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183471004114451</v>
+        <v>7.183463386688759</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19542054012855</v>
+        <v>7.19541344905373</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197704764845859</v>
+        <v>7.197698352819133</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192245650109078</v>
+        <v>7.192239976209322</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175479094258413</v>
+        <v>7.175482408943976</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180309845728154</v>
+        <v>7.180317894489329</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184349121578001</v>
+        <v>7.184356672581914</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.1894494415518</v>
+        <v>7.189456901349624</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18321567371778</v>
+        <v>7.183229140868658</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182371934153966</v>
+        <v>7.182387637820995</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183455449676912</v>
+        <v>7.183468579916857</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168750245929393</v>
+        <v>7.168761723639019</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155337094610537</v>
+        <v>7.155354128415927</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.14814485529498</v>
+        <v>7.148164312370794</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143958129475646</v>
+        <v>7.143982350767303</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124031749361886</v>
+        <v>7.124051620370795</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111412088264315</v>
+        <v>7.111438959206325</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.10282054285582</v>
+        <v>7.102850947792401</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075070264641973</v>
+        <v>7.075104280888776</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050467405898705</v>
+        <v>7.050502289639347</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048811648594205</v>
+        <v>7.048848669864332</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047300941470708</v>
+        <v>7.047346887294688</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054201406414483</v>
+        <v>7.05425790213816</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.059673294832158</v>
+        <v>7.059751530505593</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.01517331341379</v>
+        <v>7.015244904755274</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967718496494006</v>
+        <v>6.967776702477305</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968331588476897</v>
+        <v>6.968388385222216</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.948439810597491</v>
+        <v>6.94851205976282</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.89811288831157</v>
+        <v>6.898152450348592</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861566828654505</v>
+        <v>6.861608307967954</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847278872428212</v>
+        <v>6.847313572044471</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824068128367154</v>
+        <v>6.824039065679944</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842783330145611</v>
+        <v>6.842745685759424</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.857254737165704</v>
+        <v>6.857175024770864</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888199849089963</v>
+        <v>6.888161277218012</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890515299300395</v>
+        <v>6.89048924418441</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878079173034779</v>
+        <v>6.878034143635314</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871865284038916</v>
+        <v>6.871895395779317</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845980574402327</v>
+        <v>6.845998050935043</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841900807956589</v>
+        <v>6.841930049740872</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.80772601672393</v>
+        <v>6.807683952135761</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823945053312083</v>
+        <v>6.8239477126377</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818738399069254</v>
+        <v>6.81876927094798</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.81337345147002</v>
+        <v>6.813408768103736</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807341146002298</v>
+        <v>6.807381857928038</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802937231619353</v>
+        <v>6.802981586799492</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801220568582853</v>
+        <v>6.801268214797825</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783506396385945</v>
+        <v>6.783524132420256</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784018038034858</v>
+        <v>6.784049253130319</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775476384757434</v>
+        <v>6.775489221221597</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772261719077378</v>
+        <v>6.772263743087401</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768262643130758</v>
+        <v>6.768267178325818</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762070450423492</v>
+        <v>6.762084524740041</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752640325759478</v>
+        <v>6.752662441568109</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740416365436213</v>
+        <v>6.740447227658612</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728512467060865</v>
+        <v>6.728321615748641</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718725791447302</v>
+        <v>6.718802965211195</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712247203029022</v>
+        <v>6.712693886255793</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709001716584439</v>
+        <v>6.709364640887028</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.706808401936112</v>
+        <v>6.707425837346303</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.693852524820543</v>
+        <v>6.694726322527499</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.676161210108571</v>
+        <v>6.677407852956579</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.654539867541539</v>
+        <v>6.656353658930517</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.618371107144724</v>
+        <v>6.621595214308083</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.610285398303444</v>
+        <v>6.613984004014331</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.611793133053832</v>
+        <v>6.615615167837437</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.641500963118586</v>
+        <v>6.64395241059542</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.636041547737975</v>
+        <v>6.639621501902349</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.668620782017001</v>
+        <v>6.666804154985559</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141482569871362</v>
+        <v>7.141478304478559</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151626644562694</v>
+        <v>7.151619519637001</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155139197840049</v>
+        <v>7.155132194944564</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168500716054192</v>
+        <v>7.168492865237145</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183463386688759</v>
+        <v>7.183455944507065</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.19541344905373</v>
+        <v>7.195406521231594</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197698352819133</v>
+        <v>7.197692088432303</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192239976209322</v>
+        <v>7.192234432914643</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175482408943976</v>
+        <v>7.175485641932561</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180317894489329</v>
+        <v>7.180325754898228</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184356672581914</v>
+        <v>7.184364047045984</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189456901349624</v>
+        <v>7.189464186858483</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183229140868658</v>
+        <v>7.183242293589461</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182387637820995</v>
+        <v>7.182402976409752</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183468579916857</v>
+        <v>7.183481404888521</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168761723639019</v>
+        <v>7.168772930760225</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155354128415927</v>
+        <v>7.155370762613374</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148164312370794</v>
+        <v>7.148183313557634</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.143982350767303</v>
+        <v>7.144006008477375</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124051620370795</v>
+        <v>7.124071024373313</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111438959206325</v>
+        <v>7.111465207597743</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102850947792401</v>
+        <v>7.102880654632998</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075104280888776</v>
+        <v>7.075137526589912</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050502289639347</v>
+        <v>7.050536383794963</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048848669864332</v>
+        <v>7.048884848371051</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047346887294688</v>
+        <v>7.047391774893804</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.05425790213816</v>
+        <v>7.054313089730207</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.059751530505593</v>
+        <v>7.059827946797868</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.015244904755274</v>
+        <v>7.015314816649624</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967776702477305</v>
+        <v>6.967833561876975</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968388385222216</v>
+        <v>6.968443884839265</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.94851205976282</v>
+        <v>6.948582722108348</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898152450348592</v>
+        <v>6.898191158254273</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861608307967954</v>
+        <v>6.861648898674845</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847313572044471</v>
+        <v>6.847347563398889</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824039065679944</v>
+        <v>6.824010710122971</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842745685759424</v>
+        <v>6.842708942796763</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.857175024770864</v>
+        <v>6.857097120822763</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888161277218012</v>
+        <v>6.888123578111736</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.89048924418441</v>
+        <v>6.890463749337222</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.878034143635314</v>
+        <v>6.877990085152989</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871895395779317</v>
+        <v>6.871924827311391</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.845998050935043</v>
+        <v>6.846015148795577</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841930049740872</v>
+        <v>6.841958654930618</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807683952135761</v>
+        <v>6.807642782037707</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.8239477126377</v>
+        <v>6.823950275387359</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.81876927094798</v>
+        <v>6.818799402245456</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813408768103736</v>
+        <v>6.813443240819231</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807381857928038</v>
+        <v>6.807421613533882</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.802981586799492</v>
+        <v>6.803024922491671</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801268214797825</v>
+        <v>6.801314800079361</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783524132420256</v>
+        <v>6.783541460571285</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784049253130319</v>
+        <v>6.784079791922013</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775489221221597</v>
+        <v>6.775501809935037</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772263743087401</v>
+        <v>6.772265757859794</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768267178325818</v>
+        <v>6.768271601465243</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762084524740041</v>
+        <v>6.762098215075204</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752662441568109</v>
+        <v>6.752683989425663</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740447227658612</v>
+        <v>6.740477332309068</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728321615748641</v>
+        <v>6.728140136750184</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718802965211195</v>
+        <v>6.718837162146723</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.712693886255793</v>
+        <v>6.713069186831523</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709364640887028</v>
+        <v>6.709637406154679</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707425837346303</v>
+        <v>6.707909440749485</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.694726322527499</v>
+        <v>6.695461660136736</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.677407852956579</v>
+        <v>6.67855848125151</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.656353658930517</v>
+        <v>6.658146948080503</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.621595214308083</v>
+        <v>6.624868401021802</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.613984004014331</v>
+        <v>6.618107959424101</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.615615167837437</v>
+        <v>6.620393612083451</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.64395241059542</v>
+        <v>6.648456157000846</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.639621501902349</v>
+        <v>6.646909500204895</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.666804154985559</v>
+        <v>6.676265275616299</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141478304478559</v>
+        <v>7.141474137127657</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151619519637001</v>
+        <v>7.151612557971217</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155132194944564</v>
+        <v>7.155125351390383</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168492865237145</v>
+        <v>7.168485192853695</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183455944507065</v>
+        <v>7.183448671592284</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195406521231594</v>
+        <v>7.195399751089948</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197692088432303</v>
+        <v>7.197685966645306</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192234432914643</v>
+        <v>7.192229015767749</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175485641932561</v>
+        <v>7.175488796197455</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180325754898228</v>
+        <v>7.180333433488546</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184364047045984</v>
+        <v>7.184371251088606</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189464186858483</v>
+        <v>7.189471304114754</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183242293589461</v>
+        <v>7.183255142761497</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182402976409752</v>
+        <v>7.182417962498866</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183481404888521</v>
+        <v>7.183493935112433</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168772930760225</v>
+        <v>7.168783876744092</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155370762613374</v>
+        <v>7.15538701109133</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148183313557634</v>
+        <v>7.148201874676277</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144006008477375</v>
+        <v>7.144029122037492</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124071024373313</v>
+        <v>7.124089977628103</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111465207597743</v>
+        <v>7.11149085480117</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102880654632998</v>
+        <v>7.102909687111845</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075137526589912</v>
+        <v>7.075170027595485</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050536383794963</v>
+        <v>7.050569714830756</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048884848371051</v>
+        <v>7.0489202125277</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047391774893804</v>
+        <v>7.047435640368126</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054313089730207</v>
+        <v>7.054367014038793</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.059827946797868</v>
+        <v>7.059902606327427</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.015314816649624</v>
+        <v>7.015383107410846</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967833561876975</v>
+        <v>6.967889120741618</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968443884839265</v>
+        <v>6.968498131099052</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.948582722108348</v>
+        <v>6.948651849120414</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898191158254273</v>
+        <v>6.898229039221756</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861648898674845</v>
+        <v>6.861688628819905</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847347563398889</v>
+        <v>6.847380867557997</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.824010710122971</v>
+        <v>6.823983036330445</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842708942796763</v>
+        <v>6.842673069397941</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.857097120822763</v>
+        <v>6.857020964597705</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888123578111736</v>
+        <v>6.88808672254993</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890463749337222</v>
+        <v>6.890438797039748</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877990085152989</v>
+        <v>6.877946966714811</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871924827311391</v>
+        <v>6.871953601412573</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846015148795577</v>
+        <v>6.846031880125215</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841958654930618</v>
+        <v>6.841986644060631</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807642782037707</v>
+        <v>6.807602478447317</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823950275387359</v>
+        <v>6.823952746030275</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818799402245456</v>
+        <v>6.818828819184473</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813443240819231</v>
+        <v>6.813476899373529</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807421613533882</v>
+        <v>6.807460446002399</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803024922491671</v>
+        <v>6.803067273330059</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801314800079361</v>
+        <v>6.801360359323983</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783541460571285</v>
+        <v>6.783558394667429</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784079791922013</v>
+        <v>6.784109675983919</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775501809935037</v>
+        <v>6.775514157748745</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772265757859794</v>
+        <v>6.772267762561935</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768271601465243</v>
+        <v>6.76827591675209</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762098215075204</v>
+        <v>6.762111536423783</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752683989425663</v>
+        <v>6.752704990127517</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740477332309068</v>
+        <v>6.740506705852082</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728140136750184</v>
+        <v>6.728279300520877</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.718837162146723</v>
+        <v>6.719234849051219</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.713069186831523</v>
+        <v>6.7138225578974</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.709637406154679</v>
+        <v>6.710583806743206</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.707909440749485</v>
+        <v>6.70889834596922</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.695461660136736</v>
+        <v>6.69672485780208</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.67855848125151</v>
+        <v>6.680253404950341</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.658146948080503</v>
+        <v>6.660504136139267</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.624868401021802</v>
+        <v>6.628721109735423</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.618107959424101</v>
+        <v>6.622926891387717</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.620393612083451</v>
+        <v>6.625970305189877</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.648456157000846</v>
+        <v>6.654077133619295</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.646909500204895</v>
+        <v>6.655402675587516</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.676265275616299</v>
+        <v>6.68738404796384</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B114"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141474137127657</v>
+        <v>7.141470064476906</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151612557971217</v>
+        <v>7.151605754018053</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155125351390383</v>
+        <v>7.155118661801569</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168485192853695</v>
+        <v>7.168477692890676</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183448671592284</v>
+        <v>7.183441562236016</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195399751089948</v>
+        <v>7.195393133307278</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197685966645306</v>
+        <v>7.197679982644846</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192229015767749</v>
+        <v>7.192223720511853</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175488796197455</v>
+        <v>7.175491874569837</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180333433488546</v>
+        <v>7.180340936495299</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184371251088606</v>
+        <v>7.184378290548737</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189471304114754</v>
+        <v>7.189478258879302</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183255142761497</v>
+        <v>7.183267698769862</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182417962498866</v>
+        <v>7.182432608095944</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183493935112433</v>
+        <v>7.183506180631323</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168783876744092</v>
+        <v>7.168794570606906</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.15538701109133</v>
+        <v>7.155402887102482</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148201874676277</v>
+        <v>7.14822001082454</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144029122037492</v>
+        <v>7.144051709996671</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124089977628103</v>
+        <v>7.124108495648356</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11149085480117</v>
+        <v>7.111515921213954</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102909687111845</v>
+        <v>7.102938067900912</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075170027595485</v>
+        <v>7.075201808613846</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050569714830756</v>
+        <v>7.050602308044175</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.0489202125277</v>
+        <v>7.048954789486356</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047435640368126</v>
+        <v>7.047478518196092</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054367014038793</v>
+        <v>7.054419717888059</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.059902606327427</v>
+        <v>7.059975568876948</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.015383107410846</v>
+        <v>7.015449832688438</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967889120741618</v>
+        <v>6.967943423050406</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968498131099052</v>
+        <v>6.968551165832503</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.948651849120414</v>
+        <v>6.948719490092031</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898229039221756</v>
+        <v>6.898266119309971</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861688628819905</v>
+        <v>6.861727525289687</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847380867557997</v>
+        <v>6.847413504780745</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823983036330445</v>
+        <v>6.823956020129962</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842673069397941</v>
+        <v>6.842638035181454</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.857020964597705</v>
+        <v>6.856946498054786</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.88808672254993</v>
+        <v>6.888050682598332</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890438797039748</v>
+        <v>6.890414370304635</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877946966714811</v>
+        <v>6.877904758733854</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871953601412573</v>
+        <v>6.871981739855108</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846031880125215</v>
+        <v>6.846048256553132</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.841986644060631</v>
+        <v>6.842014036793079</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807602478447317</v>
+        <v>6.807563014525549</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823952746030275</v>
+        <v>6.823955128783442</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818828819184473</v>
+        <v>6.81885754676895</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813476899373529</v>
+        <v>6.813509772146691</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807460446002399</v>
+        <v>6.807498387003876</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803067273330059</v>
+        <v>6.803108672402741</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801360359323983</v>
+        <v>6.801404925921208</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783558394667429</v>
+        <v>6.783574947922652</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784109675983919</v>
+        <v>6.784138925990018</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775514157748745</v>
+        <v>6.775526271276171</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772267762561935</v>
+        <v>6.772269756444407</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.76827591675209</v>
+        <v>6.76828012817867</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762111536423783</v>
+        <v>6.7621245030297</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752704990127517</v>
+        <v>6.752725463497352</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740506705852082</v>
+        <v>6.740535373576485</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728279300520877</v>
+        <v>6.728313463520879</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.719234849051219</v>
+        <v>6.719422182735252</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.7138225578974</v>
+        <v>6.714076722632472</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.710583806743206</v>
+        <v>6.710992801329007</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.70889834596922</v>
+        <v>6.709555612326158</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.69672485780208</v>
+        <v>6.697592038510154</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.680253404950341</v>
+        <v>6.68152040449878</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.660504136139267</v>
+        <v>6.662370978502631</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.628721109735423</v>
+        <v>6.631921466723988</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.622926891387717</v>
+        <v>6.626915690579701</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.625970305189877</v>
+        <v>6.6305762026046</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.654077133619295</v>
+        <v>6.658560803163707</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.655402675587516</v>
+        <v>6.661988365406739</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,15 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.68738404796384</v>
+        <v>6.694504567953635</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B115">
+        <v>6.727772692953634</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141470064476906</v>
+        <v>7.141466083334707</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151605754018053</v>
+        <v>7.151599102478698</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155118661801569</v>
+        <v>7.155112121041265</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168477692890676</v>
+        <v>7.168470359602039</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183441562236016</v>
+        <v>7.183434610983632</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195393133307278</v>
+        <v>7.195386662798806</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197679982644846</v>
+        <v>7.197674131831801</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192223720511853</v>
+        <v>7.192218543079521</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175491874569837</v>
+        <v>7.175494879747125</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180340936495299</v>
+        <v>7.180348269871699</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184378290548737</v>
+        <v>7.184385171001651</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189478258879302</v>
+        <v>7.189485056653004</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183267698769862</v>
+        <v>7.18327997153142</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182432608095944</v>
+        <v>7.182446924669593</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183506180631323</v>
+        <v>7.183518151036914</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168794570606906</v>
+        <v>7.16880502095484</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155402887102482</v>
+        <v>7.155418403299701</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.14822001082454</v>
+        <v>7.148237736418085</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144051709996671</v>
+        <v>7.144073790070841</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124108495648356</v>
+        <v>7.124126593244004</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111515921213954</v>
+        <v>7.111540426322035</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102938067900912</v>
+        <v>7.102965818668577</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075201808613846</v>
+        <v>7.075232893273821</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050602308044175</v>
+        <v>7.050634187628519</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.048954789486356</v>
+        <v>7.04898860520694</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047478518196092</v>
+        <v>7.047520441324452</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054419717888059</v>
+        <v>7.054471242190868</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.059975568876948</v>
+        <v>7.060046891551789</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.015449832688438</v>
+        <v>7.015515045617619</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967943423050406</v>
+        <v>6.967996510827674</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968551165832503</v>
+        <v>6.968603029036339</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.948719490092031</v>
+        <v>6.948785692237879</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898266119309971</v>
+        <v>6.898302423501699</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861727525289687</v>
+        <v>6.86176561387119</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847413504780745</v>
+        <v>6.847445494555609</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823956020129962</v>
+        <v>6.823929638473411</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842638035181454</v>
+        <v>6.842603811159539</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.856946498054786</v>
+        <v>6.856873665689657</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.888050682598332</v>
+        <v>6.88801543153973</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890414370304635</v>
+        <v>6.890390452839332</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877904758733854</v>
+        <v>6.877863432843523</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.871981739855108</v>
+        <v>6.872009263460867</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846048256553132</v>
+        <v>6.846064289223039</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842014036793079</v>
+        <v>6.842040851963301</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807563014525549</v>
+        <v>6.807524364519638</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823955128783442</v>
+        <v>6.823957427628412</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.81885754676895</v>
+        <v>6.818885608853678</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813509772146691</v>
+        <v>6.813541886220237</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807498387003876</v>
+        <v>6.807535466781195</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803108672402741</v>
+        <v>6.803149151336754</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801404925921208</v>
+        <v>6.801448531833642</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783574947922652</v>
+        <v>6.78359113297003</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784138925990018</v>
+        <v>6.784167561760292</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775526271276171</v>
+        <v>6.775538156902607</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772269756444407</v>
+        <v>6.772271738834165</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.76828012817867</v>
+        <v>6.768284239539693</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.7621245030297</v>
+        <v>6.762137128431442</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752725463497352</v>
+        <v>6.752745428441703</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740535373576485</v>
+        <v>6.740563359657831</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728313463520879</v>
+        <v>6.728346926034369</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.719422182735252</v>
+        <v>6.719516541441462</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.714076722632472</v>
+        <v>6.714205868577883</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.710992801329007</v>
+        <v>6.711237371290138</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.709555612326158</v>
+        <v>6.709803974582512</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.697592038510154</v>
+        <v>6.698097806944546</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.68152040449878</v>
+        <v>6.682437085203583</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.662370978502631</v>
+        <v>6.663871879834227</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.631921466723988</v>
+        <v>6.634656680174023</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.626915690579701</v>
+        <v>6.630332260835518</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.6305762026046</v>
+        <v>6.634480538173651</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.658560803163707</v>
+        <v>6.662185455812367</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.661988365406739</v>
+        <v>6.667080028467875</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.694504567953635</v>
+        <v>6.698930799797086</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.727772692953634</v>
+        <v>6.732056036016798</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141466083334707</v>
+        <v>7.141462190651292</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151599102478698</v>
+        <v>7.151592598289056</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155112121041265</v>
+        <v>7.155105724198567</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168470359602039</v>
+        <v>7.16846318749419</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183434610983632</v>
+        <v>7.183427812620322</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195386662798806</v>
+        <v>7.195380334703484</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197674131831801</v>
+        <v>7.197668409809437</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192218543079521</v>
+        <v>7.19221347958227</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175494879747125</v>
+        <v>7.175497814300781</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180348269871699</v>
+        <v>7.180355439304886</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184385171001651</v>
+        <v>7.184391897773667</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189485056653004</v>
+        <v>7.189491702691249</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.18327997153142</v>
+        <v>7.183291970520871</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182446924669593</v>
+        <v>7.182460923179308</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183518151036914</v>
+        <v>7.183529855494985</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.16880502095484</v>
+        <v>7.168815236007018</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155418403299701</v>
+        <v>7.155433571769573</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148237736418085</v>
+        <v>7.148255065228467</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144073790070841</v>
+        <v>7.14409537918907</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124126593244004</v>
+        <v>7.124144284561087</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111540426322035</v>
+        <v>7.11156438875025</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102965818668577</v>
+        <v>7.102992960134475</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075232893273821</v>
+        <v>7.075263304182972</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050634187628519</v>
+        <v>7.050665376732441</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.04898860520694</v>
+        <v>7.049021684521854</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047520441324452</v>
+        <v>7.047561441252276</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054471242190868</v>
+        <v>7.054521626054105</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.060046891551789</v>
+        <v>7.060116628927946</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.015515045617619</v>
+        <v>7.015578796959524</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.967996510827674</v>
+        <v>6.968048424250027</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968603029036339</v>
+        <v>6.968653758972165</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.948785692237879</v>
+        <v>6.94885050080215</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898302423501699</v>
+        <v>6.898337975758134</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.86176561387119</v>
+        <v>6.861802919306994</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847445494555609</v>
+        <v>6.847476855635767</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823929638473411</v>
+        <v>6.823903869372627</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842603811159539</v>
+        <v>6.842570369659436</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.856873665689657</v>
+        <v>6.856802414397742</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.88801543153973</v>
+        <v>6.887980943808552</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890390452839332</v>
+        <v>6.890367029011337</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877863432843523</v>
+        <v>6.877822961835758</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872009263460867</v>
+        <v>6.872036192152617</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846064289223039</v>
+        <v>6.846079988818183</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842040851963301</v>
+        <v>6.84206710762277</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807524364519638</v>
+        <v>6.807486503709324</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823957427628412</v>
+        <v>6.823959646326785</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818885608853678</v>
+        <v>6.818913028209375</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813541886220237</v>
+        <v>6.813573267450304</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807535466781195</v>
+        <v>6.807571714229099</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803149151336754</v>
+        <v>6.803188740377594</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801448531833642</v>
+        <v>6.801491207672038</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.78359113297003</v>
+        <v>6.783606961893138</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784167561760292</v>
+        <v>6.78419560230393</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775538156902607</v>
+        <v>6.7755498207942</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772271738834165</v>
+        <v>6.772273709128274</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768284239539693</v>
+        <v>6.768288254444443</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762137128431442</v>
+        <v>6.762149425504283</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752745428441703</v>
+        <v>6.752764903000933</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740563359657831</v>
+        <v>6.740590687216993</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728346926034369</v>
+        <v>6.728379708348609</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.719516541441462</v>
+        <v>6.719529544870301</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.714205868577883</v>
+        <v>6.714232800970096</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.711237371290138</v>
+        <v>6.711350637240614</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.709803974582512</v>
+        <v>6.709888820018142</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.698097806944546</v>
+        <v>6.698398258893564</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.682437085203583</v>
+        <v>6.683084659684566</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.663871879834227</v>
+        <v>6.665012187429882</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.634656680174023</v>
+        <v>6.636854187862794</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.630332260835518</v>
+        <v>6.633012898936833</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.634480538173651</v>
+        <v>6.637356840074163</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.662185455812367</v>
+        <v>6.664466609492665</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.667080028467875</v>
+        <v>6.670049049565153</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.698930799797086</v>
+        <v>6.699941250457366</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.732056036016798</v>
+        <v>6.723543710568315</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141462190651292</v>
+        <v>7.14145838351091</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151592598289056</v>
+        <v>7.151586236606908</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.155105724198567</v>
+        <v>7.15509946657623</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.16846318749419</v>
+        <v>7.168456171312263</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183427812620322</v>
+        <v>7.183421162158064</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195380334703484</v>
+        <v>7.195374144371813</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197668409809437</v>
+        <v>7.197662812372394</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.19221347958227</v>
+        <v>7.192208526300819</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175497814300781</v>
+        <v>7.175500680683547</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180355439304886</v>
+        <v>7.180362450230641</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184391897773667</v>
+        <v>7.184398475955882</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189491702691249</v>
+        <v>7.189498202017498</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183291970520871</v>
+        <v>7.183303704795126</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182460923179308</v>
+        <v>7.182474614103413</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183529855494985</v>
+        <v>7.183541302768719</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168815236007018</v>
+        <v>7.168825223617003</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155433571769573</v>
+        <v>7.15544840406371</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148255065228467</v>
+        <v>7.148272010418694</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.14409537918907</v>
+        <v>7.144116493536741</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124144284561087</v>
+        <v>7.124161583118528</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.11156438875025</v>
+        <v>7.111587826309308</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.102992960134475</v>
+        <v>7.103019512120786</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075263304182972</v>
+        <v>7.075293062982074</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050665376732441</v>
+        <v>7.050695897515624</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049021684521854</v>
+        <v>7.049054051196453</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047561441252276</v>
+        <v>7.047601548109538</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054521626054105</v>
+        <v>7.054570906877107</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.060116628927946</v>
+        <v>7.06018483319032</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.015578796959524</v>
+        <v>7.015641135232139</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968048424250027</v>
+        <v>6.968099201746469</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968653758972165</v>
+        <v>6.968703392259181</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.94885050080215</v>
+        <v>6.948913959159818</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898337975758134</v>
+        <v>6.89837279907019</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861802919306994</v>
+        <v>6.861839465347125</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847476855635767</v>
+        <v>6.847507606072441</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823903869372627</v>
+        <v>6.823878691839382</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842570369659436</v>
+        <v>6.842537684249901</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.856802414397742</v>
+        <v>6.85673269334621</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887980943808552</v>
+        <v>6.887947194929612</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890367029011337</v>
+        <v>6.890344083815494</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877822961835758</v>
+        <v>6.877783319602937</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872036192152617</v>
+        <v>6.872062545002011</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846079988818183</v>
+        <v>6.846095365584832</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.84206710762277</v>
+        <v>6.842092821079397</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807486503709324</v>
+        <v>6.807449408356185</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823959646326785</v>
+        <v>6.823961788434533</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818913028209375</v>
+        <v>6.81893982658335</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813573267450304</v>
+        <v>6.813603940535913</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807571714229099</v>
+        <v>6.807607156968252</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803188740377594</v>
+        <v>6.803227468463591</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801491207672038</v>
+        <v>6.801532982765703</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783606961893138</v>
+        <v>6.783622446255435</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.78419560230393</v>
+        <v>6.784223065859992</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.7755498207942</v>
+        <v>6.775561268906598</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772273709128274</v>
+        <v>6.772275666788163</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768288254444443</v>
+        <v>6.768292176328046</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762149425504283</v>
+        <v>6.762161406499572</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752764903000933</v>
+        <v>6.752783904396955</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740590687216993</v>
+        <v>6.74061737837522</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728379708348609</v>
+        <v>6.728411830021086</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.719529544870301</v>
+        <v>6.719224316412546</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.714232800970096</v>
+        <v>6.713911588330014</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.711350637240614</v>
+        <v>6.711065560554485</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.709888820018142</v>
+        <v>6.709521651533962</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.698398258893564</v>
+        <v>6.698202051988063</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.683084659684566</v>
+        <v>6.683168841892901</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.665012187429882</v>
+        <v>6.665496337278515</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.636854187862794</v>
+        <v>6.638205756000027</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.633012898936833</v>
+        <v>6.634626975980312</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.637356840074163</v>
+        <v>6.638892191421984</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.664466609492665</v>
+        <v>6.665053188789988</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.670049049565153</v>
+        <v>6.670562880439695</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.699941250457366</v>
+        <v>6.697403256769476</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.723543710568315</v>
+        <v>6.710930290446203</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.14145838351091</v>
+        <v>7.141454659124564</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151586236606908</v>
+        <v>7.151580012799879</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.15509946657623</v>
+        <v>7.15509334367918</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168456171312263</v>
+        <v>7.168449306027321</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.183421162158064</v>
+        <v>7.18341465482343</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195374144371813</v>
+        <v>7.195368087354473</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197662812372394</v>
+        <v>7.197657335496403</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192208526300819</v>
+        <v>7.192203679676012</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175500680683547</v>
+        <v>7.175503481236205</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180362450230641</v>
+        <v>7.180369307847096</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184398475955882</v>
+        <v>7.184404910417008</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189498202017498</v>
+        <v>7.189504559435907</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183303704795126</v>
+        <v>7.183315183016077</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182474614103413</v>
+        <v>7.182488007465161</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183541302768719</v>
+        <v>7.183552501240588</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168825223617003</v>
+        <v>7.168834991292896</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.15544840406371</v>
+        <v>7.155462911227998</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148272010418694</v>
+        <v>7.148288584576424</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144116493536741</v>
+        <v>7.144137148595918</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124161583118528</v>
+        <v>7.124178501842463</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111587826309308</v>
+        <v>7.111610756039764</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103019512120786</v>
+        <v>7.103045493600241</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.075293062982074</v>
+        <v>7.0753221903962</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050695897515624</v>
+        <v>7.050725771200957</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049054051196453</v>
+        <v>7.049085727985673</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047601548109538</v>
+        <v>7.047640790730606</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054570906877107</v>
+        <v>7.054619120443739</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.06018483319032</v>
+        <v>7.060251554262035</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.015641135232139</v>
+        <v>7.015702106832665</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968099201746469</v>
+        <v>6.968148880092141</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968703392259181</v>
+        <v>6.968751963961075</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.948913959159818</v>
+        <v>6.948976108911731</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.89837279907019</v>
+        <v>6.898406915506765</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861839465347125</v>
+        <v>6.861875274797914</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.847507606072441</v>
+        <v>6.84753776324653</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823878691839382</v>
+        <v>6.823854085829419</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842537684249901</v>
+        <v>6.842505729672592</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.85673269334621</v>
+        <v>6.856664453854016</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887947194929612</v>
+        <v>6.887914161460749</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890344083815494</v>
+        <v>6.890321602843169</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877783319602937</v>
+        <v>6.877744481083191</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872062545002011</v>
+        <v>6.872088340274535</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846095365584832</v>
+        <v>6.846110429354312</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842092821079397</v>
+        <v>6.842118008935389</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807449408356185</v>
+        <v>6.807413055655887</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823961788434533</v>
+        <v>6.823963857315241</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.81893982658335</v>
+        <v>6.818966024756183</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813603940535913</v>
+        <v>6.813633929082746</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807607156968252</v>
+        <v>6.807641821414459</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803227468463591</v>
+        <v>6.803265363295563</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801532982765703</v>
+        <v>6.801573885228552</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783622446255435</v>
+        <v>6.783637597127791</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784223065859992</v>
+        <v>6.784249969935662</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775561268906598</v>
+        <v>6.775572506993234</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772275666788163</v>
+        <v>6.772277611334381</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768292176328046</v>
+        <v>6.768296008461942</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762161406499572</v>
+        <v>6.762173083081316</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752783904396955</v>
+        <v>6.752802449077913</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.74061737837522</v>
+        <v>6.740643454305902</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728411830021086</v>
+        <v>6.728443309909365</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.719224316412546</v>
+        <v>6.71893399542614</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.713911588330014</v>
+        <v>6.713586124644277</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.711065560554485</v>
+        <v>6.710744859479192</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.709521651533962</v>
+        <v>6.709064865448784</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.698202051988063</v>
+        <v>6.697907938182547</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.683168841892901</v>
+        <v>6.683174725290147</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.665496337278515</v>
+        <v>6.665964429262617</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.638205756000027</v>
+        <v>6.639611147664002</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.634626975980312</v>
+        <v>6.636389852976198</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.638892191421984</v>
+        <v>6.640712499309021</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.665053188789988</v>
+        <v>6.666034169920652</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.670562880439695</v>
+        <v>6.671479706682907</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.697403256769476</v>
+        <v>6.695846617220815</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.710930290446203</v>
+        <v>6.704223671992218</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_forecast.xlsx
+++ b/public/data/files/USDCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>7.141454659124564</v>
+        <v>7.141451014823187</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>7.151580012799879</v>
+        <v>7.1515739224342</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>7.15509334367918</v>
+        <v>7.155087351203756</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>7.168449306027321</v>
+        <v>7.16844258682432</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>7.18341465482343</v>
+        <v>7.183408286046174</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>7.195368087354473</v>
+        <v>7.19536215939166</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>7.197657335496403</v>
+        <v>7.197651975328624</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>7.192203679676012</v>
+        <v>7.192198936300267</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>7.175503481236205</v>
+        <v>7.175506218193879</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>7.180369307847096</v>
+        <v>7.1803760171276</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>7.184404910417008</v>
+        <v>7.184411205815397</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>7.189504559435907</v>
+        <v>7.189510779543191</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>7.183315183016077</v>
+        <v>7.183326413471891</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>7.182488007465161</v>
+        <v>7.182501112857166</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>7.183552501240588</v>
+        <v>7.183563458932774</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>7.168834991292896</v>
+        <v>7.168844546216115</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>7.155462911227998</v>
+        <v>7.155477103829962</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>7.148288584576424</v>
+        <v>7.148304799745043</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>7.144137148595918</v>
+        <v>7.14415735918313</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>7.124178501842463</v>
+        <v>7.12419505309837</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>7.111610756039764</v>
+        <v>7.11163319425315</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>7.103045493600241</v>
+        <v>7.10307092274108</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>7.0753221903962</v>
+        <v>7.075350706282556</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>7.050725771200957</v>
+        <v>7.050755018123462</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>7.049085727985673</v>
+        <v>7.049116736687098</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>7.047640790730606</v>
+        <v>7.047679196723072</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>7.054619120443739</v>
+        <v>7.054666301008563</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>7.060251554262035</v>
+        <v>7.060316839925454</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>7.015702106832665</v>
+        <v>7.015761756151985</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>6.968148880092141</v>
+        <v>6.968197494496094</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>6.968751963961075</v>
+        <v>6.968799507667458</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>6.948976108911731</v>
+        <v>6.949036989973997</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>6.898406915506765</v>
+        <v>6.898440346260188</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>6.861875274797914</v>
+        <v>6.861910369568017</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>6.84753776324653</v>
+        <v>6.847567343898588</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>6.823854085829419</v>
+        <v>6.823830032190152</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>6.842505729672592</v>
+        <v>6.842474481777926</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>6.856664453854016</v>
+        <v>6.856597649279449</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>6.887914161460749</v>
+        <v>6.887881820938985</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>6.890321602843169</v>
+        <v>6.890299572253221</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>6.877744481083191</v>
+        <v>6.877706422208937</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>6.872088340274535</v>
+        <v>6.872113595471641</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>6.846110429354312</v>
+        <v>6.846125189563772</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>6.842118008935389</v>
+        <v>6.842142687122804</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>6.807413055655887</v>
+        <v>6.807377423693177</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>6.823963857315241</v>
+        <v>6.823965856152384</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>6.818966024756183</v>
+        <v>6.818991642594668</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>6.813633929082746</v>
+        <v>6.81366325566277</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>6.807641821414459</v>
+        <v>6.807675732843469</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>6.803265363295563</v>
+        <v>6.803302451402061</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>6.801573885228552</v>
+        <v>6.801613942021162</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>6.783637597127791</v>
+        <v>6.783652425114305</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>6.784249969935662</v>
+        <v>6.784276331342271</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>6.775572506993234</v>
+        <v>6.775583540613288</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>6.772277611334381</v>
+        <v>6.772279542341751</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>6.768296008461942</v>
+        <v>6.768299753963592</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>6.762173083081316</v>
+        <v>6.762184466360259</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>6.752802449077913</v>
+        <v>6.75282055276003</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>6.740643454305902</v>
+        <v>6.740668935283237</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>6.728443309909365</v>
+        <v>6.728474166199662</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>6.71893399542614</v>
+        <v>6.718657596537502</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>6.713586124644277</v>
+        <v>6.713297224522567</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>6.710744859479192</v>
+        <v>6.710481355985825</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>6.709064865448784</v>
+        <v>6.708619737858625</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>6.697907938182547</v>
+        <v>6.697553060383791</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>6.683174725290147</v>
+        <v>6.683124508306807</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>6.665964429262617</v>
+        <v>6.666541845978964</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>6.639611147664002</v>
+        <v>6.641487582476044</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>6.636389852976198</v>
+        <v>6.639315987244158</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>6.640712499309021</v>
+        <v>6.645199727522768</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>6.666034169920652</v>
+        <v>6.671755012563433</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>6.671479706682907</v>
+        <v>6.680449378719679</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>6.695846617220815</v>
+        <v>6.709070180568981</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>6.704223671992218</v>
+        <v>6.732439890636634</v>
       </c>
     </row>
   </sheetData>
